--- a/Docs/SmartFlow Beauty Demo.xlsx
+++ b/Docs/SmartFlow Beauty Demo.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="374">
   <si>
     <t>key</t>
   </si>
@@ -109,7 +109,7 @@
     <t>ClientWebAppUrl</t>
   </si>
   <si>
-    <t>https://script.google.com/macros/s/AKfycbzUf-YieHsYVX0Tyd32LjdiHWzIq4KqAPAYwXZKeM_LJcRvP5X-CthBxlXyxEl-jWc/exec</t>
+    <t>https://script.google.com/macros/s/AKfycbxtu0SbRTctUotAo7xz9YDXntkW6bG4CZOoJDj06ruIlZJ02FeqdUl93UNR1_4FwnF6/exec</t>
   </si>
   <si>
     <t>telegram_id</t>
@@ -119,12 +119,6 @@
   </si>
   <si>
     <t>updated_at</t>
-  </si>
-  <si>
-    <t>WAITING_LOCATION</t>
-  </si>
-  <si>
-    <t>WAITING_PROVIDER</t>
   </si>
   <si>
     <t>timestamp</t>
@@ -199,6 +193,42 @@
 "message":{"message_id":69,"from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"ru"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781130677,"text":"test"}}</t>
   </si>
   <si>
+    <t>DOPOST_ERROR</t>
+  </si>
+  <si>
+    <t>ReferenceError: createRequestOptions is not defined</t>
+  </si>
+  <si>
+    <t>PHONE_STEP</t>
+  </si>
+  <si>
+    <t>phone=+3502452635165</t>
+  </si>
+  <si>
+    <t>PHONE_SAVED</t>
+  </si>
+  <si>
+    <t>SESSION_BEFORE_FINALIZE</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_003","option_count":1,"current_option_date":"2026-06-11T21:00:00.000Z","current_option_time":"1899-12-30T07:27:56.000Z","option1_date":"2026-06-11T21:00:00.000Z","option1_time":"1899-12-30T07:27:56.000Z","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"Анна","customer_phone":"+3502452635165","updated_at":"2026-06-12T19:44:59.612Z"}</t>
+  </si>
+  <si>
+    <t>phone=+38055245256685</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_003","option_count":1,"current_option_date":"2026-06-12T21:00:00.000Z","current_option_time":"1899-12-30T07:27:56.000Z","option1_date":"2026-06-12T21:00:00.000Z","option1_time":"1899-12-30T07:27:56.000Z","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"Анна","customer_phone":"+38055245256685","updated_at":"2026-06-12T19:49:40.516Z"}</t>
+  </si>
+  <si>
+    <t>REQUEST_CREATED_DEBUG</t>
+  </si>
+  <si>
+    <t>req_1781293782259</t>
+  </si>
+  <si>
+    <t>OWNER_NOTIFIED</t>
+  </si>
+  <si>
     <t>location_id</t>
   </si>
   <si>
@@ -214,7 +244,31 @@
     <t>current_option_date</t>
   </si>
   <si>
-    <t>current_option_period</t>
+    <t>current_option_time</t>
+  </si>
+  <si>
+    <t>option1_date</t>
+  </si>
+  <si>
+    <t>option1_time</t>
+  </si>
+  <si>
+    <t>option2_date</t>
+  </si>
+  <si>
+    <t>option2_time</t>
+  </si>
+  <si>
+    <t>option3_date</t>
+  </si>
+  <si>
+    <t>option3_time</t>
+  </si>
+  <si>
+    <t>customer_name</t>
+  </si>
+  <si>
+    <t>customer_phone</t>
   </si>
   <si>
     <t>name_uk</t>
@@ -277,10 +331,10 @@
     <t>created_at</t>
   </si>
   <si>
-    <t>req_001</t>
-  </si>
-  <si>
-    <t>cust_001</t>
+    <t>req_1781292699058</t>
+  </si>
+  <si>
+    <t>cust_1781292698620</t>
   </si>
   <si>
     <t>prov_001</t>
@@ -292,34 +346,106 @@
     <t>pending</t>
   </si>
   <si>
+    <t>req_1781293094142</t>
+  </si>
+  <si>
+    <t>cust_1781293093501</t>
+  </si>
+  <si>
+    <t>prov_003</t>
+  </si>
+  <si>
+    <t>req_1781293501120</t>
+  </si>
+  <si>
+    <t>cust_1781293500779</t>
+  </si>
+  <si>
+    <t>cust_1781293781853</t>
+  </si>
+  <si>
+    <t>confirmed</t>
+  </si>
+  <si>
     <t>option_id</t>
   </si>
   <si>
     <t>preferred_date</t>
   </si>
   <si>
-    <t>preferred_period</t>
+    <t>preferred_time</t>
   </si>
   <si>
     <t>priority</t>
   </si>
   <si>
-    <t>opt_001</t>
-  </si>
-  <si>
-    <t>morning</t>
-  </si>
-  <si>
-    <t>opt_002</t>
-  </si>
-  <si>
-    <t>afternoon</t>
-  </si>
-  <si>
-    <t>opt_003</t>
-  </si>
-  <si>
-    <t>evening</t>
+    <t>opt_1781285491078</t>
+  </si>
+  <si>
+    <t>req_1781285490611</t>
+  </si>
+  <si>
+    <t>opt_1781285491269</t>
+  </si>
+  <si>
+    <t>opt_1781286005171</t>
+  </si>
+  <si>
+    <t>req_1781286004965</t>
+  </si>
+  <si>
+    <t>opt_1781286005299</t>
+  </si>
+  <si>
+    <t>opt_1781286005498</t>
+  </si>
+  <si>
+    <t>opt_1781286476343</t>
+  </si>
+  <si>
+    <t>req_1781286476100</t>
+  </si>
+  <si>
+    <t>opt_1781286476489</t>
+  </si>
+  <si>
+    <t>opt_1781286476729</t>
+  </si>
+  <si>
+    <t>opt_1781287290327</t>
+  </si>
+  <si>
+    <t>req_1781287290026</t>
+  </si>
+  <si>
+    <t>opt_1781287290502</t>
+  </si>
+  <si>
+    <t>opt_1781287703776</t>
+  </si>
+  <si>
+    <t>req_1781287703150</t>
+  </si>
+  <si>
+    <t>opt_1781289975275</t>
+  </si>
+  <si>
+    <t>req_1781289975075</t>
+  </si>
+  <si>
+    <t>approved</t>
+  </si>
+  <si>
+    <t>opt_1781290149204</t>
+  </si>
+  <si>
+    <t>req_1781290148915</t>
+  </si>
+  <si>
+    <t>rejected</t>
+  </si>
+  <si>
+    <t>opt_1781293783659</t>
   </si>
   <si>
     <t>prov_002</t>
@@ -340,330 +466,660 @@
     <t>tuesday</t>
   </si>
   <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>Ганна</t>
+  </si>
+  <si>
+    <t>Анна</t>
+  </si>
+  <si>
+    <t>Ann</t>
+  </si>
+  <si>
+    <t>loc_002</t>
+  </si>
+  <si>
+    <t>Ольга</t>
+  </si>
+  <si>
+    <t>Olga</t>
+  </si>
+  <si>
+    <t>Марина</t>
+  </si>
+  <si>
+    <t>Marina</t>
+  </si>
+  <si>
+    <t>exception_id</t>
+  </si>
+  <si>
+    <t>date_from</t>
+  </si>
+  <si>
+    <t>date_to</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>exc_001</t>
+  </si>
+  <si>
+    <t>vacation</t>
+  </si>
+  <si>
+    <t>Отпуск</t>
+  </si>
+  <si>
+    <t>exc_002</t>
+  </si>
+  <si>
+    <t>sick_leave</t>
+  </si>
+  <si>
+    <t>Больничный</t>
+  </si>
+  <si>
+    <t>notification_id</t>
+  </si>
+  <si>
+    <t>appointment_id</t>
+  </si>
+  <si>
+    <t>send_at</t>
+  </si>
+  <si>
+    <t>sent_at</t>
+  </si>
+  <si>
+    <t>notif_001</t>
+  </si>
+  <si>
+    <t>app_001</t>
+  </si>
+  <si>
+    <t>day_before</t>
+  </si>
+  <si>
+    <t>notif_002</t>
+  </si>
+  <si>
+    <t>two_hours</t>
+  </si>
+  <si>
+    <t>uk</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>START</t>
+  </si>
+  <si>
+    <t>Вітаємо!</t>
+  </si>
+  <si>
+    <t>Добро пожаловать!</t>
+  </si>
+  <si>
+    <t>Welcome!</t>
+  </si>
+  <si>
+    <t>BOOK</t>
+  </si>
+  <si>
+    <t>Записатися</t>
+  </si>
+  <si>
+    <t>Записаться</t>
+  </si>
+  <si>
+    <t>Book</t>
+  </si>
+  <si>
+    <t>SERVICES</t>
+  </si>
+  <si>
+    <t>Послуги</t>
+  </si>
+  <si>
+    <t>Услуги</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>PRICES</t>
+  </si>
+  <si>
+    <t>Ціни</t>
+  </si>
+  <si>
+    <t>Цены</t>
+  </si>
+  <si>
+    <t>Prices</t>
+  </si>
+  <si>
+    <t>CONTACTS</t>
+  </si>
+  <si>
+    <t>Контакти</t>
+  </si>
+  <si>
+    <t>Контакты</t>
+  </si>
+  <si>
+    <t>Contacts</t>
+  </si>
+  <si>
+    <t>SELECT_LOCATION</t>
+  </si>
+  <si>
+    <t>Оберіть філію</t>
+  </si>
+  <si>
+    <t>Выберите филиал</t>
+  </si>
+  <si>
+    <t>Select location</t>
+  </si>
+  <si>
+    <t>SELECT_SERVICE</t>
+  </si>
+  <si>
+    <t>Оберіть послугу</t>
+  </si>
+  <si>
+    <t>Выберите услугу</t>
+  </si>
+  <si>
+    <t>Select service</t>
+  </si>
+  <si>
+    <t>SELECT_PROVIDER</t>
+  </si>
+  <si>
+    <t>Оберіть майстра</t>
+  </si>
+  <si>
+    <t>Выберите мастера</t>
+  </si>
+  <si>
+    <t>Select provider</t>
+  </si>
+  <si>
+    <t>SELECT_DATE</t>
+  </si>
+  <si>
+    <t>Оберіть перший зручний день</t>
+  </si>
+  <si>
+    <t>Выберите первый удобный день</t>
+  </si>
+  <si>
+    <t>Select first preferred day</t>
+  </si>
+  <si>
+    <t>LOCATION_SELECT_FROM_LIST</t>
+  </si>
+  <si>
+    <t>Будь ласка, оберіть філію кнопкою зі списку.</t>
+  </si>
+  <si>
+    <t>Пожалуйста, выберите филиал кнопкой из списка.</t>
+  </si>
+  <si>
+    <t>Please select a location from the list.</t>
+  </si>
+  <si>
+    <t>SERVICE_SELECT_FROM_LIST</t>
+  </si>
+  <si>
+    <t>Будь ласка, оберіть послугу кнопкою зі списку.</t>
+  </si>
+  <si>
+    <t>Пожалуйста, выберите услугу кнопкой из списка.</t>
+  </si>
+  <si>
+    <t>Please select a service from the list.</t>
+  </si>
+  <si>
+    <t>PROVIDER_SELECT_FROM_LIST</t>
+  </si>
+  <si>
+    <t>Будь ласка, оберіть майстра кнопкою зі списку.</t>
+  </si>
+  <si>
+    <t>Пожалуйста, выберите мастера кнопкой из списка.</t>
+  </si>
+  <si>
+    <t>Please select a provider from the list.</t>
+  </si>
+  <si>
+    <t>UNKNOWN_COMMAND</t>
+  </si>
+  <si>
+    <t>Поки я розумію тільки команду /start</t>
+  </si>
+  <si>
+    <t>Пока я понимаю только команду /start</t>
+  </si>
+  <si>
+    <t>Currently I only understand the /start command.</t>
+  </si>
+  <si>
+    <t>ANY_PROVIDER</t>
+  </si>
+  <si>
+    <t>Будь-який майстер</t>
+  </si>
+  <si>
+    <t>Любой мастер</t>
+  </si>
+  <si>
+    <t>Any provider</t>
+  </si>
+  <si>
+    <t>TODAY</t>
+  </si>
+  <si>
+    <t>Сьогодні</t>
+  </si>
+  <si>
+    <t>Сегодня</t>
+  </si>
+  <si>
+    <t>Today</t>
+  </si>
+  <si>
+    <t>TOMORROW</t>
+  </si>
+  <si>
+    <t>Завтра</t>
+  </si>
+  <si>
+    <t>Tomorrow</t>
+  </si>
+  <si>
+    <t>DAY_AFTER_TOMORROW</t>
+  </si>
+  <si>
+    <t>Післязавтра</t>
+  </si>
+  <si>
+    <t>Послезавтра</t>
+  </si>
+  <si>
+    <t>Day after tomorrow</t>
+  </si>
+  <si>
+    <t>OTHER_DATE</t>
+  </si>
+  <si>
+    <t>Інша дата</t>
+  </si>
+  <si>
+    <t>Другая дата</t>
+  </si>
+  <si>
+    <t>Other date</t>
+  </si>
+  <si>
+    <t>SESSION_LOCATION_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>Не вдалося знайти вибрану філію. Почніть заново: /start</t>
+  </si>
+  <si>
+    <t>Не найден выбранный филиал. Начните заново: /start</t>
+  </si>
+  <si>
+    <t>Selected location not found. Please start again: /start</t>
+  </si>
+  <si>
+    <t>SELECT_PERIOD</t>
+  </si>
+  <si>
+    <t>Оберіть зручний період</t>
+  </si>
+  <si>
+    <t>Выберите удобный период</t>
+  </si>
+  <si>
+    <t>Select preferred period</t>
+  </si>
+  <si>
+    <t>MORNING</t>
+  </si>
+  <si>
+    <t>Ранок</t>
+  </si>
+  <si>
+    <t>Утро</t>
+  </si>
+  <si>
+    <t>Morning</t>
+  </si>
+  <si>
+    <t>AFTERNOON</t>
+  </si>
+  <si>
+    <t>День</t>
+  </si>
+  <si>
+    <t>Afternoon</t>
+  </si>
+  <si>
+    <t>EVENING</t>
+  </si>
+  <si>
+    <t>Вечір</t>
+  </si>
+  <si>
+    <t>Вечер</t>
+  </si>
+  <si>
+    <t>Evening</t>
+  </si>
+  <si>
+    <t>DATE_SELECT_FROM_LIST</t>
+  </si>
+  <si>
+    <t>Будь ласка, оберіть дату кнопкою зі списку.</t>
+  </si>
+  <si>
+    <t>Пожалуйста, выберите дату кнопкой из списка.</t>
+  </si>
+  <si>
+    <t>Please select a date from the list.</t>
+  </si>
+  <si>
+    <t>ADD_ANOTHER_OPTION</t>
+  </si>
+  <si>
+    <t>Додати ще один варіант?</t>
+  </si>
+  <si>
+    <t>Добавить ещё один вариант?</t>
+  </si>
+  <si>
+    <t>Add another option?</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Так</t>
+  </si>
+  <si>
+    <t>Да</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>NO_CONTINUE</t>
+  </si>
+  <si>
+    <t>Ні, продовжити</t>
+  </si>
+  <si>
+    <t>Нет, продолжить</t>
+  </si>
+  <si>
+    <t>No, continue</t>
+  </si>
+  <si>
+    <t>PERIOD_SELECT_FROM_LIST</t>
+  </si>
+  <si>
+    <t>Будь ласка, оберіть період кнопкою зі списку.</t>
+  </si>
+  <si>
+    <t>Пожалуйста, выберите период кнопкой из списка.</t>
+  </si>
+  <si>
+    <t>Please select a period from the list.</t>
+  </si>
+  <si>
+    <t>ENTER_NAME</t>
+  </si>
+  <si>
+    <t>Введіть ваше ім'я</t>
+  </si>
+  <si>
+    <t>Введите ваше имя</t>
+  </si>
+  <si>
+    <t>Enter your name</t>
+  </si>
+  <si>
+    <t>ENTER_PHONE</t>
+  </si>
+  <si>
+    <t>Введіть ваш телефон (+38...)</t>
+  </si>
+  <si>
+    <t>Введите ваш телефон (+38...)</t>
+  </si>
+  <si>
+    <t>Enter your phone number (+1...)</t>
+  </si>
+  <si>
+    <t>REQUEST_DRAFT_READY</t>
+  </si>
+  <si>
+    <t>Чернетка заявки готова</t>
+  </si>
+  <si>
+    <t>Черновик заявки готов</t>
+  </si>
+  <si>
+    <t>Request draft is ready</t>
+  </si>
+  <si>
+    <t>REQUEST_CREATED</t>
+  </si>
+  <si>
+    <t>Заявку створено. Ми скоро зв'яжемося з вами.</t>
+  </si>
+  <si>
+    <t>Заявка создана. Мы скоро свяжемся с вами.</t>
+  </si>
+  <si>
+    <t>Request created. We will contact you soon.</t>
+  </si>
+  <si>
+    <t>NEW_REQUEST_OWNER_TITLE</t>
+  </si>
+  <si>
+    <t>Нова заявка</t>
+  </si>
+  <si>
+    <t>Новая заявка</t>
+  </si>
+  <si>
+    <t>New request</t>
+  </si>
+  <si>
+    <t>OWNER_REQUEST_ID</t>
+  </si>
+  <si>
+    <t>ID заявки</t>
+  </si>
+  <si>
+    <t>Request ID</t>
+  </si>
+  <si>
+    <t>OWNER_CUSTOMER</t>
+  </si>
+  <si>
+    <t>Клієнт</t>
+  </si>
+  <si>
+    <t>Клиент</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>OWNER_PHONE</t>
+  </si>
+  <si>
+    <t>Телефон</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>OWNER_LOCATION</t>
+  </si>
+  <si>
+    <t>Філія</t>
+  </si>
+  <si>
+    <t>Филиал</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>OWNER_SERVICE</t>
+  </si>
+  <si>
+    <t>Послуга</t>
+  </si>
+  <si>
+    <t>Услуга</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>OWNER_PROVIDER</t>
+  </si>
+  <si>
+    <t>Майстер</t>
+  </si>
+  <si>
+    <t>Мастер</t>
+  </si>
+  <si>
+    <t>Provider</t>
+  </si>
+  <si>
+    <t>OWNER_TIME_OPTIONS</t>
+  </si>
+  <si>
+    <t>Варіанти часу</t>
+  </si>
+  <si>
+    <t>Варианты времени</t>
+  </si>
+  <si>
+    <t>Time options</t>
+  </si>
+  <si>
+    <t>SELECT_TIME</t>
+  </si>
+  <si>
+    <t>Оберіть зручний час</t>
+  </si>
+  <si>
+    <t>Выберите удобное время</t>
+  </si>
+  <si>
+    <t>Select preferred time</t>
+  </si>
+  <si>
+    <t>TIME_SELECT_FROM_LIST</t>
+  </si>
+  <si>
+    <t>Будь ласка, оберіть час кнопкою зі списку.</t>
+  </si>
+  <si>
+    <t>Пожалуйста, выберите время кнопкой из списка.</t>
+  </si>
+  <si>
+    <t>Please select a time from the list.</t>
+  </si>
+  <si>
+    <t>REQUEST_APPROVED_OWNER</t>
+  </si>
+  <si>
+    <t>Заявку підтверджено</t>
+  </si>
+  <si>
+    <t>Заявка подтверждена</t>
+  </si>
+  <si>
+    <t>Request approved</t>
+  </si>
+  <si>
+    <t>REQUEST_REJECTED_OWNER</t>
+  </si>
+  <si>
+    <t>Заявку відхилено</t>
+  </si>
+  <si>
+    <t>Заявка отклонена</t>
+  </si>
+  <si>
+    <t>Request rejected</t>
+  </si>
+  <si>
+    <t>REQUEST_APPROVED_CLIENT</t>
+  </si>
+  <si>
+    <t>Ваш запис підтверджено</t>
+  </si>
+  <si>
+    <t>Ваша запись подтверждена</t>
+  </si>
+  <si>
+    <t>Your appointment is confirmed</t>
+  </si>
+  <si>
+    <t>REQUEST_REJECTED_CLIENT</t>
+  </si>
+  <si>
+    <t>На жаль, заявку відхилено</t>
+  </si>
+  <si>
+    <t>К сожалению, заявка отклонена</t>
+  </si>
+  <si>
+    <t>Unfortunately, your request was rejected</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>Центр</t>
+  </si>
+  <si>
+    <t>Center</t>
+  </si>
+  <si>
+    <t>Днепр</t>
+  </si>
+  <si>
+    <t>Лівий берег</t>
+  </si>
+  <si>
+    <t>Левый берег</t>
+  </si>
+  <si>
+    <t>Left Bank</t>
+  </si>
+  <si>
     <t>name</t>
   </si>
   <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">telegram_id </t>
-  </si>
-  <si>
-    <t>Анна</t>
-  </si>
-  <si>
-    <t>Ольга</t>
-  </si>
-  <si>
-    <t>loc_002</t>
-  </si>
-  <si>
-    <t>prov_003</t>
-  </si>
-  <si>
-    <t>Марина</t>
-  </si>
-  <si>
-    <t>exception_id</t>
-  </si>
-  <si>
-    <t>date_from</t>
-  </si>
-  <si>
-    <t>date_to</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>exc_001</t>
-  </si>
-  <si>
-    <t>vacation</t>
-  </si>
-  <si>
-    <t>Отпуск</t>
-  </si>
-  <si>
-    <t>exc_002</t>
-  </si>
-  <si>
-    <t>sick_leave</t>
-  </si>
-  <si>
-    <t>Больничный</t>
-  </si>
-  <si>
-    <t>notification_id</t>
-  </si>
-  <si>
-    <t>appointment_id</t>
-  </si>
-  <si>
-    <t>send_at</t>
-  </si>
-  <si>
-    <t>sent_at</t>
-  </si>
-  <si>
-    <t>notif_001</t>
-  </si>
-  <si>
-    <t>app_001</t>
-  </si>
-  <si>
-    <t>day_before</t>
-  </si>
-  <si>
-    <t>notif_002</t>
-  </si>
-  <si>
-    <t>two_hours</t>
-  </si>
-  <si>
-    <t>uk</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>START</t>
-  </si>
-  <si>
-    <t>Вітаємо!</t>
-  </si>
-  <si>
-    <t>Добро пожаловать!</t>
-  </si>
-  <si>
-    <t>Welcome!</t>
-  </si>
-  <si>
-    <t>BOOK</t>
-  </si>
-  <si>
-    <t>Записатися</t>
-  </si>
-  <si>
-    <t>Записаться</t>
-  </si>
-  <si>
-    <t>Book</t>
-  </si>
-  <si>
-    <t>SERVICES</t>
-  </si>
-  <si>
-    <t>Послуги</t>
-  </si>
-  <si>
-    <t>Услуги</t>
-  </si>
-  <si>
-    <t>Services</t>
-  </si>
-  <si>
-    <t>PRICES</t>
-  </si>
-  <si>
-    <t>Ціни</t>
-  </si>
-  <si>
-    <t>Цены</t>
-  </si>
-  <si>
-    <t>Prices</t>
-  </si>
-  <si>
-    <t>CONTACTS</t>
-  </si>
-  <si>
-    <t>Контакти</t>
-  </si>
-  <si>
-    <t>Контакты</t>
-  </si>
-  <si>
-    <t>Contacts</t>
-  </si>
-  <si>
-    <t>SELECT_LOCATION</t>
-  </si>
-  <si>
-    <t>Оберіть філію</t>
-  </si>
-  <si>
-    <t>Выберите филиал</t>
-  </si>
-  <si>
-    <t>Select location</t>
-  </si>
-  <si>
-    <t>SELECT_SERVICE</t>
-  </si>
-  <si>
-    <t>Оберіть послугу</t>
-  </si>
-  <si>
-    <t>Выберите услугу</t>
-  </si>
-  <si>
-    <t>Select service</t>
-  </si>
-  <si>
-    <t>SELECT_PROVIDER</t>
-  </si>
-  <si>
-    <t>Оберіть майстра</t>
-  </si>
-  <si>
-    <t>Выберите мастера</t>
-  </si>
-  <si>
-    <t>Select provider</t>
-  </si>
-  <si>
-    <t>SELECT_DATE</t>
-  </si>
-  <si>
-    <t>Оберіть перший зручний день</t>
-  </si>
-  <si>
-    <t>Выберите первый удобный день</t>
-  </si>
-  <si>
-    <t>Select first preferred day</t>
-  </si>
-  <si>
-    <t>LOCATION_SELECT_FROM_LIST</t>
-  </si>
-  <si>
-    <t>Будь ласка, оберіть філію кнопкою зі списку.</t>
-  </si>
-  <si>
-    <t>Пожалуйста, выберите филиал кнопкой из списка.</t>
-  </si>
-  <si>
-    <t>Please select a location from the list.</t>
-  </si>
-  <si>
-    <t>SERVICE_SELECT_FROM_LIST</t>
-  </si>
-  <si>
-    <t>Будь ласка, оберіть послугу кнопкою зі списку.</t>
-  </si>
-  <si>
-    <t>Пожалуйста, выберите услугу кнопкой из списка.</t>
-  </si>
-  <si>
-    <t>Please select a service from the list.</t>
-  </si>
-  <si>
-    <t>PROVIDER_SELECT_FROM_LIST</t>
-  </si>
-  <si>
-    <t>Будь ласка, оберіть майстра кнопкою зі списку.</t>
-  </si>
-  <si>
-    <t>Пожалуйста, выберите мастера кнопкой из списка.</t>
-  </si>
-  <si>
-    <t>Please select a provider from the list.</t>
-  </si>
-  <si>
-    <t>UNKNOWN_COMMAND</t>
-  </si>
-  <si>
-    <t>Поки я розумію тільки команду /start</t>
-  </si>
-  <si>
-    <t>Пока я понимаю только команду /start</t>
-  </si>
-  <si>
-    <t>Currently I only understand the /start command.</t>
-  </si>
-  <si>
-    <t>ANY_PROVIDER</t>
-  </si>
-  <si>
-    <t>Будь-який майстер</t>
-  </si>
-  <si>
-    <t>Любой мастер</t>
-  </si>
-  <si>
-    <t>Any provider</t>
-  </si>
-  <si>
-    <t>TODAY</t>
-  </si>
-  <si>
-    <t>Сьогодні</t>
-  </si>
-  <si>
-    <t>Сегодня</t>
-  </si>
-  <si>
-    <t>Today</t>
-  </si>
-  <si>
-    <t>TOMORROW</t>
-  </si>
-  <si>
-    <t>Завтра</t>
-  </si>
-  <si>
-    <t>Tomorrow</t>
-  </si>
-  <si>
-    <t>DAY_AFTER_TOMORROW</t>
-  </si>
-  <si>
-    <t>Післязавтра</t>
-  </si>
-  <si>
-    <t>Послезавтра</t>
-  </si>
-  <si>
-    <t>Day after tomorrow</t>
-  </si>
-  <si>
-    <t>OTHER_DATE</t>
-  </si>
-  <si>
-    <t>Інша дата</t>
-  </si>
-  <si>
-    <t>Другая дата</t>
-  </si>
-  <si>
-    <t>Other date</t>
-  </si>
-  <si>
-    <t>SESSION_LOCATION_NOT_FOUND</t>
-  </si>
-  <si>
-    <t>Не вдалося знайти вибрану філію. Почніть заново: /start</t>
-  </si>
-  <si>
-    <t>Не найден выбранный филиал. Начните заново: /start</t>
-  </si>
-  <si>
-    <t>Selected location not found. Please start again: /start</t>
-  </si>
-  <si>
-    <t>address</t>
-  </si>
-  <si>
-    <t>Центр</t>
-  </si>
-  <si>
-    <t>Днепр</t>
-  </si>
-  <si>
-    <t>Левый берег</t>
-  </si>
-  <si>
     <t>language</t>
   </si>
   <si>
@@ -673,6 +1129,24 @@
     <t>notes</t>
   </si>
   <si>
+    <t>cust_1781289974856</t>
+  </si>
+  <si>
+    <t>Аня</t>
+  </si>
+  <si>
+    <t>cust_1781290148629</t>
+  </si>
+  <si>
+    <t>Вика</t>
+  </si>
+  <si>
+    <t>lead</t>
+  </si>
+  <si>
+    <t>Света</t>
+  </si>
+  <si>
     <t>start_at</t>
   </si>
   <si>
@@ -682,10 +1156,7 @@
     <t>calendar_event_id</t>
   </si>
   <si>
-    <t>confirmed</t>
-  </si>
-  <si>
-    <t>...</t>
+    <t>appt_1781293819707</t>
   </si>
 </sst>
 </file>
@@ -693,9 +1164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -743,7 +1214,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -759,13 +1230,20 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="14" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -780,8 +1258,8 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="19" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -792,10 +1270,18 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1159,7 +1645,7 @@
         <v>20</v>
       </c>
       <c r="B8" s="2">
-        <v>7.75285374E9</v>
+        <v>7.26107007E8</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>21</v>
@@ -1230,76 +1716,100 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="8" t="s">
+      <c r="A1" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" s="10">
+      <c r="C2" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" s="13">
         <f>+380111111111</f>
         <v>380111111111</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F2" s="11" t="b">
+      <c r="H2" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C3" s="10">
+      <c r="A3" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F3" s="13">
         <f>+380111111112</f>
         <v>380111111112</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F3" s="11" t="b">
+      <c r="H3" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="10">
+      <c r="A4" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" s="13">
         <f>+380111111113</f>
         <v>380111111113</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="F4" s="11" t="b">
+      <c r="H4" s="14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1316,63 +1826,63 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="A1" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="A2" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="19">
         <v>46204.0</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="19">
         <v>46210.0</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>115</v>
+      <c r="E2" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="12">
+      <c r="A3" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="19">
         <v>46188.0</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="19">
         <v>46188.0</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>118</v>
+      <c r="E3" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -1388,59 +1898,59 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>78</v>
+      <c r="A1" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D2" s="16">
+      <c r="A2" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D2" s="20">
         <v>46187.583333333336</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9" t="s">
-        <v>84</v>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="16">
+      <c r="A3" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D3" s="20">
         <v>46188.5</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9" t="s">
-        <v>84</v>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1466,279 +1976,657 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>171</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>129</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>133</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>137</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>145</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>147</v>
+        <v>190</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>149</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>153</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>155</v>
+        <v>198</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>156</v>
+        <v>199</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>161</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>163</v>
+        <v>206</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>166</v>
+        <v>209</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>167</v>
+        <v>210</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>168</v>
+        <v>211</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>169</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>171</v>
+        <v>214</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>176</v>
+        <v>219</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>178</v>
+        <v>221</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>180</v>
+        <v>223</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>181</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>183</v>
+        <v>226</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>184</v>
+        <v>227</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>186</v>
+        <v>229</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>187</v>
+        <v>230</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>188</v>
+        <v>231</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>189</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>190</v>
+        <v>233</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>192</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>194</v>
+        <v>237</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>195</v>
+        <v>238</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>196</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>197</v>
+        <v>240</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>198</v>
+        <v>241</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>201</v>
+        <v>244</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>203</v>
+        <v>246</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>204</v>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -1752,57 +2640,78 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="6" max="6" width="12.13"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>67</v>
+      <c r="A1" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>206</v>
+        <v>354</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D2" s="17">
+        <v>354</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F2" s="7">
         <f>+380000000001</f>
         <v>380000000001</v>
       </c>
-      <c r="E2" s="2" t="b">
+      <c r="G2" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>208</v>
+        <v>357</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D3" s="17">
+        <v>358</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F3" s="7">
         <f>+380000000002</f>
         <v>380000000002</v>
       </c>
-      <c r="E3" s="2" t="b">
+      <c r="G3" s="2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1817,54 +2726,205 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="18.13"/>
+    <col customWidth="1" min="4" max="4" width="13.38"/>
+    <col customWidth="1" min="6" max="6" width="16.38"/>
+    <col customWidth="1" min="7" max="7" width="19.25"/>
+    <col customWidth="1" min="8" max="8" width="13.38"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="8" t="s">
+      <c r="A1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>211</v>
+      <c r="C1" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="10">
-        <v>123456.0</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="A2" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B2" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D2" s="7">
+        <v>3804562658652</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46185.90711637732</v>
+      </c>
+      <c r="G2" s="6">
+        <v>46185.90711637732</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B3" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D3" s="7">
+        <v>38052425635966</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46185.90912765046</v>
+      </c>
+      <c r="G3" s="6">
+        <v>46185.90912765046</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" s="7">
+        <v>3804452125648</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46185.93864143519</v>
+      </c>
+      <c r="G4" s="6">
+        <v>46185.93864143519</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D5" s="7">
+        <v>38045245268</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46185.943211805556</v>
+      </c>
+      <c r="G5" s="6">
+        <v>46185.943211805556</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="7">
+        <v>3502452635165</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46185.947925671295</v>
+      </c>
+      <c r="G6" s="6">
+        <v>46185.947925671295</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="10">
-        <v>3.801111111E9</v>
-      </c>
-      <c r="E2" s="9" t="s">
+      <c r="B7" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="7">
+        <v>38055245256685</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="12">
-        <v>46183.0</v>
-      </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
+      <c r="F7" s="6">
+        <v>46185.95117884259</v>
+      </c>
+      <c r="G7" s="6">
+        <v>46185.95117884259</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -1877,69 +2937,81 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="7" max="7" width="14.0"/>
+    <col customWidth="1" min="10" max="10" width="16.25"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>214</v>
+      <c r="A1" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="G2" s="16">
-        <v>46188.583333333336</v>
-      </c>
-      <c r="H2" s="16">
-        <v>46188.75</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>216</v>
+      <c r="A2" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="22">
+        <v>46186.395833333336</v>
+      </c>
+      <c r="H2" s="20"/>
+      <c r="I2" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="J2" s="12"/>
+      <c r="K2" s="6">
+        <v>46185.95161697917</v>
+      </c>
+      <c r="L2" s="6">
+        <v>46185.95161697917</v>
       </c>
     </row>
   </sheetData>
@@ -1970,26 +3042,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
-        <v>123456.0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="5">
-        <v>46184.020833333336</v>
+      <c r="A2" s="5">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="6">
+        <v>46185.951275659725</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6">
-        <v>7.75285374E9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="7">
-        <v>46184.93502211805</v>
-      </c>
+      <c r="C3" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -2005,721 +3067,842 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="6">
+        <v>46184.062834641205</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="7">
-        <v>46184.062834641205</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="3">
+      <c r="A3" s="6">
+        <v>46184.062838032405</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7">
-        <v>46184.062838032405</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="4">
+      <c r="A4" s="6">
+        <v>46184.062845821754</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="7">
-        <v>46184.062845821754</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="5">
+      <c r="A5" s="6">
+        <v>46184.06284782407</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7">
-        <v>46184.06284782407</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="C5" s="2">
         <v>7.75285374E9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>46184.062851689814</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6">
+        <v>46184.06285528935</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6">
+        <v>46184.0628725</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6">
+        <v>46184.06287454861</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7">
-        <v>46184.06285528935</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7">
-        <v>46184.0628725</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7">
-        <v>46184.06287454861</v>
-      </c>
-      <c r="B9" s="2" t="s">
+    <row r="10">
+      <c r="A10" s="6">
+        <v>46184.06287892361</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7">
-        <v>46184.06287892361</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6">
+        <v>46184.06288090278</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7">
-        <v>46184.06288090278</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="C11" s="2">
         <v>7.75285374E9</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7">
+      <c r="A12" s="6">
         <v>46184.06288592593</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7">
+      <c r="A13" s="6">
         <v>46184.06289001157</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6">
+        <v>46184.06300329861</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6">
+        <v>46184.063011087965</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7">
-        <v>46184.06300329861</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7">
-        <v>46184.063011087965</v>
-      </c>
-      <c r="B15" s="2" t="s">
+    <row r="16">
+      <c r="A16" s="6">
+        <v>46184.063023599534</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7">
-        <v>46184.063023599534</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6">
+        <v>46184.063026689815</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7">
-        <v>46184.063026689815</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="C17" s="2">
         <v>7.75285374E9</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7">
+      <c r="A18" s="6">
         <v>46184.06303276621</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7">
+      <c r="A19" s="6">
         <v>46184.063038935186</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7">
+      <c r="A20" s="6">
         <v>46184.063061493056</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6">
+        <v>46184.06306418982</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7">
-        <v>46184.06306418982</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6">
+        <v>46184.06306945602</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7">
-        <v>46184.06306945602</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6">
+        <v>46184.063072523146</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7">
-        <v>46184.063072523146</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="C23" s="2">
         <v>7.75285374E9</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7">
+      <c r="A24" s="6">
         <v>46184.06307773148</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7">
+      <c r="A25" s="6">
         <v>46184.063082569446</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7">
+      <c r="A26" s="6">
         <v>46184.06309688657</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6">
+        <v>46184.06309922454</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7">
-        <v>46184.06309922454</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6">
+        <v>46184.063104050925</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7">
-        <v>46184.063104050925</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="C28" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6">
+        <v>46184.063106828704</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7">
-        <v>46184.063106828704</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="C29" s="2">
         <v>7.75285374E9</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7">
+      <c r="A30" s="6">
         <v>46184.063111678246</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7">
+      <c r="A31" s="6">
         <v>46184.06311567129</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7">
+      <c r="A32" s="6">
         <v>46184.06313052084</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6">
+        <v>46184.06313314815</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7">
-        <v>46184.06313314815</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6">
+        <v>46184.06313862269</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7">
-        <v>46184.06313862269</v>
-      </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6">
+        <v>46184.06314118055</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7">
-        <v>46184.06314118055</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="C35" s="2">
         <v>7.75285374E9</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7">
+      <c r="A36" s="6">
         <v>46184.06314576389</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7">
+      <c r="A37" s="6">
         <v>46184.06315028935</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7">
+      <c r="A38" s="6">
         <v>46184.06316583333</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6">
+        <v>46184.06316777778</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7">
-        <v>46184.06316777778</v>
-      </c>
-      <c r="B39" s="2" t="s">
+      <c r="C39" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6">
+        <v>46184.06317201389</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7">
-        <v>46184.06317201389</v>
-      </c>
-      <c r="B40" s="2" t="s">
+      <c r="C40" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6">
+        <v>46184.06317864583</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7">
-        <v>46184.06317864583</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="C41" s="2">
         <v>7.75285374E9</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7">
+      <c r="A42" s="6">
         <v>46184.06318341436</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7">
+      <c r="A43" s="6">
         <v>46184.063187395834</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7">
+      <c r="A44" s="6">
         <v>46184.06321230324</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6">
+        <v>46184.0632146412</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7">
-        <v>46184.0632146412</v>
-      </c>
-      <c r="B45" s="2" t="s">
+      <c r="C45" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6">
+        <v>46184.0632199074</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7">
-        <v>46184.0632199074</v>
-      </c>
-      <c r="B46" s="2" t="s">
+      <c r="C46" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6">
+        <v>46184.06322258102</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7">
-        <v>46184.06322258102</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="C47" s="2">
         <v>7.75285374E9</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7">
+      <c r="A48" s="6">
         <v>46184.063226886574</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7">
+      <c r="A49" s="6">
         <v>46184.0632308912</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7">
+      <c r="A50" s="6">
         <v>46184.063420729166</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6">
+        <v>46184.063431435185</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7">
-        <v>46184.063431435185</v>
-      </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6">
+        <v>46184.06344136574</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7">
-        <v>46184.06344136574</v>
-      </c>
-      <c r="B52" s="2" t="s">
+      <c r="C52" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6">
+        <v>46184.063448553236</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7">
-        <v>46184.063448553236</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="C53" s="2">
         <v>7.75285374E9</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7">
+      <c r="A54" s="6">
         <v>46184.06345524306</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7">
+      <c r="A55" s="6">
         <v>46184.06346207176</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7">
+      <c r="A56" s="6">
         <v>46184.06521584491</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7">
+      <c r="A57" s="6">
         <v>46184.06534123843</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7">
+      <c r="A58" s="6">
         <v>46184.40455040509</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7">
+      <c r="A59" s="6">
         <v>46184.40464099537</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7">
+      <c r="A60" s="6">
         <v>46184.40471289352</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7">
+      <c r="A61" s="6">
         <v>46184.40481731482</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7">
+      <c r="A62" s="6">
         <v>46184.414640532406</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7">
+      <c r="A63" s="6">
         <v>46184.414743483794</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7">
+      <c r="A64" s="6">
         <v>46184.414803113425</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7">
+      <c r="A65" s="6">
         <v>46184.41697719907</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7">
+      <c r="A66" s="6">
         <v>46184.41712943287</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="7">
+      <c r="A67" s="6">
         <v>46184.417209189814</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="7">
+      <c r="A68" s="6">
         <v>46184.42106340278</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="7">
+      <c r="A69" s="6">
         <v>46184.42115165509</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7">
+      <c r="A70" s="6">
         <v>46184.42121688658</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6">
+        <v>46185.938648738425</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6">
+        <v>46185.943222789356</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6">
+        <v>46185.947906875</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6">
+        <v>46185.94791225695</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C74" s="7">
+        <v>3502452635165</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6">
+        <v>46185.94791965278</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6">
+        <v>46185.94793200232</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6">
+        <v>46185.951158888885</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6">
+        <v>46185.95116344908</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C78" s="7">
+        <v>38055245256685</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6">
+        <v>46185.951173043984</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6">
+        <v>46185.95120231481</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6">
+        <v>46185.95125975694</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2736,36 +3919,78 @@
   <cols>
     <col customWidth="1" min="6" max="6" width="20.38"/>
     <col customWidth="1" min="7" max="7" width="21.63"/>
+    <col customWidth="1" min="15" max="16" width="16.0"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2">
-      <c r="F2" s="7"/>
+      <c r="A2" s="5">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -2780,89 +4005,89 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>67</v>
+      <c r="B1" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="A2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="13">
         <v>60.0</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="13">
         <v>90.0</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="13">
         <v>500.0</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="13">
         <v>700.0</v>
       </c>
-      <c r="I2" s="11" t="b">
+      <c r="I2" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="10">
+      <c r="A3" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="13">
         <v>180.0</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="13">
         <v>300.0</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="13">
         <v>1500.0</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="13">
         <v>3000.0</v>
       </c>
-      <c r="I3" s="11" t="b">
+      <c r="I3" s="14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2877,51 +4102,125 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="20.38"/>
+    <col customWidth="1" min="2" max="2" width="19.0"/>
+    <col customWidth="1" min="7" max="7" width="16.13"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>79</v>
+      <c r="A1" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="G2" s="12">
-        <v>46183.0</v>
+      <c r="A2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" s="6">
+        <v>46185.93864650463</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" s="6">
+        <v>46185.94321923611</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="6">
+        <v>46185.947929629634</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="6">
+        <v>46185.95118355324</v>
       </c>
     </row>
   </sheetData>
@@ -2935,85 +4234,354 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="16.25"/>
+    <col customWidth="1" min="4" max="4" width="20.63"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>78</v>
+      <c r="A1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="12">
-        <v>46188.0</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="A2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.3527314814818965</v>
+      </c>
+      <c r="E2" s="5">
         <v>1.0</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>84</v>
+      <c r="F2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" s="6">
+        <v>46185.85522081019</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="12">
-        <v>46189.0</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="10">
+      <c r="A3" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="10">
+        <v>46185.0</v>
+      </c>
+      <c r="D3" s="15">
+        <v>0.7693981481497758</v>
+      </c>
+      <c r="E3" s="5">
         <v>2.0</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>84</v>
+      <c r="F3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" s="6">
+        <v>46185.85522081019</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="12">
-        <v>46190.0</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" s="10">
+      <c r="A4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D4" s="15">
+        <v>0.3527314814818965</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="6">
+        <v>46185.86117096065</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="10">
+        <v>46187.0</v>
+      </c>
+      <c r="D5" s="15">
+        <v>0.5193981481497758</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" s="6">
+        <v>46185.86117096065</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="10">
+        <v>46185.0</v>
+      </c>
+      <c r="D6" s="15">
+        <v>0.7693981481497758</v>
+      </c>
+      <c r="E6" s="5">
         <v>3.0</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>84</v>
+      <c r="F6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="6">
+        <v>46185.86117096065</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D7" s="15">
+        <v>0.3527314814818965</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="6">
+        <v>46185.86662434028</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="10">
+        <v>46187.0</v>
+      </c>
+      <c r="D8" s="15">
+        <v>0.43606481481401715</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="6">
+        <v>46185.86662434028</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" s="10">
+        <v>46185.0</v>
+      </c>
+      <c r="D9" s="15">
+        <v>0.7693981481497758</v>
+      </c>
+      <c r="E9" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G9" s="6">
+        <v>46185.86662434028</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D10" s="15">
+        <v>0.3527314814818965</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="6">
+        <v>46185.87604545139</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0.3943981481497758</v>
+      </c>
+      <c r="E11" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="6">
+        <v>46185.87604545139</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D12" s="15">
+        <v>0.3527314814818965</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G12" s="6">
+        <v>46185.880830740745</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D13" s="15">
+        <v>0.3958333333321207</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G13" s="6">
+        <v>46185.90712123843</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="10">
+        <v>46185.0</v>
+      </c>
+      <c r="D14" s="15">
+        <v>0.3333333333321207</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G14" s="6">
+        <v>46185.909134305555</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D15" s="15">
+        <v>0.3958333333321207</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G15" s="6">
+        <v>46185.95119975695</v>
       </c>
     </row>
   </sheetData>
@@ -3029,46 +4597,46 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>67</v>
+      <c r="A1" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="11" t="b">
+      <c r="A2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="11" t="b">
+      <c r="A3" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="11" t="b">
+      <c r="A4" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3085,53 +4653,53 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>67</v>
+      <c r="A1" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="A2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" s="16">
         <v>0.375</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="16">
         <v>0.75</v>
       </c>
-      <c r="E2" s="11" t="b">
+      <c r="E2" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" s="9" t="s">
+      <c r="A3" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="13">
+      <c r="B3" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="16">
         <v>0.4166666666666667</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="16">
         <v>0.8333333333333334</v>
       </c>
-      <c r="E3" s="11" t="b">
+      <c r="E3" s="14" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Docs/SmartFlow Beauty Demo.xlsx
+++ b/Docs/SmartFlow Beauty Demo.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="391">
   <si>
     <t>key</t>
   </si>
@@ -367,6 +367,12 @@
     <t>confirmed</t>
   </si>
   <si>
+    <t>req_1781322885424</t>
+  </si>
+  <si>
+    <t>cust_1781322885063</t>
+  </si>
+  <si>
     <t>option_id</t>
   </si>
   <si>
@@ -448,6 +454,9 @@
     <t>opt_1781293783659</t>
   </si>
   <si>
+    <t>opt_1781322885791</t>
+  </si>
+  <si>
     <t>prov_002</t>
   </si>
   <si>
@@ -1087,13 +1096,49 @@
     <t>REQUEST_REJECTED_CLIENT</t>
   </si>
   <si>
-    <t>На жаль, заявку відхилено</t>
-  </si>
-  <si>
-    <t>К сожалению, заявка отклонена</t>
-  </si>
-  <si>
-    <t>Unfortunately, your request was rejected</t>
+    <t>На жаль, заявку відхилено. Ми вам передзвонимо</t>
+  </si>
+  <si>
+    <t>К сожалению, заявка отклонена. Мы Вам перезвоним.</t>
+  </si>
+  <si>
+    <t>Unfortunately, your request was rejected. We will call you back</t>
+  </si>
+  <si>
+    <t>REQUEST_ALREADY_PROCESSED</t>
+  </si>
+  <si>
+    <t>Заявку вже оброблено</t>
+  </si>
+  <si>
+    <t>Заявка уже обработана</t>
+  </si>
+  <si>
+    <t>Request already processed</t>
+  </si>
+  <si>
+    <t>OWNER_REQUEST_CONFIRMED_STATUS</t>
+  </si>
+  <si>
+    <t>✅ Підтверджено</t>
+  </si>
+  <si>
+    <t>✅ Подтверждено</t>
+  </si>
+  <si>
+    <t>✅ Confirmed</t>
+  </si>
+  <si>
+    <t>OWNER_REQUEST_REJECTED_STATUS</t>
+  </si>
+  <si>
+    <t>❌ Відхилено</t>
+  </si>
+  <si>
+    <t>❌ Отклонено</t>
+  </si>
+  <si>
+    <t>❌ Rejected</t>
   </si>
   <si>
     <t>address</t>
@@ -1147,6 +1192,9 @@
     <t>Света</t>
   </si>
   <si>
+    <t>Оля</t>
+  </si>
+  <si>
     <t>start_at</t>
   </si>
   <si>
@@ -1157,6 +1205,9 @@
   </si>
   <si>
     <t>appt_1781293819707</t>
+  </si>
+  <si>
+    <t>appt_1781322908547</t>
   </si>
 </sst>
 </file>
@@ -1214,7 +1265,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1281,6 +1332,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1732,7 +1786,7 @@
         <v>80</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G1" s="17" t="s">
         <v>28</v>
@@ -1749,13 +1803,13 @@
         <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F2" s="13">
         <f>+380111111111</f>
@@ -1767,19 +1821,19 @@
     </row>
     <row r="3">
       <c r="A3" s="12" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F3" s="13">
         <f>+380111111112</f>
@@ -1797,13 +1851,13 @@
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F4" s="13">
         <f>+380111111113</f>
@@ -1827,19 +1881,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>2</v>
@@ -1847,7 +1901,7 @@
     </row>
     <row r="2">
       <c r="A2" s="12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>100</v>
@@ -1859,18 +1913,18 @@
         <v>46210.0</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C3" s="19">
         <v>46188.0</v>
@@ -1879,10 +1933,10 @@
         <v>46188.0</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -1899,19 +1953,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>96</v>
@@ -1919,13 +1973,13 @@
     </row>
     <row r="2">
       <c r="A2" s="12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D2" s="20">
         <v>46187.583333333336</v>
@@ -1937,13 +1991,13 @@
     </row>
     <row r="3">
       <c r="A3" s="12" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D3" s="20">
         <v>46188.5</v>
@@ -1966,9 +2020,9 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="45.13"/>
-    <col customWidth="1" min="2" max="2" width="38.25"/>
+    <col customWidth="1" min="2" max="2" width="40.13"/>
     <col customWidth="1" min="3" max="3" width="49.25"/>
-    <col customWidth="1" min="4" max="4" width="37.13"/>
+    <col customWidth="1" min="4" max="4" width="48.13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1976,657 +2030,699 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -2658,10 +2754,10 @@
         <v>80</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G1" s="17" t="s">
         <v>85</v>
@@ -2672,16 +2768,16 @@
         <v>101</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="F2" s="7">
         <f>+380000000001</f>
@@ -2693,19 +2789,19 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="F3" s="7">
         <f>+380000000002</f>
@@ -2742,13 +2838,13 @@
         <v>28</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>97</v>
@@ -2757,10 +2853,10 @@
         <v>30</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>96</v>
@@ -2768,13 +2864,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="B2" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="D2" s="7">
         <v>3804562658652</v>
@@ -2794,13 +2890,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="B3" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="D3" s="7">
         <v>38052425635966</v>
@@ -2815,7 +2911,7 @@
         <v>46185.90912765046</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4">
@@ -2826,7 +2922,7 @@
         <v>7.75285374E9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D4" s="7">
         <v>3804452125648</v>
@@ -2841,7 +2937,7 @@
         <v>46185.93864143519</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5">
@@ -2852,7 +2948,7 @@
         <v>7.75285374E9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="D5" s="7">
         <v>38045245268</v>
@@ -2867,7 +2963,7 @@
         <v>46185.943211805556</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6">
@@ -2878,7 +2974,7 @@
         <v>7.75285374E9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D6" s="7">
         <v>3502452635165</v>
@@ -2893,7 +2989,7 @@
         <v>46185.947925671295</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7">
@@ -2904,7 +3000,7 @@
         <v>7.75285374E9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D7" s="7">
         <v>38055245256685</v>
@@ -2923,8 +3019,30 @@
       </c>
     </row>
     <row r="8">
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
+      <c r="A8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D8" s="7">
+        <v>3805542545878</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46186.288021562505</v>
+      </c>
+      <c r="G8" s="6">
+        <v>46186.288021562505</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>109</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -2944,7 +3062,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B1" s="21" t="s">
         <v>94</v>
@@ -2962,16 +3080,16 @@
         <v>64</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="H1" s="21" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="I1" s="21" t="s">
         <v>96</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="K1" s="17" t="s">
         <v>97</v>
@@ -2982,7 +3100,7 @@
     </row>
     <row r="2">
       <c r="A2" s="18" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>62</v>
@@ -3012,6 +3130,38 @@
       </c>
       <c r="L2" s="6">
         <v>46185.95161697917</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="23">
+        <v>46187.395833333336</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K3" s="6">
+        <v>46186.28829336805</v>
+      </c>
+      <c r="L3" s="6">
+        <v>46186.28829336805</v>
       </c>
     </row>
   </sheetData>
@@ -3047,7 +3197,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="6">
-        <v>46185.951275659725</v>
+        <v>46186.28811368055</v>
       </c>
     </row>
     <row r="3">
@@ -4223,6 +4373,29 @@
         <v>46185.95118355324</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G6" s="6">
+        <v>46186.28802574074</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -4241,19 +4414,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>96</v>
@@ -4264,10 +4437,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C2" s="10">
         <v>46186.0</v>
@@ -4287,10 +4460,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C3" s="10">
         <v>46185.0</v>
@@ -4310,10 +4483,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C4" s="10">
         <v>46186.0</v>
@@ -4333,10 +4506,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C5" s="10">
         <v>46187.0</v>
@@ -4356,10 +4529,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="C6" s="10">
         <v>46185.0</v>
@@ -4379,10 +4552,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C7" s="10">
         <v>46186.0</v>
@@ -4402,10 +4575,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="10">
         <v>46187.0</v>
@@ -4425,10 +4598,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="C9" s="10">
         <v>46185.0</v>
@@ -4448,10 +4621,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C10" s="10">
         <v>46186.0</v>
@@ -4471,10 +4644,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C11" s="10">
         <v>46186.0</v>
@@ -4494,10 +4667,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C12" s="10">
         <v>46186.0</v>
@@ -4517,10 +4690,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C13" s="10">
         <v>46186.0</v>
@@ -4532,7 +4705,7 @@
         <v>1.0</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G13" s="6">
         <v>46185.90712123843</v>
@@ -4540,10 +4713,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C14" s="10">
         <v>46185.0</v>
@@ -4555,7 +4728,7 @@
         <v>1.0</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G14" s="6">
         <v>46185.909134305555</v>
@@ -4563,7 +4736,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -4578,10 +4751,33 @@
         <v>1.0</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G15" s="6">
         <v>46185.95119975695</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="10">
+        <v>46187.0</v>
+      </c>
+      <c r="D16" s="15">
+        <v>0.3958333333321207</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G16" s="6">
+        <v>46186.28802998843</v>
       </c>
     </row>
   </sheetData>
@@ -4631,7 +4827,7 @@
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>86</v>
@@ -4657,13 +4853,13 @@
         <v>66</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E1" s="11" t="s">
         <v>85</v>
@@ -4674,7 +4870,7 @@
         <v>100</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C2" s="16">
         <v>0.375</v>
@@ -4691,7 +4887,7 @@
         <v>100</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C3" s="16">
         <v>0.4166666666666667</v>

--- a/Docs/SmartFlow Beauty Demo.xlsx
+++ b/Docs/SmartFlow Beauty Demo.xlsx
@@ -8,17 +8,20 @@
     <sheet state="visible" name="AuditLog" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="UserSessions" sheetId="4" r:id="rId8"/>
     <sheet state="visible" name="Services" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="Requests" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="RequestOptions" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="ProviderServices" sheetId="8" r:id="rId12"/>
-    <sheet state="visible" name="ProviderSchedule" sheetId="9" r:id="rId13"/>
-    <sheet state="visible" name="Providers" sheetId="10" r:id="rId14"/>
-    <sheet state="visible" name="ProviderExceptions" sheetId="11" r:id="rId15"/>
-    <sheet state="visible" name="Notifications" sheetId="12" r:id="rId16"/>
-    <sheet state="visible" name="Messages" sheetId="13" r:id="rId17"/>
-    <sheet state="visible" name="Locations" sheetId="14" r:id="rId18"/>
-    <sheet state="visible" name="Customers" sheetId="15" r:id="rId19"/>
-    <sheet state="visible" name="Appointments" sheetId="16" r:id="rId20"/>
+    <sheet state="visible" name="CustomerServiceSettings" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="Requests" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="RequestOptions" sheetId="8" r:id="rId12"/>
+    <sheet state="visible" name="ProviderServices" sheetId="9" r:id="rId13"/>
+    <sheet state="visible" name="ProviderSchedule" sheetId="10" r:id="rId14"/>
+    <sheet state="visible" name="ProviderScheduleOverrides" sheetId="11" r:id="rId15"/>
+    <sheet state="visible" name="Instructions" sheetId="12" r:id="rId16"/>
+    <sheet state="visible" name="Providers" sheetId="13" r:id="rId17"/>
+    <sheet state="visible" name="ProviderExceptions" sheetId="14" r:id="rId18"/>
+    <sheet state="visible" name="Notifications" sheetId="15" r:id="rId19"/>
+    <sheet state="visible" name="Messages" sheetId="16" r:id="rId20"/>
+    <sheet state="visible" name="Locations" sheetId="17" r:id="rId21"/>
+    <sheet state="visible" name="Customers" sheetId="18" r:id="rId22"/>
+    <sheet state="visible" name="Appointments" sheetId="19" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="494">
   <si>
     <t>key</t>
   </si>
@@ -109,7 +112,7 @@
     <t>ClientWebAppUrl</t>
   </si>
   <si>
-    <t>https://script.google.com/macros/s/AKfycbxtu0SbRTctUotAo7xz9YDXntkW6bG4CZOoJDj06ruIlZJ02FeqdUl93UNR1_4FwnF6/exec</t>
+    <t>https://script.google.com/macros/s/AKfycbzxWul5heUu_rHzgpP_We__04AV_pDxgYgjNW0DQHltnTEGIwXMSkgqvo2sxSWlVQ42/exec</t>
   </si>
   <si>
     <t>telegram_id</t>
@@ -229,6 +232,78 @@
     <t>OWNER_NOTIFIED</t>
   </si>
   <si>
+    <t>OWNER_CALLBACK</t>
+  </si>
+  <si>
+    <t>{"id":"3118605852587160298","from":{"id":726107007,"is_bot":false,"first_name":"Serhii","username":"Serhii_Tsi","language_code":"en"},"message":{"message_id":1136,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":726107007,"first_name":"Serhii","username":"Serhii_Tsi","type":"private"},"date":1781334087,"text":"Новая заявка\n\n👤 Клиент: Аня\n📞 Телефон: 6545498798798\n\n📍 Филиал: Центр\n💅 Услуга: Окрашивание\n👩‍💼 Мастер: Анна\n\nВарианты времени:\n1) 15.06.2026 10:30","entities":[{"offset":0,"length":12,"type":"bold"},{"offset":116,"length":17,"type":"bold"}],"reply_markup":{"inline_keyboard":[[{"text":"✅ 1","callback_data":"approve_option_1|req_1781334080788"}],[{"text":"❌ Reject","callback_data":"reject_request|req_1781334080788"}]]}},"chat_instance":"-653345212733041723","data":"approve_option_1|req_1781334080788"}</t>
+  </si>
+  <si>
+    <t>ReferenceError: updateRequestStatus is not defined</t>
+  </si>
+  <si>
+    <t>SHOW_TIME_OPTIONS</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","option_count":0,"current_option_date":"2026-06-14T21:00:00.000Z","current_option_time":"","option1_date":"","option1_time":"","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"","customer_phone":"","updated_at":"2026-06-13T07:11:56.948Z"}</t>
+  </si>
+  <si>
+    <t>AVAILABLE_SLOTS</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","option_count":0,"current_option_date":"2026-06-14T21:00:00.000Z","current_option_time":"","option1_date":"","option1_time":"","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"","customer_phone":"","updated_at":"2026-06-13T07:21:38.958Z"}</t>
+  </si>
+  <si>
+    <t>["09:00","09:30","10:00","10:30","11:00","11:30","12:00","12:30","13:00","13:30","14:00","14:30","15:00"]</t>
+  </si>
+  <si>
+    <t>{"id":"3118605851096329130","from":{"id":726107007,"is_bot":false,"first_name":"Serhii","username":"Serhii_Tsi","language_code":"en"},"message":{"message_id":1202,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":726107007,"first_name":"Serhii","username":"Serhii_Tsi","type":"private"},"date":1781335354,"text":"Новая заявка\n\n👤 Клиент: Оля\n📞 Телефон: 25452358485\n\n📍 Филиал: Центр\n💅 Услуга: Окрашивание\n👩‍💼 Мастер: Анна\n\nВарианты времени:\n1) 15.06.2026 10:30","entities":[{"offset":0,"length":12,"type":"bold"},{"offset":114,"length":17,"type":"bold"}],"reply_markup":{"inline_keyboard":[[{"text":"✅ 1","callback_data":"approve_option_1|req_1781335348889"}],[{"text":"❌ Reject","callback_data":"reject_request|req_1781335348889"}]]}},"chat_instance":"-653345212733041723","data":"approve_option_1|req_1781335348889"}</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","option_count":0,"current_option_date":"2026-06-14T21:00:00.000Z","current_option_time":"","option1_date":"","option1_time":"","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"","customer_phone":"","updated_at":"2026-06-13T07:23:38.262Z"}</t>
+  </si>
+  <si>
+    <t>["13:30","14:00","14:30","15:00"]</t>
+  </si>
+  <si>
+    <t>{"id":"3118605848925929003","from":{"id":726107007,"is_bot":false,"first_name":"Serhii","username":"Serhii_Tsi","language_code":"en"},"message":{"message_id":1224,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":726107007,"first_name":"Serhii","username":"Serhii_Tsi","type":"private"},"date":1781335489,"text":"Новая заявка\n\n👤 Клиент: Дана\n📞 Телефон: 52325648458\n\n📍 Филиал: Центр\n💅 Услуга: Окрашивание\n👩‍💼 Мастер: Анна\n\nВарианты времени:\n1) 15.06.2026 14:00","entities":[{"offset":0,"length":12,"type":"bold"},{"offset":115,"length":17,"type":"bold"}],"reply_markup":{"inline_keyboard":[[{"text":"✅ 1","callback_data":"approve_option_1|req_1781335484784"}],[{"text":"❌ Reject","callback_data":"reject_request|req_1781335484784"}]]}},"chat_instance":"-653345212733041723","data":"approve_option_1|req_1781335484784"}</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_003","option_count":0,"current_option_date":"2026-06-12T21:00:00.000Z","current_option_time":"","option1_date":"","option1_time":"","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"","customer_phone":"","updated_at":"2026-06-13T08:09:06.113Z"}</t>
+  </si>
+  <si>
+    <t>["09:00","09:30","10:00","10:30","11:00","11:30","12:00","12:30","13:00","13:30","14:00"]</t>
+  </si>
+  <si>
+    <t>{"id":"3118605849940805194","from":{"id":726107007,"is_bot":false,"first_name":"Serhii","username":"Serhii_Tsi","language_code":"en"},"message":{"message_id":1246,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":726107007,"first_name":"Serhii","username":"Serhii_Tsi","type":"private"},"date":1781338213,"text":"Новая заявка\n\n👤 Клиент: Оля\n📞 Телефон: +3524587568\n\n📍 Филиал: Центр\n💅 Услуга: Окрашивание\n👩‍💼 Мастер: Марина\n\nВарианты времени:\n1) 13.06.2026 14:00","entities":[{"offset":0,"length":12,"type":"bold"},{"offset":116,"length":17,"type":"bold"}],"reply_markup":{"inline_keyboard":[[{"text":"✅ 1","callback_data":"approve_option_1|req_1781338203105"}],[{"text":"❌ Reject","callback_data":"reject_request|req_1781338203105"}]]}},"chat_instance":"-653345212733041723","data":"approve_option_1|req_1781338203105"}</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","option_count":0,"current_option_date":"2026-06-12T21:00:00.000Z","current_option_time":"","option1_date":"","option1_time":"","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"","customer_phone":"","updated_at":"2026-06-13T08:53:58.826Z"}</t>
+  </si>
+  <si>
+    <t>["09:00","09:30","10:00","10:30","11:00"]</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","option_count":0,"current_option_date":"2026-06-14T21:00:00.000Z","current_option_time":"","option1_date":"","option1_time":"","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"","customer_phone":"","updated_at":"2026-06-13T09:17:56.627Z"}</t>
+  </si>
+  <si>
+    <t>["07:00","07:30","17:00"]</t>
+  </si>
+  <si>
+    <t>{"id":"3118605852107323766","from":{"id":726107007,"is_bot":false,"first_name":"Serhii","username":"Serhii_Tsi","language_code":"en"},"message":{"message_id":1280,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":726107007,"first_name":"Serhii","username":"Serhii_Tsi","type":"private"},"date":1781342364,"text":"Новая заявка\n\n👤 Клиент: Оля\n📞 Телефон: +380664452124\n\n📍 Филиал: Центр\n💅 Услуга: Окрашивание\n👩‍💼 Мастер: Анна\n\nВарианты времени:\n1) 15.06.2026 07:30","entities":[{"offset":0,"length":12,"type":"bold"},{"offset":41,"length":13,"type":"phone_number"},{"offset":116,"length":17,"type":"bold"}],"reply_markup":{"inline_keyboard":[[{"text":"✅ 1","callback_data":"approve_option_1|req_1781342354313"}],[{"text":"❌ Reject","callback_data":"reject_request|req_1781342354313"}]]}},"chat_instance":"-653345212733041723","data":"approve_option_1|req_1781342354313"}</t>
+  </si>
+  <si>
+    <t>MY_APPOINTMENTS_PHONE</t>
+  </si>
+  <si>
+    <t>SHOW_MY_APPOINTMENTS</t>
+  </si>
+  <si>
+    <t>SHOW_MY_APPOINTMENTS_COUNT</t>
+  </si>
+  <si>
     <t>location_id</t>
   </si>
   <si>
@@ -280,16 +355,10 @@
     <t>name_en</t>
   </si>
   <si>
-    <t>min_duration</t>
-  </si>
-  <si>
-    <t>max_duration</t>
-  </si>
-  <si>
-    <t>price_from</t>
-  </si>
-  <si>
-    <t>price_to</t>
+    <t>default_duration_minutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base_price	</t>
   </si>
   <si>
     <t>active</t>
@@ -319,12 +388,30 @@
     <t>Hair coloring</t>
   </si>
   <si>
+    <t>customer_id</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>service_name</t>
+  </si>
+  <si>
+    <t>provider_name</t>
+  </si>
+  <si>
+    <t>duration_minutes</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
     <t>request_id</t>
   </si>
   <si>
-    <t>customer_id</t>
-  </si>
-  <si>
     <t>status</t>
   </si>
   <si>
@@ -373,6 +460,51 @@
     <t>cust_1781322885063</t>
   </si>
   <si>
+    <t>req_1781330788097</t>
+  </si>
+  <si>
+    <t>cust_1781330787581</t>
+  </si>
+  <si>
+    <t>rejected</t>
+  </si>
+  <si>
+    <t>req_1781333630936</t>
+  </si>
+  <si>
+    <t>cust_1781333630596</t>
+  </si>
+  <si>
+    <t>req_1781334080788</t>
+  </si>
+  <si>
+    <t>cust_1781334079107</t>
+  </si>
+  <si>
+    <t>req_1781335348889</t>
+  </si>
+  <si>
+    <t>cust_1781335348469</t>
+  </si>
+  <si>
+    <t>req_1781335484784</t>
+  </si>
+  <si>
+    <t>cust_1781335484421</t>
+  </si>
+  <si>
+    <t>req_1781338203105</t>
+  </si>
+  <si>
+    <t>cust_1781338202420</t>
+  </si>
+  <si>
+    <t>req_1781342354313</t>
+  </si>
+  <si>
+    <t>cust_1781342353607</t>
+  </si>
+  <si>
     <t>option_id</t>
   </si>
   <si>
@@ -448,15 +580,33 @@
     <t>req_1781290148915</t>
   </si>
   <si>
-    <t>rejected</t>
-  </si>
-  <si>
     <t>opt_1781293783659</t>
   </si>
   <si>
     <t>opt_1781322885791</t>
   </si>
   <si>
+    <t>opt_1781330788586</t>
+  </si>
+  <si>
+    <t>opt_1781333631581</t>
+  </si>
+  <si>
+    <t>opt_1781334082959</t>
+  </si>
+  <si>
+    <t>opt_1781335349433</t>
+  </si>
+  <si>
+    <t>opt_1781335485162</t>
+  </si>
+  <si>
+    <t>opt_1781338204252</t>
+  </si>
+  <si>
+    <t>opt_1781342355024</t>
+  </si>
+  <si>
     <t>prov_002</t>
   </si>
   <si>
@@ -469,24 +619,90 @@
     <t>end_time</t>
   </si>
   <si>
-    <t>monday</t>
-  </si>
-  <si>
-    <t>tuesday</t>
-  </si>
-  <si>
-    <t>phone</t>
+    <t>is_working</t>
+  </si>
+  <si>
+    <t>Анна</t>
+  </si>
+  <si>
+    <t>MON</t>
+  </si>
+  <si>
+    <t>TUE</t>
+  </si>
+  <si>
+    <t>WED</t>
+  </si>
+  <si>
+    <t>THU</t>
+  </si>
+  <si>
+    <t>FRI</t>
+  </si>
+  <si>
+    <t>SAT</t>
+  </si>
+  <si>
+    <t>SUN</t>
+  </si>
+  <si>
+    <t>выходной</t>
+  </si>
+  <si>
+    <t>Марина</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>короткий день</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProviderSchedule.day_of_week: </t>
+  </si>
+  <si>
+    <t>MON, TUE, WED, THU, FRI, SAT, SUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пример для </t>
+  </si>
+  <si>
+    <t>ProviderSchedule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProviderScheduleOverrides.date: </t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD, for example 2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">start_time / end_time: </t>
+  </si>
+  <si>
+    <t>HH:MM, for example 09:00 or 14:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_working: </t>
+  </si>
+  <si>
+    <t>TRUE или FALSE</t>
+  </si>
+  <si>
+    <t>ProviderScheduleOverrides</t>
+  </si>
+  <si>
+    <t>calendar_id</t>
   </si>
   <si>
     <t>Ганна</t>
   </si>
   <si>
-    <t>Анна</t>
-  </si>
-  <si>
     <t>Ann</t>
   </si>
   <si>
+    <t>primary</t>
+  </si>
+  <si>
     <t>loc_002</t>
   </si>
   <si>
@@ -496,9 +712,6 @@
     <t>Olga</t>
   </si>
   <si>
-    <t>Марина</t>
-  </si>
-  <si>
     <t>Marina</t>
   </si>
   <si>
@@ -910,13 +1123,13 @@
     <t>ENTER_PHONE</t>
   </si>
   <si>
-    <t>Введіть ваш телефон (+38...)</t>
-  </si>
-  <si>
-    <t>Введите ваш телефон (+38...)</t>
-  </si>
-  <si>
-    <t>Enter your phone number (+1...)</t>
+    <t>Введіть ваш телефон</t>
+  </si>
+  <si>
+    <t>Введите ваш телефон</t>
+  </si>
+  <si>
+    <t>Enter your phone number</t>
   </si>
   <si>
     <t>REQUEST_DRAFT_READY</t>
@@ -1141,6 +1354,90 @@
     <t>❌ Rejected</t>
   </si>
   <si>
+    <t>NO_AVAILABLE_TIME</t>
+  </si>
+  <si>
+    <t>На цю дату немає доступного часу. Оберіть іншу дату.</t>
+  </si>
+  <si>
+    <t>На эту дату нет доступного времени. Выберите другую дату.</t>
+  </si>
+  <si>
+    <t>No available time for this date. Please select another date.</t>
+  </si>
+  <si>
+    <t>SELECT_CUSTOM_DATE</t>
+  </si>
+  <si>
+    <t>Оберіть дату</t>
+  </si>
+  <si>
+    <t>Выберите дату</t>
+  </si>
+  <si>
+    <t>Select date</t>
+  </si>
+  <si>
+    <t>MY_APPOINTMENTS</t>
+  </si>
+  <si>
+    <t>Мої записи</t>
+  </si>
+  <si>
+    <t>Мои записи</t>
+  </si>
+  <si>
+    <t>My appointments</t>
+  </si>
+  <si>
+    <t>YOUR_APPOINTMENTS</t>
+  </si>
+  <si>
+    <t>Ваші записи</t>
+  </si>
+  <si>
+    <t>Ваши записи</t>
+  </si>
+  <si>
+    <t>Your appointments</t>
+  </si>
+  <si>
+    <t>ENTER_PHONE_FOR_APPOINTMENTS</t>
+  </si>
+  <si>
+    <t>Введіть номер телефону</t>
+  </si>
+  <si>
+    <t>Введите номер телефона</t>
+  </si>
+  <si>
+    <t>Enter phone number</t>
+  </si>
+  <si>
+    <t>PHONE_INVALID</t>
+  </si>
+  <si>
+    <t>Невірний формат телефону</t>
+  </si>
+  <si>
+    <t>Неверный формат телефона</t>
+  </si>
+  <si>
+    <t>Invalid phone format</t>
+  </si>
+  <si>
+    <t>NO_ACTIVE_APPOINTMENTS</t>
+  </si>
+  <si>
+    <t>У вас немає активних записів. Перевірте номер телефону та спробуйте ще раз.</t>
+  </si>
+  <si>
+    <t>У вас нет активных записей. Проверьте номер телефона и попробуйте ещё раз.</t>
+  </si>
+  <si>
+    <t>You have no active appointments. Please check the phone number and try again.</t>
+  </si>
+  <si>
     <t>address</t>
   </si>
   <si>
@@ -1171,9 +1468,6 @@
     <t>last_visit_at</t>
   </si>
   <si>
-    <t>notes</t>
-  </si>
-  <si>
     <t>cust_1781289974856</t>
   </si>
   <si>
@@ -1195,6 +1489,12 @@
     <t>Оля</t>
   </si>
   <si>
+    <t>Нина</t>
+  </si>
+  <si>
+    <t>Дана</t>
+  </si>
+  <si>
     <t>start_at</t>
   </si>
   <si>
@@ -1204,10 +1504,22 @@
     <t>calendar_event_id</t>
   </si>
   <si>
-    <t>appt_1781293819707</t>
-  </si>
-  <si>
-    <t>appt_1781322908547</t>
+    <t>appt_1781335362329</t>
+  </si>
+  <si>
+    <t>appt_1781335538233</t>
+  </si>
+  <si>
+    <t>appt_1781338222893</t>
+  </si>
+  <si>
+    <t>t03h2nhnq7fqrfka6j7vfm5c0c@google.com</t>
+  </si>
+  <si>
+    <t>appt_1781342386659</t>
+  </si>
+  <si>
+    <t>84453ksvp3vphhlnpb5v7nrir4@google.com</t>
   </si>
 </sst>
 </file>
@@ -1242,11 +1554,11 @@
       <color rgb="FF0000FF"/>
     </font>
     <font>
-      <b/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -1265,7 +1577,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1300,10 +1612,16 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1312,25 +1630,22 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="19" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -1373,6 +1688,18 @@
 </file>
 
 <file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1765,106 +2092,310 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="3" max="3" width="13.25"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>85</v>
+      <c r="A1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>101</v>
+      <c r="A2" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F2" s="13">
-        <f>+380111111111</f>
-        <v>380111111111</v>
-      </c>
-      <c r="H2" s="14" t="b">
+        <v>195</v>
+      </c>
+      <c r="D2" s="9">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F2" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>150</v>
+      <c r="A3" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F3" s="13">
-        <f>+380111111112</f>
-        <v>380111111112</v>
-      </c>
-      <c r="H3" s="14" t="b">
+        <v>196</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F3" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>101</v>
+      <c r="A4" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F4" s="13">
-        <f>+380111111113</f>
-        <v>380111111113</v>
-      </c>
-      <c r="H4" s="14" t="b">
+        <v>197</v>
+      </c>
+      <c r="D4" s="9">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F4" s="2" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F5" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D6" s="9">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F6" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="F7" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F10" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F11" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F12" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F13" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F14" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="F15" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -1880,63 +2411,66 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>2</v>
+      <c r="A1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" s="19">
-        <v>46204.0</v>
-      </c>
-      <c r="D2" s="19">
-        <v>46210.0</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>161</v>
+      <c r="A2" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" s="8">
+        <v>46187.0</v>
+      </c>
+      <c r="F2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="C3" s="19">
-        <v>46188.0</v>
-      </c>
-      <c r="D3" s="19">
-        <v>46188.0</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>164</v>
+      <c r="A3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C3" s="8">
+        <v>46189.0</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="F3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -1950,61 +2484,226 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="27.75"/>
+    <col customWidth="1" min="2" max="2" width="41.38"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>96</v>
+      <c r="A1" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="D2" s="20">
-        <v>46187.583333333336</v>
-      </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12" t="s">
-        <v>102</v>
+      <c r="A2" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G2" s="9">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="H2" s="9">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I2" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D3" s="20">
-        <v>46188.5</v>
-      </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12" t="s">
-        <v>102</v>
+      <c r="A3" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G3" s="9">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="H3" s="9">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I3" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I4" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I5" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I6" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="D7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="I7" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F12" s="8">
+        <v>46188.0</v>
+      </c>
+      <c r="I12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F13" s="8">
+        <v>46189.0</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="I13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -2013,6 +2712,271 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="13.25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F2" s="15">
+        <f>+380111111111</f>
+        <v>380111111111</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I2" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F3" s="15">
+        <f>+380111111112</f>
+        <v>380111111112</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I3" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F4" s="15">
+        <f>+380111111113</f>
+        <v>380111111113</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I4" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="20">
+        <v>46204.0</v>
+      </c>
+      <c r="D2" s="20">
+        <v>46210.0</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="20">
+        <v>46188.0</v>
+      </c>
+      <c r="D3" s="20">
+        <v>46188.0</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="D2" s="21">
+        <v>46187.583333333336</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="D3" s="21">
+        <v>46188.5</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2030,699 +2994,797 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>174</v>
+        <v>244</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>175</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>176</v>
+        <v>246</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>177</v>
+        <v>247</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>178</v>
+        <v>248</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>179</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>181</v>
+        <v>251</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>182</v>
+        <v>252</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>183</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>184</v>
+        <v>254</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>185</v>
+        <v>255</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>186</v>
+        <v>256</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>188</v>
+        <v>258</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>189</v>
+        <v>259</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>191</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>192</v>
+        <v>262</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>193</v>
+        <v>263</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>194</v>
+        <v>264</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>195</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>196</v>
+        <v>266</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>198</v>
+        <v>268</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>199</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>201</v>
+        <v>271</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>202</v>
+        <v>272</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>203</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>204</v>
+        <v>274</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>205</v>
+        <v>275</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>206</v>
+        <v>276</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>207</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>208</v>
+        <v>278</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>209</v>
+        <v>279</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>211</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>213</v>
+        <v>283</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>214</v>
+        <v>284</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>215</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>216</v>
+        <v>286</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>217</v>
+        <v>287</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>219</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>221</v>
+        <v>291</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>222</v>
+        <v>292</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>223</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>224</v>
+        <v>294</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>225</v>
+        <v>295</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>226</v>
+        <v>296</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>227</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>228</v>
+        <v>298</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>229</v>
+        <v>299</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>230</v>
+        <v>300</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>231</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>232</v>
+        <v>302</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>233</v>
+        <v>303</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>234</v>
+        <v>304</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>235</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>236</v>
+        <v>306</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>237</v>
+        <v>307</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>237</v>
+        <v>307</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>238</v>
+        <v>308</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>239</v>
+        <v>309</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>240</v>
+        <v>310</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>241</v>
+        <v>311</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>242</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>243</v>
+        <v>313</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>245</v>
+        <v>315</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>246</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>247</v>
+        <v>317</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>248</v>
+        <v>318</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>249</v>
+        <v>319</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>250</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>251</v>
+        <v>321</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>252</v>
+        <v>322</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>253</v>
+        <v>323</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>254</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>255</v>
+        <v>325</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>256</v>
+        <v>326</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>257</v>
+        <v>327</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>258</v>
+        <v>328</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>261</v>
+        <v>331</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>262</v>
+        <v>332</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>263</v>
+        <v>333</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>264</v>
+        <v>334</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>265</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>267</v>
+        <v>337</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>268</v>
+        <v>338</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>269</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>270</v>
+        <v>340</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>271</v>
+        <v>341</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>272</v>
+        <v>342</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>273</v>
+        <v>343</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>274</v>
+        <v>344</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>275</v>
+        <v>345</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>276</v>
+        <v>346</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>277</v>
+        <v>347</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>278</v>
+        <v>348</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>279</v>
+        <v>349</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>281</v>
+        <v>351</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>282</v>
+        <v>352</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>283</v>
+        <v>353</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>284</v>
+        <v>354</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>285</v>
+        <v>355</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>286</v>
+        <v>356</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>287</v>
+        <v>357</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>288</v>
+        <v>358</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>289</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>290</v>
+        <v>360</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>291</v>
+        <v>361</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>293</v>
+        <v>363</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>294</v>
+        <v>364</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>295</v>
+        <v>365</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>296</v>
+        <v>366</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>297</v>
+        <v>367</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>298</v>
+        <v>368</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>299</v>
+        <v>369</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>301</v>
+        <v>371</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>302</v>
+        <v>372</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>303</v>
+        <v>373</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>304</v>
+        <v>374</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>305</v>
+        <v>375</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>306</v>
+        <v>376</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>307</v>
+        <v>377</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>307</v>
+        <v>377</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>308</v>
+        <v>378</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>309</v>
+        <v>379</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>310</v>
+        <v>380</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>311</v>
+        <v>381</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>312</v>
+        <v>382</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>313</v>
+        <v>383</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>314</v>
+        <v>384</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>314</v>
+        <v>384</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>315</v>
+        <v>385</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>316</v>
+        <v>386</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>317</v>
+        <v>387</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>318</v>
+        <v>388</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>319</v>
+        <v>389</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>320</v>
+        <v>390</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>321</v>
+        <v>391</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>322</v>
+        <v>392</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>323</v>
+        <v>393</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>324</v>
+        <v>394</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>325</v>
+        <v>395</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>326</v>
+        <v>396</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>327</v>
+        <v>397</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>328</v>
+        <v>398</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>329</v>
+        <v>399</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>332</v>
+        <v>402</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>333</v>
+        <v>403</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>334</v>
+        <v>404</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>335</v>
+        <v>405</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>336</v>
+        <v>406</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>337</v>
+        <v>407</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>338</v>
+        <v>408</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>339</v>
+        <v>409</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>340</v>
+        <v>410</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>341</v>
+        <v>411</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>342</v>
+        <v>412</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>343</v>
+        <v>413</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>344</v>
+        <v>414</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>345</v>
+        <v>415</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>346</v>
+        <v>416</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>347</v>
+        <v>417</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>348</v>
+        <v>418</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>349</v>
+        <v>419</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>351</v>
+        <v>421</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>352</v>
+        <v>422</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>353</v>
+        <v>423</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>354</v>
+        <v>424</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>355</v>
+        <v>425</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>356</v>
+        <v>426</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>357</v>
+        <v>427</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>359</v>
+        <v>429</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>360</v>
+        <v>430</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>361</v>
+        <v>431</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>362</v>
+        <v>432</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>363</v>
+        <v>433</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>364</v>
+        <v>434</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>365</v>
+        <v>435</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>366</v>
+        <v>436</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>367</v>
+        <v>437</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -2730,7 +3792,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2741,43 +3803,43 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>85</v>
+      <c r="A1" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>369</v>
+        <v>467</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>369</v>
+        <v>467</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>370</v>
+        <v>468</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>371</v>
+        <v>469</v>
       </c>
       <c r="F2" s="7">
         <f>+380000000001</f>
@@ -2789,19 +3851,19 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>150</v>
+        <v>221</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>372</v>
+        <v>470</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>373</v>
+        <v>471</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>374</v>
+        <v>472</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>371</v>
+        <v>469</v>
       </c>
       <c r="F3" s="7">
         <f>+380000000002</f>
@@ -2816,7 +3878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2832,45 +3894,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>375</v>
+        <v>473</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>376</v>
+        <v>474</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>377</v>
+        <v>475</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>378</v>
+        <v>124</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>379</v>
+        <v>476</v>
       </c>
       <c r="B2" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>380</v>
+        <v>477</v>
       </c>
       <c r="D2" s="7">
         <v>3804562658652</v>
@@ -2884,19 +3946,19 @@
       <c r="G2" s="6">
         <v>46185.90711637732</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>109</v>
+      <c r="I2" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>381</v>
+        <v>478</v>
       </c>
       <c r="B3" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>382</v>
+        <v>479</v>
       </c>
       <c r="D3" s="7">
         <v>38052425635966</v>
@@ -2910,19 +3972,19 @@
       <c r="G3" s="6">
         <v>46185.90912765046</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>383</v>
+      <c r="I3" s="2" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="B4" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="D4" s="7">
         <v>3804452125648</v>
@@ -2936,19 +3998,19 @@
       <c r="G4" s="6">
         <v>46185.93864143519</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>383</v>
+      <c r="I4" s="2" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="B5" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>384</v>
+        <v>481</v>
       </c>
       <c r="D5" s="7">
         <v>38045245268</v>
@@ -2962,19 +4024,19 @@
       <c r="G5" s="6">
         <v>46185.943211805556</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>383</v>
+      <c r="I5" s="2" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="B6" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="D6" s="7">
         <v>3502452635165</v>
@@ -2988,19 +4050,19 @@
       <c r="G6" s="6">
         <v>46185.947925671295</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>383</v>
+      <c r="I6" s="2" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="B7" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="D7" s="7">
         <v>38055245256685</v>
@@ -3014,19 +4076,19 @@
       <c r="G7" s="6">
         <v>46185.95117884259</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>109</v>
+      <c r="I7" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="B8" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>385</v>
+        <v>482</v>
       </c>
       <c r="D8" s="7">
         <v>3805542545878</v>
@@ -3040,8 +4102,190 @@
       <c r="G8" s="6">
         <v>46186.288021562505</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>109</v>
+      <c r="I8" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D9" s="7">
+        <v>380452452568</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46186.3794858912</v>
+      </c>
+      <c r="G9" s="6">
+        <v>46186.3794858912</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D10" s="7">
+        <v>380542452357</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46186.412391157406</v>
+      </c>
+      <c r="G10" s="6">
+        <v>46186.412391157406</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D11" s="2">
+        <v>6.545498798798E12</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46186.417582256945</v>
+      </c>
+      <c r="G11" s="6">
+        <v>46186.417582256945</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2.5452358485E10</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46186.43227394676</v>
+      </c>
+      <c r="G12" s="6">
+        <v>46186.43227394676</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D13" s="2">
+        <v>5.2325648458E10</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46186.433847465276</v>
+      </c>
+      <c r="G13" s="6">
+        <v>46186.433847465276</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D14" s="7">
+        <v>3524587568</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46186.46530578704</v>
+      </c>
+      <c r="G14" s="6">
+        <v>46186.46530578704</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D15" s="7">
+        <v>380664452124</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46186.51335193287</v>
+      </c>
+      <c r="G15" s="6">
+        <v>46186.51335193287</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -3049,7 +4293,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3057,112 +4301,206 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="7" max="7" width="14.0"/>
+    <col customWidth="1" min="8" max="8" width="16.5"/>
     <col customWidth="1" min="10" max="10" width="16.25"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="21" t="s">
-        <v>386</v>
-      </c>
-      <c r="H1" s="21" t="s">
-        <v>387</v>
-      </c>
-      <c r="I1" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="J1" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="L1" s="17" t="s">
+      <c r="A1" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>485</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>486</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>487</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="L1" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="s">
-        <v>389</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G2" s="22">
-        <v>46186.395833333336</v>
-      </c>
-      <c r="H2" s="20"/>
-      <c r="I2" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="J2" s="12"/>
+      <c r="A2" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="G2" s="23">
+        <v>46188.4375</v>
+      </c>
+      <c r="H2" s="23">
+        <v>46188.5625</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="J2" s="13"/>
       <c r="K2" s="6">
-        <v>46185.95161697917</v>
+        <v>46186.43243436342</v>
       </c>
       <c r="L2" s="6">
-        <v>46185.95161697917</v>
+        <v>46186.43243436342</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>390</v>
+        <v>489</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G3" s="23">
-        <v>46187.395833333336</v>
+        <v>129</v>
+      </c>
+      <c r="G3" s="24">
+        <v>46188.583333333336</v>
+      </c>
+      <c r="H3" s="24">
+        <v>46188.708333333336</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="K3" s="6">
-        <v>46186.28829336805</v>
+        <v>46186.43447028935</v>
       </c>
       <c r="L3" s="6">
-        <v>46186.28829336805</v>
-      </c>
+        <v>46186.43447028935</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="24">
+        <v>46186.583333333336</v>
+      </c>
+      <c r="H4" s="24">
+        <v>46186.708333333336</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="K4" s="6">
+        <v>46186.465542743055</v>
+      </c>
+      <c r="L4" s="6">
+        <v>46186.465615</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" s="24">
+        <v>46188.3125</v>
+      </c>
+      <c r="H5" s="24">
+        <v>46188.4375</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="K5" s="6">
+        <v>46186.513734479166</v>
+      </c>
+      <c r="L5" s="6">
+        <v>46186.51379153936</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7">
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -3197,7 +4535,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="6">
-        <v>46186.28811368055</v>
+        <v>46186.573699988425</v>
       </c>
     </row>
     <row r="3">
@@ -3214,6 +4552,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="18.5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -4053,6 +5394,545 @@
       </c>
       <c r="C81" s="2" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6">
+        <v>46186.41775136574</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6">
+        <v>46186.417783854165</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6">
+        <v>46186.42497141204</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6">
+        <v>46186.42505675926</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6">
+        <v>46186.431714861115</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6">
+        <v>46186.431775543984</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6">
+        <v>46186.43241512732</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6">
+        <v>46186.43308650463</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6">
+        <v>46186.43313398148</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6">
+        <v>46186.43444618056</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6">
+        <v>46186.464660011574</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6">
+        <v>46186.464710138884</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6">
+        <v>46186.465507500005</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6">
+        <v>46186.49582439815</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6">
+        <v>46186.49588797454</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6">
+        <v>46186.51247297454</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6">
+        <v>46186.51256541666</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6">
+        <v>46186.51371832176</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6">
+        <v>46186.54792916667</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C100" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6">
+        <v>46186.55133717593</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C101" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6">
+        <v>46186.55133998842</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C102" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6">
+        <v>46186.55134502315</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C103" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6">
+        <v>46186.55738844907</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C104" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6">
+        <v>46186.55739122685</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C105" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6">
+        <v>46186.55740452546</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C106" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6">
+        <v>46186.55855090277</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C107" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6">
+        <v>46186.55855365741</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C108" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6">
+        <v>46186.55856258102</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C109" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6">
+        <v>46186.56195840277</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C110" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6">
+        <v>46186.56196146991</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C111" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6">
+        <v>46186.561970752315</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C112" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6">
+        <v>46186.56308354167</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C113" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6">
+        <v>46186.56308648148</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C114" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6">
+        <v>46186.563095370366</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C115" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6">
+        <v>46186.56360149306</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C116" s="2">
+        <v>3.80664452124E11</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6">
+        <v>46186.56360570602</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C117" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6">
+        <v>46186.56361887731</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C118" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6">
+        <v>46186.56397189815</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C119" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6">
+        <v>46186.56398672453</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C120" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6">
+        <v>46186.56401130787</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C121" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6">
+        <v>46186.564427731486</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C122" s="7">
+        <v>37576</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6">
+        <v>46186.56443180556</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C123" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6">
+        <v>46186.564444895834</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C124" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6">
+        <v>46186.57339975695</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C125" s="2">
+        <v>5.12455545E8</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6">
+        <v>46186.57340252315</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C126" s="2">
+        <v>5.12455545E8</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6">
+        <v>46186.57341622685</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C127" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6">
+        <v>46186.57365791667</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C128" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6">
+        <v>46186.57366061343</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C129" s="2">
+        <v>6.64452124E8</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6">
+        <v>46186.57366921296</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C130" s="2">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -4077,46 +5957,46 @@
         <v>28</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>30</v>
@@ -4153,91 +6033,76 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="5" max="5" width="26.5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>82</v>
+        <v>104</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" s="13">
-        <v>60.0</v>
-      </c>
-      <c r="F2" s="13">
-        <v>90.0</v>
-      </c>
-      <c r="G2" s="13">
+      <c r="A2" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="14">
+        <v>80.0</v>
+      </c>
+      <c r="F2" s="15">
         <v>500.0</v>
       </c>
-      <c r="H2" s="13">
-        <v>700.0</v>
-      </c>
-      <c r="I2" s="14" t="b">
+      <c r="G2" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="13">
+      <c r="A3" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="14">
         <v>180.0</v>
       </c>
-      <c r="F3" s="13">
-        <v>300.0</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="15">
         <v>1500.0</v>
       </c>
-      <c r="H3" s="13">
-        <v>3000.0</v>
-      </c>
-      <c r="I3" s="14" t="b">
+      <c r="G3" s="11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4253,147 +6118,42 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="20.38"/>
-    <col customWidth="1" min="2" max="2" width="19.0"/>
-    <col customWidth="1" min="7" max="7" width="16.13"/>
+    <col customWidth="1" min="8" max="8" width="15.75"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="A1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G2" s="6">
-        <v>46185.93864650463</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G3" s="6">
-        <v>46185.94321923611</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" s="6">
-        <v>46185.947929629634</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G5" s="6">
-        <v>46185.95118355324</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G6" s="6">
-        <v>46186.28802574074</v>
+      <c r="G1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -4408,376 +6168,308 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="16.25"/>
-    <col customWidth="1" min="4" max="4" width="20.63"/>
+    <col customWidth="1" min="1" max="1" width="20.38"/>
+    <col customWidth="1" min="2" max="2" width="19.0"/>
+    <col customWidth="1" min="7" max="7" width="16.13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>97</v>
+      <c r="A1" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C2" s="10">
-        <v>46186.0</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.3527314814818965</v>
-      </c>
-      <c r="E2" s="5">
-        <v>1.0</v>
+        <v>127</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="G2" s="6">
-        <v>46185.85522081019</v>
+        <v>46185.93864650463</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" s="10">
-        <v>46185.0</v>
-      </c>
-      <c r="D3" s="15">
-        <v>0.7693981481497758</v>
-      </c>
-      <c r="E3" s="5">
-        <v>2.0</v>
+        <v>132</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="G3" s="6">
-        <v>46185.85522081019</v>
+        <v>46185.94321923611</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C4" s="10">
-        <v>46186.0</v>
-      </c>
-      <c r="D4" s="15">
-        <v>0.3527314814818965</v>
-      </c>
-      <c r="E4" s="5">
-        <v>1.0</v>
+        <v>135</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="G4" s="6">
-        <v>46185.86117096065</v>
+        <v>46185.947929629634</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>121</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" s="10">
-        <v>46187.0</v>
-      </c>
-      <c r="D5" s="15">
-        <v>0.5193981481497758</v>
-      </c>
-      <c r="E5" s="5">
-        <v>2.0</v>
+        <v>136</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="G5" s="6">
-        <v>46185.86117096065</v>
+        <v>46185.95118355324</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="10">
-        <v>46185.0</v>
-      </c>
-      <c r="D6" s="15">
-        <v>0.7693981481497758</v>
-      </c>
-      <c r="E6" s="5">
-        <v>3.0</v>
+        <v>139</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="G6" s="6">
-        <v>46185.86117096065</v>
+        <v>46186.28802574074</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="10">
-        <v>46186.0</v>
-      </c>
-      <c r="D7" s="15">
-        <v>0.3527314814818965</v>
-      </c>
-      <c r="E7" s="5">
-        <v>1.0</v>
+        <v>141</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="G7" s="6">
-        <v>46185.86662434028</v>
+        <v>46186.37949186342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C8" s="10">
-        <v>46187.0</v>
-      </c>
-      <c r="D8" s="15">
-        <v>0.43606481481401715</v>
-      </c>
-      <c r="E8" s="5">
-        <v>2.0</v>
+        <v>144</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="G8" s="6">
-        <v>46185.86662434028</v>
+        <v>46186.41239509259</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" s="10">
-        <v>46185.0</v>
-      </c>
-      <c r="D9" s="15">
-        <v>0.7693981481497758</v>
-      </c>
-      <c r="E9" s="5">
-        <v>3.0</v>
+        <v>146</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="G9" s="6">
-        <v>46185.86662434028</v>
+        <v>46186.417601712965</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="10">
-        <v>46186.0</v>
-      </c>
-      <c r="D10" s="15">
-        <v>0.3527314814818965</v>
-      </c>
-      <c r="E10" s="5">
-        <v>1.0</v>
+      <c r="E10" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="G10" s="6">
-        <v>46185.87604545139</v>
+        <v>46186.43227880787</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C11" s="10">
-        <v>46186.0</v>
-      </c>
-      <c r="D11" s="15">
-        <v>0.3943981481497758</v>
-      </c>
-      <c r="E11" s="5">
-        <v>2.0</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="G11" s="6">
-        <v>46185.87604545139</v>
+        <v>46186.43385166666</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="10">
-        <v>46186.0</v>
-      </c>
-      <c r="D12" s="15">
-        <v>0.3527314814818965</v>
-      </c>
-      <c r="E12" s="5">
-        <v>1.0</v>
+        <v>152</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="G12" s="6">
-        <v>46185.880830740745</v>
+        <v>46186.46531371528</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C13" s="10">
-        <v>46186.0</v>
-      </c>
-      <c r="D13" s="15">
-        <v>0.3958333333321207</v>
-      </c>
-      <c r="E13" s="5">
-        <v>1.0</v>
+        <v>154</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G13" s="6">
-        <v>46185.90712123843</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="10">
-        <v>46185.0</v>
-      </c>
-      <c r="D14" s="15">
-        <v>0.3333333333321207</v>
-      </c>
-      <c r="E14" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G14" s="6">
-        <v>46185.909134305555</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="10">
-        <v>46186.0</v>
-      </c>
-      <c r="D15" s="15">
-        <v>0.3958333333321207</v>
-      </c>
-      <c r="E15" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G15" s="6">
-        <v>46185.95119975695</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="10">
-        <v>46187.0</v>
-      </c>
-      <c r="D16" s="15">
-        <v>0.3958333333321207</v>
-      </c>
-      <c r="E16" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G16" s="6">
-        <v>46186.28802998843</v>
+        <v>46186.51336010417</v>
       </c>
     </row>
   </sheetData>
@@ -4791,49 +6483,538 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="16.25"/>
+    <col customWidth="1" min="4" max="4" width="20.63"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>85</v>
+      <c r="A1" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="14" t="b">
-        <v>1</v>
+      <c r="A2" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D2" s="17">
+        <v>0.3527314814818965</v>
+      </c>
+      <c r="E2" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="6">
+        <v>46185.85522081019</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="14" t="b">
-        <v>1</v>
+      <c r="A3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="10">
+        <v>46185.0</v>
+      </c>
+      <c r="D3" s="17">
+        <v>0.7693981481497758</v>
+      </c>
+      <c r="E3" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3" s="6">
+        <v>46185.85522081019</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D4" s="17">
+        <v>0.3527314814818965</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G4" s="6">
+        <v>46185.86117096065</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="10">
+        <v>46187.0</v>
+      </c>
+      <c r="D5" s="17">
+        <v>0.5193981481497758</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="6">
+        <v>46185.86117096065</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="10">
+        <v>46185.0</v>
+      </c>
+      <c r="D6" s="17">
+        <v>0.7693981481497758</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G6" s="6">
+        <v>46185.86117096065</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C7" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D7" s="17">
+        <v>0.3527314814818965</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G7" s="6">
+        <v>46185.86662434028</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="10">
+        <v>46187.0</v>
+      </c>
+      <c r="D8" s="17">
+        <v>0.43606481481401715</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G8" s="6">
+        <v>46185.86662434028</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="10">
+        <v>46185.0</v>
+      </c>
+      <c r="D9" s="17">
+        <v>0.7693981481497758</v>
+      </c>
+      <c r="E9" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G9" s="6">
+        <v>46185.86662434028</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C10" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D10" s="17">
+        <v>0.3527314814818965</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G10" s="6">
+        <v>46185.87604545139</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D11" s="17">
+        <v>0.3943981481497758</v>
+      </c>
+      <c r="E11" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G11" s="6">
+        <v>46185.87604545139</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D12" s="17">
+        <v>0.3527314814818965</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="6">
+        <v>46185.880830740745</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D13" s="17">
+        <v>0.3958333333321207</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G13" s="6">
+        <v>46185.90712123843</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="10">
+        <v>46185.0</v>
+      </c>
+      <c r="D14" s="17">
+        <v>0.3333333333321207</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G14" s="6">
+        <v>46185.909134305555</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D15" s="17">
+        <v>0.3958333333321207</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G15" s="6">
+        <v>46185.95119975695</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="10">
+        <v>46187.0</v>
+      </c>
+      <c r="D16" s="17">
+        <v>0.3958333333321207</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G16" s="6">
+        <v>46186.28802998843</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" s="14" t="b">
-        <v>1</v>
+      <c r="C17" s="10">
+        <v>46240.0</v>
+      </c>
+      <c r="D17" s="17">
+        <v>0.6458333333321207</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G17" s="6">
+        <v>46186.37949752314</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" s="10">
+        <v>46195.0</v>
+      </c>
+      <c r="D18" s="17">
+        <v>0.4375</v>
+      </c>
+      <c r="E18" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G18" s="6">
+        <v>46186.41240255787</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" s="10">
+        <v>46188.0</v>
+      </c>
+      <c r="D19" s="17">
+        <v>0.4375</v>
+      </c>
+      <c r="E19" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G19" s="6">
+        <v>46186.41762684028</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C20" s="10">
+        <v>46188.0</v>
+      </c>
+      <c r="D20" s="17">
+        <v>0.4375</v>
+      </c>
+      <c r="E20" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G20" s="6">
+        <v>46186.432285104165</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C21" s="10">
+        <v>46188.0</v>
+      </c>
+      <c r="D21" s="17">
+        <v>0.5833333333321207</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G21" s="6">
+        <v>46186.433856041665</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" s="10">
+        <v>46186.0</v>
+      </c>
+      <c r="D22" s="17">
+        <v>0.5833333333321207</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G22" s="6">
+        <v>46186.46532699074</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="10">
+        <v>46188.0</v>
+      </c>
+      <c r="D23" s="17">
+        <v>0.3125</v>
+      </c>
+      <c r="E23" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G23" s="6">
+        <v>46186.51336833333</v>
       </c>
     </row>
   </sheetData>
@@ -4849,53 +7030,46 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>85</v>
+      <c r="A1" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.375</v>
-      </c>
-      <c r="D2" s="16">
-        <v>0.75</v>
-      </c>
-      <c r="E2" s="14" t="b">
+      <c r="A2" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="16">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="D3" s="16">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E3" s="14" t="b">
+      <c r="A3" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="11" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Docs/SmartFlow Beauty Demo.xlsx
+++ b/Docs/SmartFlow Beauty Demo.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="758">
   <si>
     <t>key</t>
   </si>
@@ -640,6 +640,258 @@
     <t>{"customer_id":"cust_1781369668627","telegram_id":7752853740,"name":"Аня","phone":"0442536598","language":"ru","created_at":"2026-06-13T16:54:28.627Z","updated_at":"2026-06-13T16:54:28.627Z","last_visit_at":"","status":"confirmed","notes":""}</t>
   </si>
   <si>
+    <t>text=Алиса, state=WAITING_PROVIDER, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>text=Другая дата, state=WAITING_OPTION_DATE, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>text=18.06, state=WAITING_CUSTOM_DATE, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","option_count":0,"current_option_date":"2026-06-17T21:00:00.000Z","current_option_time":"","option1_date":"","option1_time":"","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"","customer_phone":""}</t>
+  </si>
+  <si>
+    <t>text=09:30, state=WAITING_OPTION_TIME, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>text=Да, state=WAITING_ADD_ANOTHER_OPTION, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>text=19.06, state=WAITING_CUSTOM_DATE, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","option_count":1,"current_option_date":"2026-06-18T21:00:00.000Z","current_option_time":"1899-12-30T07:27:56.000Z","option1_date":"Thu Jun 18 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","option1_time":"1899-12-30T07:27:56.000Z","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"","customer_phone":""}</t>
+  </si>
+  <si>
+    <t>text=10:30, state=WAITING_OPTION_TIME, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>text=0556325487, state=WAITING_CUSTOMER_PHONE, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","option_count":2,"current_option_date":"2026-06-18T21:00:00.000Z","current_option_time":"1899-12-30T08:27:56.000Z","option1_date":"Thu Jun 18 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","option1_time":"1899-12-30T07:27:56.000Z","option2_date":"Fri Jun 19 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","option2_time":"1899-12-30T08:27:56.000Z","option3_date":"","option3_time":"","customer_name":"Аня","customer_phone":"0556325487"}</t>
+  </si>
+  <si>
+    <t>cust_1781370822092</t>
+  </si>
+  <si>
+    <t>req_1781370822889</t>
+  </si>
+  <si>
+    <t>{"id":"3118605852257923479","from":{"id":726107007,"is_bot":false,"first_name":"Serhii","username":"Serhii_Tsi","language_code":"en"},"message":{"message_id":1888,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":726107007,"first_name":"Serhii","username":"Serhii_Tsi","type":"private"},"date":1781370831,"text":"Новая заявка\n\n👤 Клиент: Аня\n📞 Телефон: 0556325487\n\n📍 Филиал: Центр\n💅 Услуга: Окрашивание\n👩‍💼 Мастер: Алиса\n\nВарианты времени:\n1) 18.06.2026 09:30\n2) 19.06.2026 10:30","entities":[{"offset":0,"length":12,"type":"bold"},{"offset":114,"length":17,"type":"bold"}],"reply_markup":{"inline_keyboard":[[{"text":"✅ 1","callback_data":"approve_option_1|req_1781370822889"},{"text":"✅ 2","callback_data":"approve_option_2|req_1781370822889"}],[{"text":"❌ Reject","callback_data":"reject_request|req_1781370822889"}]]}},"chat_instance":"-653345212733041723","data":"approve_option_2|req_1781370822889"}</t>
+  </si>
+  <si>
+    <t>{"request_id":"req_1781370822889","customer_id":"cust_1781370822092","service_id":"serv_002","provider_id":"prov_001","location_id":"loc_001","status":"pending","created_at":"2026-06-13T17:13:42.889Z"}</t>
+  </si>
+  <si>
+    <t>{"option_id":"opt_1781370823781","request_id":"req_1781370822889","preferred_date":"Fri Jun 19 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","preferred_time":"1899-12-30T08:27:56.000Z","priority":2,"status":"pending","created_at":"2026-06-13T17:13:43.625Z"}</t>
+  </si>
+  <si>
+    <t>appt_1781370852127</t>
+  </si>
+  <si>
+    <t>4d3vuvtlle027320tnsc05v7io@google.com</t>
+  </si>
+  <si>
+    <t>{"customer_id":"cust_1781370822092","telegram_id":7752853740,"name":"Аня","phone":"0556325487","language":"ru","created_at":"2026-06-13T17:13:42.091Z","updated_at":"2026-06-13T17:13:42.091Z","last_visit_at":"","status":"confirmed","notes":""}</t>
+  </si>
+  <si>
+    <t>text=Мои записи, state=, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>text=0556325487, state=WAITING_MY_APPOINTMENTS_PHONE, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>{"id":"5628137153744732991","from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"ru"},"message":{"message_id":1904,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781371465,"text":"19.06.2026 10:30\n\n💅 Окрашивание\n👩‍💼 Алиса\n📍 Центр","reply_markup":{"inline_keyboard":[[{"text":"❌ Отменить","callback_data":"cancel_appointment|appt_1781370852127"}]]}},"chat_instance":"-760725032823406943","data":"cancel_appointment|appt_1781370852127"}</t>
+  </si>
+  <si>
+    <t>{"id":"5628137157104645704","from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"ru"},"message":{"message_id":1911,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781376601,"text":"19.06.2026 10:30\n\n💅 Окрашивание\n👩‍💼 Алиса\n📍 Центр","reply_markup":{"inline_keyboard":[[{"text":"❌ Отменить","callback_data":"cancel_appointment|appt_1781370852127"}]]}},"chat_instance":"-760725032823406943","data":"cancel_appointment|appt_1781370852127"}</t>
+  </si>
+  <si>
+    <t>{"id":"5628137156106329497","from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"ru"},"message":{"message_id":1911,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781376601,"edit_date":1781376606,"text":"Вы уверены, что хотите отменить запись?","reply_markup":{"inline_keyboard":[[{"text":"✅ Да","callback_data":"confirm_cancel|appt_1781370852127"}],[{"text":"↩️ Нет","callback_data":"keep_appointment|appt_1781370852127"}]]}},"chat_instance":"-760725032823406943","data":"keep_appointment|appt_1781370852127"}</t>
+  </si>
+  <si>
+    <t>{"id":"5628137155361657039","from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"ru"},"message":{"message_id":1911,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781376601,"edit_date":1781376606,"text":"Вы уверены, что хотите отменить запись?","reply_markup":{"inline_keyboard":[[{"text":"✅ Да","callback_data":"confirm_cancel|appt_1781370852127"}],[{"text":"↩️ Нет","callback_data":"keep_appointment|appt_1781370852127"}]]}},"chat_instance":"-760725032823406943","data":"confirm_cancel|appt_1781370852127"}</t>
+  </si>
+  <si>
+    <t>text=20.06, state=WAITING_CUSTOM_DATE, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","option_count":0,"current_option_date":"2026-06-19T21:00:00.000Z","current_option_time":"","option1_date":"","option1_time":"","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"","customer_phone":""}</t>
+  </si>
+  <si>
+    <t>text=11:00, state=WAITING_OPTION_TIME, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>text=Алена, state=WAITING_CUSTOMER_NAME, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>text=0441112233, state=WAITING_CUSTOMER_PHONE, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","option_count":1,"current_option_date":"2026-06-19T21:00:00.000Z","current_option_time":"1899-12-30T08:57:56.000Z","option1_date":"Sat Jun 20 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","option1_time":"1899-12-30T08:57:56.000Z","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"Алена","customer_phone":"0441112233"}</t>
+  </si>
+  <si>
+    <t>cust_1781377329748</t>
+  </si>
+  <si>
+    <t>req_1781377331088</t>
+  </si>
+  <si>
+    <t>{"id":"3118605851243197977","from":{"id":726107007,"is_bot":false,"first_name":"Serhii","username":"Serhii_Tsi","language_code":"en"},"message":{"message_id":1937,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":726107007,"first_name":"Serhii","username":"Serhii_Tsi","type":"private"},"date":1781377339,"text":"Новая заявка\n\n👤 Клиент: Алена\n📞 Телефон: 0441112233\n\n📍 Филиал: Центр\n💅 Услуга: Окрашивание\n👩‍💼 Мастер: Алиса\n\nВарианты времени:\n1) 20.06.2026 11:00","entities":[{"offset":0,"length":12,"type":"bold"},{"offset":116,"length":17,"type":"bold"}],"reply_markup":{"inline_keyboard":[[{"text":"✅ 1","callback_data":"approve_option_1|req_1781377331088"}],[{"text":"❌ Reject","callback_data":"reject_request|req_1781377331088"}]]}},"chat_instance":"-653345212733041723","data":"approve_option_1|req_1781377331088"}</t>
+  </si>
+  <si>
+    <t>{"request_id":"req_1781377331088","customer_id":"cust_1781377329748","service_id":"serv_002","provider_id":"prov_001","location_id":"loc_001","status":"pending","created_at":"2026-06-13T19:02:11.088Z"}</t>
+  </si>
+  <si>
+    <t>{"option_id":"opt_1781377332330","request_id":"req_1781377331088","preferred_date":"Sat Jun 20 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","preferred_time":"1899-12-30T08:57:56.000Z","priority":1,"status":"pending","created_at":"2026-06-13T19:02:12.330Z"}</t>
+  </si>
+  <si>
+    <t>appt_1781377351401</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","option_count":0,"current_option_date":"2026-06-18T21:00:00.000Z","current_option_time":"","option1_date":"","option1_time":"","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"","customer_phone":""}</t>
+  </si>
+  <si>
+    <t>text=Алёна, state=WAITING_CUSTOMER_NAME, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>text=0772223311, state=WAITING_CUSTOMER_PHONE, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","option_count":1,"current_option_date":"2026-06-18T21:00:00.000Z","current_option_time":"1899-12-30T07:27:56.000Z","option1_date":"Fri Jun 19 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","option1_time":"1899-12-30T07:27:56.000Z","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"Алёна","customer_phone":"0772223311"}</t>
+  </si>
+  <si>
+    <t>cust_1781377741811</t>
+  </si>
+  <si>
+    <t>req_1781377742514</t>
+  </si>
+  <si>
+    <t>{"id":"3118605848652908087","from":{"id":726107007,"is_bot":false,"first_name":"Serhii","username":"Serhii_Tsi","language_code":"en"},"message":{"message_id":1960,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":726107007,"first_name":"Serhii","username":"Serhii_Tsi","type":"private"},"date":1781377746,"text":"Новая заявка\n\n👤 Клиент: Алёна\n📞 Телефон: 0772223311\n\n📍 Филиал: Центр\n💅 Услуга: Окрашивание\n👩‍💼 Мастер: Алиса\n\nВарианты времени:\n1) 19.06.2026 09:30","entities":[{"offset":0,"length":12,"type":"bold"},{"offset":116,"length":17,"type":"bold"}],"reply_markup":{"inline_keyboard":[[{"text":"✅ 1","callback_data":"approve_option_1|req_1781377742514"}],[{"text":"❌ Reject","callback_data":"reject_request|req_1781377742514"}]]}},"chat_instance":"-653345212733041723","data":"approve_option_1|req_1781377742514"}</t>
+  </si>
+  <si>
+    <t>{"request_id":"req_1781377742514","customer_id":"cust_1781377741811","service_id":"serv_002","provider_id":"prov_001","location_id":"loc_001","status":"pending","created_at":"2026-06-13T19:09:02.514Z"}</t>
+  </si>
+  <si>
+    <t>{"option_id":"opt_1781377743146","request_id":"req_1781377742514","preferred_date":"Fri Jun 19 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","preferred_time":"1899-12-30T07:27:56.000Z","priority":1,"status":"pending","created_at":"2026-06-13T19:09:03.146Z"}</t>
+  </si>
+  <si>
+    <t>appt_1781377760289</t>
+  </si>
+  <si>
+    <t>mr64h60rbij7eutg0d7fp3aq8o@google.com</t>
+  </si>
+  <si>
+    <t>{"customer_id":"cust_1781377741811","telegram_id":7752853740,"name":"Алёна","phone":"0772223311","language":"ru","created_at":"2026-06-13T19:09:01.811Z","updated_at":"2026-06-13T19:09:01.811Z","last_visit_at":"","status":"confirmed","notes":""}</t>
+  </si>
+  <si>
+    <t>text=0772223311, state=WAITING_MY_APPOINTMENTS_PHONE, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>{"id":"5628137156336161378","from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"ru"},"message":{"message_id":1969,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781377811,"text":"19.06.2026 09:30\n\n💅 Окрашивание\n👩‍💼 Алиса\n📍 Центр","reply_markup":{"inline_keyboard":[[{"text":"❌ Отменить","callback_data":"cancel_appointment|appt_1781377760289"}]]}},"chat_instance":"-760725032823406943","data":"cancel_appointment|appt_1781377760289"}</t>
+  </si>
+  <si>
+    <t>{"id":"5628137153863422125","from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"ru"},"message":{"message_id":1969,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781377811,"edit_date":1781377817,"text":"Вы уверены, что хотите отменить запись?","reply_markup":{"inline_keyboard":[[{"text":"✅ Да","callback_data":"confirm_cancel|appt_1781377760289"}],[{"text":"↩️ Нет","callback_data":"keep_appointment|appt_1781377760289"}]]}},"chat_instance":"-760725032823406943","data":"confirm_cancel|appt_1781377760289"}</t>
+  </si>
+  <si>
+    <t>text=12:30, state=WAITING_OPTION_TIME, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>text=вар, state=WAITING_CUSTOMER_NAME, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>text=380562356699, state=WAITING_CUSTOMER_PHONE, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","option_count":1,"current_option_date":"2026-06-18T21:00:00.000Z","current_option_time":"1899-12-30T10:27:56.000Z","option1_date":"Fri Jun 19 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","option1_time":"1899-12-30T10:27:56.000Z","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"вар","customer_phone":"380562356699"}</t>
+  </si>
+  <si>
+    <t>cust_1781378623251</t>
+  </si>
+  <si>
+    <t>req_1781378625051</t>
+  </si>
+  <si>
+    <t>{"id":"3118605850926814949","from":{"id":726107007,"is_bot":false,"first_name":"Serhii","username":"Serhii_Tsi","language_code":"en"},"message":{"message_id":1991,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":726107007,"first_name":"Serhii","username":"Serhii_Tsi","type":"private"},"date":1781378640,"text":"Новая заявка\n\n👤 Клиент: вар\n📞 Телефон: 380562356699\n\n📍 Филиал: Центр\n💅 Услуга: Окрашивание\n👩‍💼 Мастер: Алиса\n\nВарианты времени:\n1) 19.06.2026 12:30","entities":[{"offset":0,"length":12,"type":"bold"},{"offset":116,"length":17,"type":"bold"}],"reply_markup":{"inline_keyboard":[[{"text":"✅ 1","callback_data":"approve_option_1|req_1781378625051"}],[{"text":"❌ Reject","callback_data":"reject_request|req_1781378625051"}]]}},"chat_instance":"-653345212733041723","data":"approve_option_1|req_1781378625051"}</t>
+  </si>
+  <si>
+    <t>{"request_id":"req_1781378625051","customer_id":"cust_1781378623251","service_id":"serv_002","provider_id":"prov_001","location_id":"loc_001","status":"pending","created_at":"2026-06-13T19:23:45.051Z"}</t>
+  </si>
+  <si>
+    <t>{"option_id":"opt_1781378626046","request_id":"req_1781378625051","preferred_date":"Fri Jun 19 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","preferred_time":"1899-12-30T10:27:56.000Z","priority":1,"status":"pending","created_at":"2026-06-13T19:23:46.046Z"}</t>
+  </si>
+  <si>
+    <t>appt_1781378648318</t>
+  </si>
+  <si>
+    <t>ta0034ss8sc80oqsh9o035mpmo@google.com</t>
+  </si>
+  <si>
+    <t>{"customer_id":"cust_1781378623251","telegram_id":7752853740,"name":"вар","phone":"380562356699","language":"ru","created_at":"2026-06-13T19:23:43.250Z","updated_at":"2026-06-13T19:23:43.250Z","last_visit_at":"","status":"confirmed","notes":""}</t>
+  </si>
+  <si>
+    <t>text=380562356699, state=WAITING_MY_APPOINTMENTS_PHONE, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>{"id":"5628137156268251229","from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"ru"},"message":{"message_id":2000,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781378753,"text":"19.06.2026 12:30\n\n💅 Окрашивание\n👩‍💼 Алиса\n📍 Центр","reply_markup":{"inline_keyboard":[[{"text":"❌ Отменить","callback_data":"cancel_appointment|appt_1781378648318"}]]}},"chat_instance":"-760725032823406943","data":"cancel_appointment|appt_1781378648318"}</t>
+  </si>
+  <si>
+    <t>{"id":"5628137157420985125","from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"ru"},"message":{"message_id":2000,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781378753,"edit_date":1781378758,"text":"Вы уверены, что хотите отменить запись?","reply_markup":{"inline_keyboard":[[{"text":"✅ Да","callback_data":"confirm_cancel|appt_1781378648318"}],[{"text":"↩️ Нет","callback_data":"keep_appointment|appt_1781378648318"}]]}},"chat_instance":"-760725032823406943","data":"keep_appointment|appt_1781378648318"}</t>
+  </si>
+  <si>
+    <t>{"id":"5628137157683174389","from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"ru"},"message":{"message_id":2001,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781378767,"text":"19.06.2026 12:30\n\n💅 Окрашивание\n👩‍💼 Алиса\n📍 Центр","reply_markup":{"inline_keyboard":[[{"text":"❌ Отменить","callback_data":"cancel_appointment|appt_1781378648318"}]]}},"chat_instance":"-760725032823406943","data":"cancel_appointment|appt_1781378648318"}</t>
+  </si>
+  <si>
+    <t>{"id":"5628137155184974120","from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"ru"},"message":{"message_id":2001,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781378767,"edit_date":1781378773,"text":"Вы уверены, что хотите отменить запись?","reply_markup":{"inline_keyboard":[[{"text":"✅ Да","callback_data":"confirm_cancel|appt_1781378648318"}],[{"text":"↩️ Нет","callback_data":"keep_appointment|appt_1781378648318"}]]}},"chat_instance":"-760725032823406943","data":"confirm_cancel|appt_1781378648318"}</t>
+  </si>
+  <si>
+    <t>text=15:00, state=WAITING_OPTION_TIME, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>text=вап, state=WAITING_CUSTOMER_NAME, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>text=0552635478, state=WAITING_CUSTOMER_PHONE, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","option_count":1,"current_option_date":"2026-06-18T21:00:00.000Z","current_option_time":"1899-12-30T12:57:56.000Z","option1_date":"Fri Jun 19 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","option1_time":"1899-12-30T12:57:56.000Z","option2_date":"","option2_time":"","option3_date":"","option3_time":"","customer_name":"вап","customer_phone":"0552635478"}</t>
+  </si>
+  <si>
+    <t>cust_1781379287010</t>
+  </si>
+  <si>
+    <t>req_1781379287838</t>
+  </si>
+  <si>
+    <t>{"id":"3118605848923719495","from":{"id":726107007,"is_bot":false,"first_name":"Serhii","username":"Serhii_Tsi","language_code":"en"},"message":{"message_id":2023,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":726107007,"first_name":"Serhii","username":"Serhii_Tsi","type":"private"},"date":1781379295,"text":"Новая заявка\n\n👤 Клиент: вап\n📞 Телефон: 0552635478\n\n📍 Филиал: Центр\n💅 Услуга: Окрашивание\n👩‍💼 Мастер: Алиса\n\nВарианты времени:\n1) 19.06.2026 15:00","entities":[{"offset":0,"length":12,"type":"bold"},{"offset":114,"length":17,"type":"bold"}],"reply_markup":{"inline_keyboard":[[{"text":"✅ 1","callback_data":"approve_option_1|req_1781379287838"}],[{"text":"❌ Reject","callback_data":"reject_request|req_1781379287838"}]]}},"chat_instance":"-653345212733041723","data":"approve_option_1|req_1781379287838"}</t>
+  </si>
+  <si>
+    <t>{"request_id":"req_1781379287838","customer_id":"cust_1781379287010","service_id":"serv_002","provider_id":"prov_001","location_id":"loc_001","status":"pending","created_at":"2026-06-13T19:34:47.838Z"}</t>
+  </si>
+  <si>
+    <t>{"option_id":"opt_1781379289023","request_id":"req_1781379287838","preferred_date":"Fri Jun 19 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","preferred_time":"1899-12-30T12:57:56.000Z","priority":1,"status":"pending","created_at":"2026-06-13T19:34:49.023Z"}</t>
+  </si>
+  <si>
+    <t>appt_1781379304671</t>
+  </si>
+  <si>
+    <t>c5rfphj9mk62ribb8ve74hksmo@google.com</t>
+  </si>
+  <si>
+    <t>{"customer_id":"cust_1781379287010","telegram_id":7752853740,"name":"вап","phone":"0552635478","language":"ru","created_at":"2026-06-13T19:34:47.009Z","updated_at":"2026-06-13T19:34:47.009Z","last_visit_at":"","status":"confirmed","notes":""}</t>
+  </si>
+  <si>
+    <t>text=0552635478, state=WAITING_MY_APPOINTMENTS_PHONE, chatId=7752853740</t>
+  </si>
+  <si>
+    <t>{"id":"5628137155645874229","from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"ru"},"message":{"message_id":2032,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781379372,"text":"19.06.2026 15:00\n\n💅 Окрашивание\n👩‍💼 Алиса\n📍 Центр","reply_markup":{"inline_keyboard":[[{"text":"❌ Отменить","callback_data":"cancel_appointment|appt_1781379304671"}]]}},"chat_instance":"-760725032823406943","data":"cancel_appointment|appt_1781379304671"}</t>
+  </si>
+  <si>
+    <t>{"id":"5628137153437313950","from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"ru"},"message":{"message_id":2032,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781379372,"edit_date":1781379378,"text":"Вы уверены, что хотите отменить запись?","reply_markup":{"inline_keyboard":[[{"text":"✅ Да","callback_data":"confirm_cancel|appt_1781379304671"}],[{"text":"↩️ Нет","callback_data":"keep_appointment|appt_1781379304671"}]]}},"chat_instance":"-760725032823406943","data":"confirm_cancel|appt_1781379304671"}</t>
+  </si>
+  <si>
     <t>location_id</t>
   </si>
   <si>
@@ -1006,6 +1258,33 @@
     <t>opt_1781369670032</t>
   </si>
   <si>
+    <t>opt_1781370823625</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)</t>
+  </si>
+  <si>
+    <t>opt_1781370823781</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)</t>
+  </si>
+  <si>
+    <t>opt_1781377332330</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)</t>
+  </si>
+  <si>
+    <t>opt_1781377743146</t>
+  </si>
+  <si>
+    <t>opt_1781378626046</t>
+  </si>
+  <si>
+    <t>opt_1781379289023</t>
+  </si>
+  <si>
     <t>prov_002</t>
   </si>
   <si>
@@ -1834,6 +2113,30 @@
     <t>You have no active appointments. Please check the phone number and try again.</t>
   </si>
   <si>
+    <t>APPOINTMENT_CANCELLED</t>
+  </si>
+  <si>
+    <t>Запис скасовано</t>
+  </si>
+  <si>
+    <t>Запись отменена</t>
+  </si>
+  <si>
+    <t>Appointment cancelled</t>
+  </si>
+  <si>
+    <t>OWNER_APPOINTMENT_CANCELLED</t>
+  </si>
+  <si>
+    <t>Клієнт скасував запис</t>
+  </si>
+  <si>
+    <t>Клиент отменил запись</t>
+  </si>
+  <si>
+    <t>Client cancelled appointment</t>
+  </si>
+  <si>
     <t>address</t>
   </si>
   <si>
@@ -1942,6 +2245,33 @@
     <t>0442536598</t>
   </si>
   <si>
+    <t>0556325487</t>
+  </si>
+  <si>
+    <t>Алена</t>
+  </si>
+  <si>
+    <t>0441112233</t>
+  </si>
+  <si>
+    <t>Алёна</t>
+  </si>
+  <si>
+    <t>0772223311</t>
+  </si>
+  <si>
+    <t>вар</t>
+  </si>
+  <si>
+    <t>380562356699</t>
+  </si>
+  <si>
+    <t>вап</t>
+  </si>
+  <si>
+    <t>0552635478</t>
+  </si>
+  <si>
     <t>start_at</t>
   </si>
   <si>
@@ -1979,6 +2309,9 @@
   </si>
   <si>
     <t>7cs2310d57srgasekcvbfpbk14@google.com</t>
+  </si>
+  <si>
+    <t>cancelled</t>
   </si>
 </sst>
 </file>
@@ -2561,36 +2894,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>230</v>
+        <v>314</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>323</v>
+        <v>416</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>326</v>
+        <v>419</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>233</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="16" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>327</v>
+        <v>420</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>328</v>
+        <v>421</v>
       </c>
       <c r="D2" s="11">
         <v>0.2916666666666667</v>
@@ -2604,13 +2937,13 @@
     </row>
     <row r="3">
       <c r="A3" s="16" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>327</v>
+        <v>420</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>329</v>
+        <v>422</v>
       </c>
       <c r="D3" s="11">
         <v>0.2916666666666667</v>
@@ -2624,13 +2957,13 @@
     </row>
     <row r="4">
       <c r="A4" s="16" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>327</v>
+        <v>420</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>330</v>
+        <v>423</v>
       </c>
       <c r="D4" s="11">
         <v>0.2916666666666667</v>
@@ -2644,13 +2977,13 @@
     </row>
     <row r="5">
       <c r="A5" s="16" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>327</v>
+        <v>420</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>331</v>
+        <v>424</v>
       </c>
       <c r="D5" s="11">
         <v>0.2916666666666667</v>
@@ -2664,13 +2997,13 @@
     </row>
     <row r="6">
       <c r="A6" s="16" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>327</v>
+        <v>420</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>332</v>
+        <v>425</v>
       </c>
       <c r="D6" s="11">
         <v>0.2916666666666667</v>
@@ -2684,13 +3017,13 @@
     </row>
     <row r="7">
       <c r="A7" s="16" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>327</v>
+        <v>420</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>333</v>
+        <v>426</v>
       </c>
       <c r="D7" s="11">
         <v>0.375</v>
@@ -2704,19 +3037,19 @@
     </row>
     <row r="8">
       <c r="A8" s="16" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>327</v>
+        <v>420</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>334</v>
+        <v>427</v>
       </c>
       <c r="F8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>335</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -2729,13 +3062,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>328</v>
+        <v>421</v>
       </c>
       <c r="D10" s="11">
         <v>0.2916666666666667</v>
@@ -2749,13 +3082,13 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>329</v>
+        <v>422</v>
       </c>
       <c r="D11" s="11">
         <v>0.2916666666666667</v>
@@ -2769,13 +3102,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>330</v>
+        <v>423</v>
       </c>
       <c r="D12" s="11">
         <v>0.2916666666666667</v>
@@ -2789,13 +3122,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>331</v>
+        <v>424</v>
       </c>
       <c r="D13" s="11">
         <v>0.2916666666666667</v>
@@ -2809,13 +3142,13 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>332</v>
+        <v>425</v>
       </c>
       <c r="D14" s="11">
         <v>0.2916666666666667</v>
@@ -2829,13 +3162,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>333</v>
+        <v>426</v>
       </c>
       <c r="D15" s="11">
         <v>0.375</v>
@@ -2849,19 +3182,19 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>334</v>
+        <v>427</v>
       </c>
       <c r="F16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>335</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -2878,33 +3211,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>230</v>
+        <v>314</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>337</v>
+        <v>430</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>326</v>
+        <v>419</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>233</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="C2" s="10">
         <v>46187.0</v>
@@ -2913,15 +3246,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>335</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="C3" s="10">
         <v>46189.0</v>
@@ -2936,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>338</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -2957,33 +3290,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>339</v>
+        <v>432</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>340</v>
+        <v>433</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>342</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>343</v>
+        <v>436</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>344</v>
+        <v>437</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>328</v>
+        <v>421</v>
       </c>
       <c r="G2" s="11">
         <v>0.2916666666666667</v>
@@ -2997,19 +3330,19 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>345</v>
+        <v>438</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>346</v>
+        <v>439</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>329</v>
+        <v>422</v>
       </c>
       <c r="G3" s="11">
         <v>0.2916666666666667</v>
@@ -3023,19 +3356,19 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>347</v>
+        <v>440</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>348</v>
+        <v>441</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>330</v>
+        <v>423</v>
       </c>
       <c r="G4" s="11">
         <v>0.2916666666666667</v>
@@ -3049,13 +3382,13 @@
     </row>
     <row r="5">
       <c r="D5" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>331</v>
+        <v>424</v>
       </c>
       <c r="G5" s="11">
         <v>0.2916666666666667</v>
@@ -3069,13 +3402,13 @@
     </row>
     <row r="6">
       <c r="D6" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>332</v>
+        <v>425</v>
       </c>
       <c r="G6" s="11">
         <v>0.2916666666666667</v>
@@ -3089,13 +3422,13 @@
     </row>
     <row r="7">
       <c r="D7" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>333</v>
+        <v>426</v>
       </c>
       <c r="G7" s="11">
         <v>0.375</v>
@@ -3109,35 +3442,35 @@
     </row>
     <row r="8">
       <c r="D8" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>334</v>
+        <v>427</v>
       </c>
       <c r="I8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>335</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10">
       <c r="D10" s="22" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>349</v>
+        <v>442</v>
       </c>
     </row>
     <row r="12">
       <c r="D12" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="F12" s="10">
         <v>46188.0</v>
@@ -3146,15 +3479,15 @@
         <v>0</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>335</v>
+        <v>428</v>
       </c>
     </row>
     <row r="13">
       <c r="D13" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="F13" s="10">
         <v>46189.0</v>
@@ -3169,7 +3502,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>338</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -3189,55 +3522,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>200</v>
+        <v>284</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>214</v>
+        <v>298</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>215</v>
+        <v>299</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>216</v>
+        <v>300</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>228</v>
+        <v>312</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>350</v>
+        <v>443</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>219</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="16" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>118</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>351</v>
+        <v>444</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>352</v>
+        <v>445</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>353</v>
+        <v>446</v>
       </c>
       <c r="F2" s="19">
         <f>+380111111111</f>
         <v>380111111111</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>354</v>
+        <v>447</v>
       </c>
       <c r="I2" s="14" t="b">
         <v>1</v>
@@ -3245,26 +3578,26 @@
     </row>
     <row r="3">
       <c r="A3" s="16" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>118</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>355</v>
+        <v>448</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>355</v>
+        <v>448</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>356</v>
+        <v>449</v>
       </c>
       <c r="F3" s="19">
         <f>+380111111113</f>
         <v>380111111113</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>354</v>
+        <v>447</v>
       </c>
       <c r="I3" s="14" t="b">
         <v>1</v>
@@ -3284,19 +3617,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="s">
-        <v>357</v>
+        <v>450</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>358</v>
+        <v>451</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>359</v>
+        <v>452</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>360</v>
+        <v>453</v>
       </c>
       <c r="F1" s="20" t="s">
         <v>2</v>
@@ -3304,10 +3637,10 @@
     </row>
     <row r="2">
       <c r="A2" s="16" t="s">
-        <v>361</v>
+        <v>454</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="C2" s="23">
         <v>46204.0</v>
@@ -3316,18 +3649,18 @@
         <v>46210.0</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>362</v>
+        <v>455</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>363</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="s">
-        <v>364</v>
+        <v>457</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>322</v>
+        <v>415</v>
       </c>
       <c r="C3" s="23">
         <v>46188.0</v>
@@ -3336,10 +3669,10 @@
         <v>46188.0</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>365</v>
+        <v>458</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>366</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -3356,58 +3689,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="s">
-        <v>367</v>
+        <v>460</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>368</v>
+        <v>461</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>360</v>
+        <v>453</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>369</v>
+        <v>462</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>370</v>
+        <v>463</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>235</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="16" t="s">
-        <v>371</v>
+        <v>464</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>372</v>
+        <v>465</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>373</v>
+        <v>466</v>
       </c>
       <c r="D2" s="24">
         <v>46187.583333333336</v>
       </c>
       <c r="E2" s="16"/>
       <c r="F2" s="16" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="s">
-        <v>374</v>
+        <v>467</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>372</v>
+        <v>465</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>375</v>
+        <v>468</v>
       </c>
       <c r="D3" s="24">
         <v>46188.5</v>
       </c>
       <c r="E3" s="16"/>
       <c r="F3" s="16" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -3433,797 +3766,825 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>469</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>377</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>378</v>
+        <v>471</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>379</v>
+        <v>472</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>380</v>
+        <v>473</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>381</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>382</v>
+        <v>475</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>383</v>
+        <v>476</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>384</v>
+        <v>477</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>385</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>386</v>
+        <v>479</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>387</v>
+        <v>480</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>388</v>
+        <v>481</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>389</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>390</v>
+        <v>483</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>391</v>
+        <v>484</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>392</v>
+        <v>485</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>393</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>394</v>
+        <v>487</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>396</v>
+        <v>489</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>397</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>398</v>
+        <v>491</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>399</v>
+        <v>492</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>400</v>
+        <v>493</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>401</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>402</v>
+        <v>495</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>403</v>
+        <v>496</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>404</v>
+        <v>497</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>405</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>406</v>
+        <v>499</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>407</v>
+        <v>500</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>409</v>
+        <v>502</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>410</v>
+        <v>503</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>411</v>
+        <v>504</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>412</v>
+        <v>505</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>413</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>414</v>
+        <v>507</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>415</v>
+        <v>508</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>416</v>
+        <v>509</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>417</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>418</v>
+        <v>511</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>419</v>
+        <v>512</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>420</v>
+        <v>513</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>421</v>
+        <v>514</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>422</v>
+        <v>515</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>423</v>
+        <v>516</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>424</v>
+        <v>517</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>425</v>
+        <v>518</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>426</v>
+        <v>519</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>427</v>
+        <v>520</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>428</v>
+        <v>521</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>429</v>
+        <v>522</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>430</v>
+        <v>523</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>431</v>
+        <v>524</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>432</v>
+        <v>525</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>433</v>
+        <v>526</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>434</v>
+        <v>527</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>435</v>
+        <v>528</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>436</v>
+        <v>529</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>437</v>
+        <v>530</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>438</v>
+        <v>531</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>439</v>
+        <v>532</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>439</v>
+        <v>532</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>441</v>
+        <v>534</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>442</v>
+        <v>535</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>444</v>
+        <v>537</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>445</v>
+        <v>538</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>446</v>
+        <v>539</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>447</v>
+        <v>540</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>448</v>
+        <v>541</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>450</v>
+        <v>543</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>451</v>
+        <v>544</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>452</v>
+        <v>545</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>453</v>
+        <v>546</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>454</v>
+        <v>547</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>455</v>
+        <v>548</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>456</v>
+        <v>549</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>457</v>
+        <v>550</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>458</v>
+        <v>551</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>459</v>
+        <v>552</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>460</v>
+        <v>553</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>461</v>
+        <v>554</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>462</v>
+        <v>555</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>462</v>
+        <v>555</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>463</v>
+        <v>556</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>464</v>
+        <v>557</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>465</v>
+        <v>558</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>466</v>
+        <v>559</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>467</v>
+        <v>560</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>468</v>
+        <v>561</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>469</v>
+        <v>562</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>470</v>
+        <v>563</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>471</v>
+        <v>564</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>472</v>
+        <v>565</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>473</v>
+        <v>566</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>474</v>
+        <v>567</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>475</v>
+        <v>568</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>476</v>
+        <v>569</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>477</v>
+        <v>570</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>478</v>
+        <v>571</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>479</v>
+        <v>572</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>480</v>
+        <v>573</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>481</v>
+        <v>574</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>482</v>
+        <v>575</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>483</v>
+        <v>576</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>484</v>
+        <v>577</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>485</v>
+        <v>578</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>486</v>
+        <v>579</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>487</v>
+        <v>580</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>488</v>
+        <v>581</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>489</v>
+        <v>582</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>490</v>
+        <v>583</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>491</v>
+        <v>584</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>492</v>
+        <v>585</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>493</v>
+        <v>586</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>494</v>
+        <v>587</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>495</v>
+        <v>588</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>496</v>
+        <v>589</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>497</v>
+        <v>590</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>498</v>
+        <v>591</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>499</v>
+        <v>592</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>500</v>
+        <v>593</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>501</v>
+        <v>594</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>502</v>
+        <v>595</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>503</v>
+        <v>596</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>504</v>
+        <v>597</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>505</v>
+        <v>598</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>506</v>
+        <v>599</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>507</v>
+        <v>600</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>508</v>
+        <v>601</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>509</v>
+        <v>602</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>509</v>
+        <v>602</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>510</v>
+        <v>603</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>511</v>
+        <v>604</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>512</v>
+        <v>605</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>513</v>
+        <v>606</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>514</v>
+        <v>607</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>515</v>
+        <v>608</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>516</v>
+        <v>609</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>516</v>
+        <v>609</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>517</v>
+        <v>610</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>518</v>
+        <v>611</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>519</v>
+        <v>612</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>520</v>
+        <v>613</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>521</v>
+        <v>614</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>522</v>
+        <v>615</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>523</v>
+        <v>616</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>524</v>
+        <v>617</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>525</v>
+        <v>618</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>526</v>
+        <v>619</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>527</v>
+        <v>620</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>528</v>
+        <v>621</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>529</v>
+        <v>622</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>530</v>
+        <v>623</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>531</v>
+        <v>624</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>532</v>
+        <v>625</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>533</v>
+        <v>626</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>534</v>
+        <v>627</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>535</v>
+        <v>628</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>536</v>
+        <v>629</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>537</v>
+        <v>630</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>538</v>
+        <v>631</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>539</v>
+        <v>632</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>540</v>
+        <v>633</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>541</v>
+        <v>634</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>542</v>
+        <v>635</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>543</v>
+        <v>636</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>544</v>
+        <v>637</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>545</v>
+        <v>638</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>546</v>
+        <v>639</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>547</v>
+        <v>640</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>548</v>
+        <v>641</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>549</v>
+        <v>642</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>550</v>
+        <v>643</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>551</v>
+        <v>644</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>552</v>
+        <v>645</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>553</v>
+        <v>646</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>554</v>
+        <v>647</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>555</v>
+        <v>648</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>556</v>
+        <v>649</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>557</v>
+        <v>650</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>558</v>
+        <v>651</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>559</v>
+        <v>652</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>560</v>
+        <v>653</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>561</v>
+        <v>654</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>562</v>
+        <v>655</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>563</v>
+        <v>656</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>564</v>
+        <v>657</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>565</v>
+        <v>658</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>566</v>
+        <v>659</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>567</v>
+        <v>660</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>568</v>
+        <v>661</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>569</v>
+        <v>662</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>570</v>
+        <v>663</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>571</v>
+        <v>664</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>572</v>
+        <v>665</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>573</v>
+        <v>666</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>574</v>
+        <v>667</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>575</v>
+        <v>668</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>576</v>
+        <v>669</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>577</v>
+        <v>670</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>578</v>
+        <v>671</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>579</v>
+        <v>672</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>580</v>
+        <v>673</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>581</v>
+        <v>674</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>582</v>
+        <v>675</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>583</v>
+        <v>676</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>584</v>
+        <v>677</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>585</v>
+        <v>678</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>586</v>
+        <v>679</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>587</v>
+        <v>680</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>588</v>
+        <v>681</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>589</v>
+        <v>682</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>590</v>
+        <v>683</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>591</v>
+        <v>684</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>592</v>
+        <v>685</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>593</v>
+        <v>686</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>594</v>
+        <v>687</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>595</v>
+        <v>688</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>596</v>
+        <v>689</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>597</v>
+        <v>690</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>698</v>
       </c>
     </row>
   </sheetData>
@@ -4243,25 +4604,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="s">
-        <v>200</v>
+        <v>284</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>214</v>
+        <v>298</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>215</v>
+        <v>299</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>216</v>
+        <v>300</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>598</v>
+        <v>699</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>228</v>
+        <v>312</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>219</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2">
@@ -4269,16 +4630,16 @@
         <v>118</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>599</v>
+        <v>700</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>599</v>
+        <v>700</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>600</v>
+        <v>701</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>601</v>
+        <v>702</v>
       </c>
       <c r="F2" s="7">
         <f>+380000000001</f>
@@ -4303,52 +4664,52 @@
     <col customWidth="1" min="1" max="1" width="18.13"/>
     <col customWidth="1" min="3" max="3" width="14.63"/>
     <col customWidth="1" min="4" max="4" width="13.38"/>
-    <col customWidth="1" min="6" max="6" width="16.38"/>
+    <col customWidth="1" min="6" max="6" width="17.75"/>
     <col customWidth="1" min="7" max="7" width="19.25"/>
     <col customWidth="1" min="8" max="8" width="13.38"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>227</v>
+        <v>311</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>602</v>
+        <v>703</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>228</v>
+        <v>312</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>603</v>
+        <v>704</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>236</v>
+        <v>320</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>604</v>
+        <v>705</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>235</v>
+        <v>319</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>233</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>605</v>
+        <v>706</v>
       </c>
       <c r="B2" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>606</v>
+        <v>707</v>
       </c>
       <c r="D2" s="13">
         <v>3804562658652</v>
@@ -4363,18 +4724,18 @@
         <v>46185.90711637732</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>607</v>
+        <v>708</v>
       </c>
       <c r="B3" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>608</v>
+        <v>709</v>
       </c>
       <c r="D3" s="13">
         <v>38052425635966</v>
@@ -4389,18 +4750,18 @@
         <v>46185.90912765046</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>238</v>
+        <v>322</v>
       </c>
       <c r="B4" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>355</v>
+        <v>448</v>
       </c>
       <c r="D4" s="13">
         <v>3804452125648</v>
@@ -4415,18 +4776,18 @@
         <v>46185.93864143519</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>242</v>
+        <v>326</v>
       </c>
       <c r="B5" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>610</v>
+        <v>711</v>
       </c>
       <c r="D5" s="13">
         <v>38045245268</v>
@@ -4441,18 +4802,18 @@
         <v>46185.943211805556</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>245</v>
+        <v>329</v>
       </c>
       <c r="B6" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>327</v>
+        <v>420</v>
       </c>
       <c r="D6" s="13">
         <v>3502452635165</v>
@@ -4467,18 +4828,18 @@
         <v>46185.947925671295</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>246</v>
+        <v>330</v>
       </c>
       <c r="B7" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>327</v>
+        <v>420</v>
       </c>
       <c r="D7" s="13">
         <v>38055245256685</v>
@@ -4493,18 +4854,18 @@
         <v>46185.95117884259</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>249</v>
+        <v>333</v>
       </c>
       <c r="B8" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>611</v>
+        <v>712</v>
       </c>
       <c r="D8" s="13">
         <v>3805542545878</v>
@@ -4519,18 +4880,18 @@
         <v>46186.288021562505</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>251</v>
+        <v>335</v>
       </c>
       <c r="B9" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>612</v>
+        <v>713</v>
       </c>
       <c r="D9" s="13">
         <v>380452452568</v>
@@ -4545,18 +4906,18 @@
         <v>46186.3794858912</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>254</v>
+        <v>338</v>
       </c>
       <c r="B10" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>611</v>
+        <v>712</v>
       </c>
       <c r="D10" s="13">
         <v>380542452357</v>
@@ -4571,21 +4932,21 @@
         <v>46186.412391157406</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>256</v>
+        <v>340</v>
       </c>
       <c r="B11" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>606</v>
+        <v>707</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>613</v>
+        <v>714</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -4597,21 +4958,21 @@
         <v>46186.417582256945</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>258</v>
+        <v>342</v>
       </c>
       <c r="B12" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>611</v>
+        <v>712</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>614</v>
+        <v>715</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -4623,21 +4984,21 @@
         <v>46186.43227394676</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>260</v>
+        <v>344</v>
       </c>
       <c r="B13" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>615</v>
+        <v>716</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>616</v>
+        <v>717</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -4649,18 +5010,18 @@
         <v>46186.433847465276</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>262</v>
+        <v>346</v>
       </c>
       <c r="B14" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>611</v>
+        <v>712</v>
       </c>
       <c r="D14" s="13">
         <v>3524587568</v>
@@ -4675,18 +5036,18 @@
         <v>46186.46530578704</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>264</v>
+        <v>348</v>
       </c>
       <c r="B15" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>611</v>
+        <v>712</v>
       </c>
       <c r="D15" s="13">
         <v>380664452124</v>
@@ -4701,21 +5062,21 @@
         <v>46186.51335193287</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>266</v>
+        <v>350</v>
       </c>
       <c r="B16" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>617</v>
+        <v>718</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>618</v>
+        <v>719</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -4727,18 +5088,18 @@
         <v>46186.6387830787</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>268</v>
+        <v>352</v>
       </c>
       <c r="B17" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>619</v>
+        <v>720</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="2" t="s">
@@ -4751,18 +5112,18 @@
         <v>46186.64895253472</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>270</v>
+        <v>354</v>
       </c>
       <c r="B18" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>620</v>
+        <v>721</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="2" t="s">
@@ -4775,18 +5136,18 @@
         <v>46186.65146695602</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>272</v>
+        <v>356</v>
       </c>
       <c r="B19" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>606</v>
+        <v>707</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="2" t="s">
@@ -4799,18 +5160,18 @@
         <v>46186.653875601856</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>621</v>
+        <v>722</v>
       </c>
       <c r="B20" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>482</v>
+        <v>575</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="2" t="s">
@@ -4823,18 +5184,18 @@
         <v>46186.66598475694</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>276</v>
+        <v>360</v>
       </c>
       <c r="B21" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>482</v>
+        <v>575</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="2" t="s">
@@ -4847,18 +5208,18 @@
         <v>46186.753397002314</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>622</v>
+        <v>723</v>
       </c>
       <c r="B22" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>611</v>
+        <v>712</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="2" t="s">
@@ -4871,18 +5232,18 @@
         <v>46186.7895603588</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>623</v>
+        <v>724</v>
       </c>
       <c r="B23" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>327</v>
+        <v>420</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="2" t="s">
@@ -4895,18 +5256,18 @@
         <v>46186.794753912036</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>624</v>
+        <v>725</v>
       </c>
       <c r="B24" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>625</v>
+        <v>726</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="2" t="s">
@@ -4919,18 +5280,18 @@
         <v>46186.79852614584</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>626</v>
+        <v>727</v>
       </c>
       <c r="B25" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>627</v>
+        <v>728</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="2" t="s">
@@ -4943,18 +5304,18 @@
         <v>46186.80252622685</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>628</v>
+        <v>729</v>
       </c>
       <c r="B26" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>629</v>
+        <v>730</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="2" t="s">
@@ -4967,7 +5328,7 @@
         <v>46186.806059780094</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="27">
@@ -4978,10 +5339,10 @@
         <v>7.75285374E9</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>629</v>
+        <v>730</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>630</v>
+        <v>731</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -4993,7 +5354,7 @@
         <v>46186.81029096065</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="28">
@@ -5004,10 +5365,10 @@
         <v>7.75285374E9</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>482</v>
+        <v>575</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>631</v>
+        <v>732</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -5019,7 +5380,7 @@
         <v>46186.8185825463</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="29">
@@ -5030,10 +5391,10 @@
         <v>7.75285374E9</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>629</v>
+        <v>730</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>632</v>
+        <v>733</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -5045,7 +5406,7 @@
         <v>46186.82353692129</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
     </row>
     <row r="30">
@@ -5056,10 +5417,10 @@
         <v>7.75285374E9</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>606</v>
+        <v>707</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>633</v>
+        <v>734</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -5071,23 +5432,138 @@
         <v>46186.829497997685</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
     </row>
     <row r="31">
-      <c r="D31" s="13"/>
+      <c r="A31" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B31" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>735</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="6">
+        <v>46186.84284827547</v>
+      </c>
+      <c r="G31" s="6">
+        <v>46186.84284827547</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="32">
-      <c r="D32" s="13"/>
+      <c r="A32" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B32" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>737</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" s="6">
+        <v>46186.918168379634</v>
+      </c>
+      <c r="G32" s="6">
+        <v>46186.918168379634</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>710</v>
+      </c>
     </row>
     <row r="33">
-      <c r="D33" s="13"/>
+      <c r="A33" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B33" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>739</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="6">
+        <v>46186.922937627314</v>
+      </c>
+      <c r="G33" s="6">
+        <v>46186.922937627314</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="34">
-      <c r="D34" s="13"/>
+      <c r="A34" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B34" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>741</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="6">
+        <v>46186.9331394676</v>
+      </c>
+      <c r="G34" s="6">
+        <v>46186.9331394676</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="35">
-      <c r="D35" s="13"/>
+      <c r="A35" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B35" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>743</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="6">
+        <v>46186.94082186343</v>
+      </c>
+      <c r="G35" s="6">
+        <v>46186.94082186343</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="36">
       <c r="D36" s="13"/>
@@ -7991,37 +8467,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="s">
-        <v>368</v>
+        <v>461</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>234</v>
+        <v>318</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>227</v>
+        <v>311</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>201</v>
+        <v>285</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>200</v>
+        <v>284</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>634</v>
+        <v>744</v>
       </c>
       <c r="H1" s="25" t="s">
-        <v>635</v>
+        <v>745</v>
       </c>
       <c r="I1" s="25" t="s">
-        <v>235</v>
+        <v>319</v>
       </c>
       <c r="J1" s="25" t="s">
-        <v>636</v>
+        <v>746</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>236</v>
+        <v>320</v>
       </c>
       <c r="L1" s="22" t="s">
         <v>30</v>
@@ -8029,19 +8505,19 @@
     </row>
     <row r="2">
       <c r="A2" s="17" t="s">
-        <v>637</v>
+        <v>747</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>257</v>
+        <v>341</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>258</v>
+        <v>342</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="F2" s="17" t="s">
         <v>118</v>
@@ -8053,7 +8529,7 @@
         <v>46188.5625</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="J2" s="16"/>
       <c r="K2" s="6">
@@ -8065,19 +8541,19 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>638</v>
+        <v>748</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>259</v>
+        <v>343</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>260</v>
+        <v>344</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>118</v>
@@ -8089,7 +8565,7 @@
         <v>46188.708333333336</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="K3" s="6">
         <v>46186.43447028935</v>
@@ -8100,19 +8576,19 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>639</v>
+        <v>749</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>261</v>
+        <v>345</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>262</v>
+        <v>346</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>118</v>
@@ -8124,10 +8600,10 @@
         <v>46186.708333333336</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>640</v>
+        <v>750</v>
       </c>
       <c r="K4" s="6">
         <v>46186.465542743055</v>
@@ -8138,19 +8614,19 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>641</v>
+        <v>751</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>263</v>
+        <v>347</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>264</v>
+        <v>348</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>118</v>
@@ -8162,10 +8638,10 @@
         <v>46188.4375</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>642</v>
+        <v>752</v>
       </c>
       <c r="K5" s="6">
         <v>46186.513734479166</v>
@@ -8176,19 +8652,19 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>643</v>
+        <v>753</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>265</v>
+        <v>349</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>266</v>
+        <v>350</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>118</v>
@@ -8200,10 +8676,10 @@
         <v>46188.458333333336</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>644</v>
+        <v>754</v>
       </c>
       <c r="K6" s="6">
         <v>46186.639005150464</v>
@@ -8214,19 +8690,19 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>645</v>
+        <v>755</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>271</v>
+        <v>355</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>272</v>
+        <v>356</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>118</v>
@@ -8238,10 +8714,10 @@
         <v>46191.520833333336</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>646</v>
+        <v>756</v>
       </c>
       <c r="K7" s="6">
         <v>46186.65416020833</v>
@@ -8261,10 +8737,10 @@
         <v>169</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>118</v>
@@ -8276,7 +8752,7 @@
         <v>46188.729166666664</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>177</v>
@@ -8299,10 +8775,10 @@
         <v>192</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>118</v>
@@ -8314,7 +8790,7 @@
         <v>46188.833333333336</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>198</v>
@@ -8324,6 +8800,193 @@
       </c>
       <c r="L9" s="6">
         <v>46186.829758946755</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="27">
+        <v>46192.4375</v>
+      </c>
+      <c r="H10" s="27">
+        <v>46192.5625</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="K10" s="6">
+        <v>46186.84319591435</v>
+      </c>
+      <c r="L10" s="6">
+        <v>46186.9101066088</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G11" s="27">
+        <v>46193.458333333336</v>
+      </c>
+      <c r="H11" s="27">
+        <v>46193.583333333336</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="K11" s="6">
+        <v>46186.91841899305</v>
+      </c>
+      <c r="L11" s="6">
+        <v>46186.91841899305</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G12" s="27">
+        <v>46192.395833333336</v>
+      </c>
+      <c r="H12" s="27">
+        <v>46192.520833333336</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="K12" s="6">
+        <v>46186.92315149306</v>
+      </c>
+      <c r="L12" s="6">
+        <v>46186.92387899305</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G13" s="27">
+        <v>46192.520833333336</v>
+      </c>
+      <c r="H13" s="27">
+        <v>46192.645833333336</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="K13" s="6">
+        <v>46186.93342960648</v>
+      </c>
+      <c r="L13" s="6">
+        <v>46186.934943078704</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="27">
+        <v>46192.625</v>
+      </c>
+      <c r="H14" s="27">
+        <v>46192.75</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="K14" s="6">
+        <v>46186.94102628472</v>
+      </c>
+      <c r="L14" s="6">
+        <v>46186.94194075232</v>
       </c>
     </row>
   </sheetData>
@@ -8359,7 +9022,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="6">
-        <v>46186.829586458334</v>
+        <v>46186.94181881944</v>
       </c>
     </row>
     <row r="3">
@@ -12255,6 +12918,2162 @@
       </c>
       <c r="C357" s="5">
         <v>7.75285374E9</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="6">
+        <v>46186.8402871412</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C358" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="6">
+        <v>46186.84039403935</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="6">
+        <v>46186.84047112269</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="6">
+        <v>46186.840490358794</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="6">
+        <v>46186.8405671875</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="6">
+        <v>46186.84068150463</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="6">
+        <v>46186.84084211805</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="6">
+        <v>46186.84087893518</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="6">
+        <v>46186.84094443287</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="6">
+        <v>46186.841122199075</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="6">
+        <v>46186.84135017361</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="6">
+        <v>46186.841392766204</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="6">
+        <v>46186.84144934028</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="6">
+        <v>46186.84149951389</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="6">
+        <v>46186.8416395949</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="6">
+        <v>46186.84179731482</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="6">
+        <v>46186.842074976856</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="6">
+        <v>46186.84210196759</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="6">
+        <v>46186.842163194444</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="6">
+        <v>46186.84228755787</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="6">
+        <v>46186.84241409722</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="6">
+        <v>46186.842652430554</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="6">
+        <v>46186.842810381946</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C380" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="6">
+        <v>46186.84283944445</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="6">
+        <v>46186.84285185185</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="6">
+        <v>46186.842860324075</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C383" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="6">
+        <v>46186.842871747685</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C384" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="6">
+        <v>46186.84314827547</v>
+      </c>
+      <c r="B385" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C385" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="6">
+        <v>46186.843157083335</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="6">
+        <v>46186.84315988426</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C387" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="6">
+        <v>46186.84316508102</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C388" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="6">
+        <v>46186.84318252315</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C389" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="6">
+        <v>46186.843221504634</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C390" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="6">
+        <v>46186.84326469907</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="6">
+        <v>46186.84326967593</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C392" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="6">
+        <v>46186.843275046296</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="6">
+        <v>46186.84328054398</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C394" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="6">
+        <v>46186.84328541667</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C395" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="6">
+        <v>46186.84329538194</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="6">
+        <v>46186.84330561342</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C397" s="5">
+        <v>7.75285374E9</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="6">
+        <v>46186.84369701389</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C398" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="6">
+        <v>46186.84375826389</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="6">
+        <v>46186.84388719907</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="6">
+        <v>46186.843904375</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C401" s="2">
+        <v>5.56325487E8</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="6">
+        <v>46186.84999876157</v>
+      </c>
+      <c r="B402" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C402" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="6">
+        <v>46186.85009103009</v>
+      </c>
+      <c r="B403" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C403" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="6">
+        <v>46186.850208715274</v>
+      </c>
+      <c r="B404" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C404" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="6">
+        <v>46186.85022724537</v>
+      </c>
+      <c r="B405" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C405" s="2">
+        <v>5.56325487E8</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="6">
+        <v>46186.85032677083</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C406" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="6">
+        <v>46186.90948365741</v>
+      </c>
+      <c r="B407" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C407" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="6">
+        <v>46186.90956373843</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C408" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="6">
+        <v>46186.90969335648</v>
+      </c>
+      <c r="B409" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C409" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="6">
+        <v>46186.909704826394</v>
+      </c>
+      <c r="B410" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C410" s="2">
+        <v>5.56325487E8</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="6">
+        <v>46186.909792280094</v>
+      </c>
+      <c r="B411" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C411" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="6">
+        <v>46186.909965046296</v>
+      </c>
+      <c r="B412" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C412" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="6">
+        <v>46186.91008100694</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C413" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="6">
+        <v>46186.91657075231</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C414" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="6">
+        <v>46186.916663854165</v>
+      </c>
+      <c r="B415" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C415" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="6">
+        <v>46186.91673525463</v>
+      </c>
+      <c r="B416" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C416" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="6">
+        <v>46186.916753321755</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C417" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="6">
+        <v>46186.91682949074</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C418" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="6">
+        <v>46186.916949375</v>
+      </c>
+      <c r="B419" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C419" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="6">
+        <v>46186.9171627662</v>
+      </c>
+      <c r="B420" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C420" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="6">
+        <v>46186.917184328704</v>
+      </c>
+      <c r="B421" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C421" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="6">
+        <v>46186.91724996528</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C422" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="6">
+        <v>46186.917345532405</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="6">
+        <v>46186.91756277777</v>
+      </c>
+      <c r="B424" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C424" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="6">
+        <v>46186.91757974537</v>
+      </c>
+      <c r="B425" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C425" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="6">
+        <v>46186.91762140046</v>
+      </c>
+      <c r="B426" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C426" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="6">
+        <v>46186.91767545139</v>
+      </c>
+      <c r="B427" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C427" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="6">
+        <v>46186.91782137731</v>
+      </c>
+      <c r="B428" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C428" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="6">
+        <v>46186.91795429398</v>
+      </c>
+      <c r="B429" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C429" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="6">
+        <v>46186.91814736111</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C430" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="6">
+        <v>46186.91816194444</v>
+      </c>
+      <c r="B431" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C431" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="6">
+        <v>46186.918171550926</v>
+      </c>
+      <c r="B432" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C432" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="6">
+        <v>46186.91819344908</v>
+      </c>
+      <c r="B433" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C433" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="6">
+        <v>46186.918201064815</v>
+      </c>
+      <c r="B434" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C434" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="6">
+        <v>46186.91838107639</v>
+      </c>
+      <c r="B435" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C435" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="6">
+        <v>46186.918396759254</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C436" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="6">
+        <v>46186.91840275463</v>
+      </c>
+      <c r="B437" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C437" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="6">
+        <v>46186.91840789352</v>
+      </c>
+      <c r="B438" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C438" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="6">
+        <v>46186.91841267361</v>
+      </c>
+      <c r="B439" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C439" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="6">
+        <v>46186.91844543982</v>
+      </c>
+      <c r="B440" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C440" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="6">
+        <v>46186.92124755787</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C441" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="6">
+        <v>46186.921375983795</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C442" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="6">
+        <v>46186.92144960648</v>
+      </c>
+      <c r="B443" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C443" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="6">
+        <v>46186.921481550926</v>
+      </c>
+      <c r="B444" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C444" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="6">
+        <v>46186.92160864583</v>
+      </c>
+      <c r="B445" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C445" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="6">
+        <v>46186.92174809027</v>
+      </c>
+      <c r="B446" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C446" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="6">
+        <v>46186.921912962964</v>
+      </c>
+      <c r="B447" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C447" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="6">
+        <v>46186.92221696759</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C448" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="6">
+        <v>46186.92224465278</v>
+      </c>
+      <c r="B449" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C449" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="6">
+        <v>46186.92231913195</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C450" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="6">
+        <v>46186.92248976852</v>
+      </c>
+      <c r="B451" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C451" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="6">
+        <v>46186.92259627314</v>
+      </c>
+      <c r="B452" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C452" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="6">
+        <v>46186.922775416664</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C453" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="6">
+        <v>46186.922915057876</v>
+      </c>
+      <c r="B454" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C454" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="6">
+        <v>46186.92292915509</v>
+      </c>
+      <c r="B455" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C455" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="6">
+        <v>46186.92294081018</v>
+      </c>
+      <c r="B456" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C456" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="6">
+        <v>46186.922948113424</v>
+      </c>
+      <c r="B457" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C457" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="6">
+        <v>46186.92295548611</v>
+      </c>
+      <c r="B458" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C458" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="6">
+        <v>46186.92311181713</v>
+      </c>
+      <c r="B459" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C459" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="6">
+        <v>46186.923120300926</v>
+      </c>
+      <c r="B460" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C460" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="6">
+        <v>46186.92312409722</v>
+      </c>
+      <c r="B461" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C461" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="6">
+        <v>46186.92313214121</v>
+      </c>
+      <c r="B462" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C462" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="6">
+        <v>46186.92314009259</v>
+      </c>
+      <c r="B463" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C463" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="6">
+        <v>46186.92317270833</v>
+      </c>
+      <c r="B464" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C464" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="6">
+        <v>46186.92322719908</v>
+      </c>
+      <c r="B465" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C465" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="6">
+        <v>46186.92323503472</v>
+      </c>
+      <c r="B466" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C466" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="6">
+        <v>46186.92324287037</v>
+      </c>
+      <c r="B467" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C467" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="6">
+        <v>46186.92325100694</v>
+      </c>
+      <c r="B468" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C468" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="6">
+        <v>46186.92326252315</v>
+      </c>
+      <c r="B469" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C469" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="6">
+        <v>46186.92328325231</v>
+      </c>
+      <c r="B470" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C470" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="6">
+        <v>46186.92329922454</v>
+      </c>
+      <c r="B471" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C471" s="5">
+        <v>7.75285374E9</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="6">
+        <v>46186.923459467595</v>
+      </c>
+      <c r="B472" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C472" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="6">
+        <v>46186.923540937496</v>
+      </c>
+      <c r="B473" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C473" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="6">
+        <v>46186.92366158565</v>
+      </c>
+      <c r="B474" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C474" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="6">
+        <v>46186.92368224537</v>
+      </c>
+      <c r="B475" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C475" s="2">
+        <v>7.72223311E8</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="6">
+        <v>46186.92379863426</v>
+      </c>
+      <c r="B476" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C476" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="6">
+        <v>46186.92386092593</v>
+      </c>
+      <c r="B477" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C477" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="6">
+        <v>46186.93167302084</v>
+      </c>
+      <c r="B478" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C478" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="6">
+        <v>46186.93175275463</v>
+      </c>
+      <c r="B479" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C479" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="6">
+        <v>46186.93183296296</v>
+      </c>
+      <c r="B480" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C480" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="6">
+        <v>46186.93184615741</v>
+      </c>
+      <c r="B481" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C481" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="6">
+        <v>46186.931904363424</v>
+      </c>
+      <c r="B482" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C482" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="6">
+        <v>46186.931989282406</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C483" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="6">
+        <v>46186.9321597338</v>
+      </c>
+      <c r="B484" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C484" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="6">
+        <v>46186.93238048611</v>
+      </c>
+      <c r="B485" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C485" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="6">
+        <v>46186.932405914355</v>
+      </c>
+      <c r="B486" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C486" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="6">
+        <v>46186.93245748842</v>
+      </c>
+      <c r="B487" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C487" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="6">
+        <v>46186.93256071759</v>
+      </c>
+      <c r="B488" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C488" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="6">
+        <v>46186.932732291665</v>
+      </c>
+      <c r="B489" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C489" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="6">
+        <v>46186.9329352662</v>
+      </c>
+      <c r="B490" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C490" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="6">
+        <v>46186.933095451386</v>
+      </c>
+      <c r="B491" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C491" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="6">
+        <v>46186.9331275</v>
+      </c>
+      <c r="B492" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C492" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="6">
+        <v>46186.93315011574</v>
+      </c>
+      <c r="B493" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C493" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="6">
+        <v>46186.933163865746</v>
+      </c>
+      <c r="B494" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C494" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="6">
+        <v>46186.93317611111</v>
+      </c>
+      <c r="B495" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C495" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="6">
+        <v>46186.933397685185</v>
+      </c>
+      <c r="B496" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C496" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="6">
+        <v>46186.93340721064</v>
+      </c>
+      <c r="B497" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C497" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="6">
+        <v>46186.93341179398</v>
+      </c>
+      <c r="B498" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C498" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="6">
+        <v>46186.93341730324</v>
+      </c>
+      <c r="B499" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C499" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="6">
+        <v>46186.93342263889</v>
+      </c>
+      <c r="B500" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C500" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="6">
+        <v>46186.93344361111</v>
+      </c>
+      <c r="B501" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C501" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="6">
+        <v>46186.933477708335</v>
+      </c>
+      <c r="B502" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C502" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="6">
+        <v>46186.933482962966</v>
+      </c>
+      <c r="B503" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C503" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="6">
+        <v>46186.93348796296</v>
+      </c>
+      <c r="B504" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C504" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="6">
+        <v>46186.933493564815</v>
+      </c>
+      <c r="B505" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C505" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="6">
+        <v>46186.93349834491</v>
+      </c>
+      <c r="B506" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C506" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="6">
+        <v>46186.93350730324</v>
+      </c>
+      <c r="B507" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C507" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="6">
+        <v>46186.93351732639</v>
+      </c>
+      <c r="B508" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C508" s="5">
+        <v>7.75285374E9</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="6">
+        <v>46186.93366481482</v>
+      </c>
+      <c r="B509" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C509" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="6">
+        <v>46186.93447677083</v>
+      </c>
+      <c r="B510" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C510" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="6">
+        <v>46186.93459533565</v>
+      </c>
+      <c r="B511" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C511" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="6">
+        <v>46186.93461668982</v>
+      </c>
+      <c r="B512" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C512" s="2">
+        <v>3.80562356699E11</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="6">
+        <v>46186.93469775463</v>
+      </c>
+      <c r="B513" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C513" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="6">
+        <v>46186.93475565972</v>
+      </c>
+      <c r="B514" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C514" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="6">
+        <v>46186.93487548611</v>
+      </c>
+      <c r="B515" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C515" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="6">
+        <v>46186.93492909722</v>
+      </c>
+      <c r="B516" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C516" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="6">
+        <v>46186.93943946759</v>
+      </c>
+      <c r="B517" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C517" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="6">
+        <v>46186.93952564815</v>
+      </c>
+      <c r="B518" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C518" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="6">
+        <v>46186.93961234954</v>
+      </c>
+      <c r="B519" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C519" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="6">
+        <v>46186.93963792824</v>
+      </c>
+      <c r="B520" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C520" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="6">
+        <v>46186.93971619213</v>
+      </c>
+      <c r="B521" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C521" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="6">
+        <v>46186.93980248843</v>
+      </c>
+      <c r="B522" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C522" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="6">
+        <v>46186.93997303241</v>
+      </c>
+      <c r="B523" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C523" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="6">
+        <v>46186.94020776621</v>
+      </c>
+      <c r="B524" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C524" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="6">
+        <v>46186.940246631944</v>
+      </c>
+      <c r="B525" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C525" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="6">
+        <v>46186.940307303244</v>
+      </c>
+      <c r="B526" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C526" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="6">
+        <v>46186.940381747685</v>
+      </c>
+      <c r="B527" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C527" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="6">
+        <v>46186.9404864699</v>
+      </c>
+      <c r="B528" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C528" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="6">
+        <v>46186.94059925926</v>
+      </c>
+      <c r="B529" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C529" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="6">
+        <v>46186.94076671296</v>
+      </c>
+      <c r="B530" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C530" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="6">
+        <v>46186.94079503472</v>
+      </c>
+      <c r="B531" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C531" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="6">
+        <v>46186.940825833335</v>
+      </c>
+      <c r="B532" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C532" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="6">
+        <v>46186.940834629626</v>
+      </c>
+      <c r="B533" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C533" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="6">
+        <v>46186.940848275466</v>
+      </c>
+      <c r="B534" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C534" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="6">
+        <v>46186.9410028125</v>
+      </c>
+      <c r="B535" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C535" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="6">
+        <v>46186.94100767361</v>
+      </c>
+      <c r="B536" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C536" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="6">
+        <v>46186.941009814815</v>
+      </c>
+      <c r="B537" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C537" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="6">
+        <v>46186.94101516204</v>
+      </c>
+      <c r="B538" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C538" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="6">
+        <v>46186.941019942125</v>
+      </c>
+      <c r="B539" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C539" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="6">
+        <v>46186.941040590274</v>
+      </c>
+      <c r="B540" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C540" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="6">
+        <v>46186.941073344904</v>
+      </c>
+      <c r="B541" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C541" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="6">
+        <v>46186.94107818287</v>
+      </c>
+      <c r="B542" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C542" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="6">
+        <v>46186.9410828125</v>
+      </c>
+      <c r="B543" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C543" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="6">
+        <v>46186.94108768518</v>
+      </c>
+      <c r="B544" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C544" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="6">
+        <v>46186.94109797454</v>
+      </c>
+      <c r="B545" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C545" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="6">
+        <v>46186.941113946756</v>
+      </c>
+      <c r="B546" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C546" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="6">
+        <v>46186.94112258102</v>
+      </c>
+      <c r="B547" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C547" s="5">
+        <v>7.75285374E9</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="6">
+        <v>46186.94154565972</v>
+      </c>
+      <c r="B548" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C548" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="6">
+        <v>46186.94161709491</v>
+      </c>
+      <c r="B549" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C549" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="6">
+        <v>46186.94173997686</v>
+      </c>
+      <c r="B550" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C550" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="6">
+        <v>46186.9417575</v>
+      </c>
+      <c r="B551" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C551" s="2">
+        <v>5.52635478E8</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="6">
+        <v>46186.94187967593</v>
+      </c>
+      <c r="B552" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C552" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="6">
+        <v>46186.94192912037</v>
+      </c>
+      <c r="B553" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C553" s="2" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -12279,46 +15098,46 @@
         <v>28</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>200</v>
+        <v>284</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>201</v>
+        <v>285</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>203</v>
+        <v>287</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>204</v>
+        <v>288</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>205</v>
+        <v>289</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>206</v>
+        <v>290</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>207</v>
+        <v>291</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>208</v>
+        <v>292</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>209</v>
+        <v>293</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>210</v>
+        <v>294</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>211</v>
+        <v>295</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>212</v>
+        <v>296</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>213</v>
+        <v>297</v>
       </c>
       <c r="P1" s="9"/>
     </row>
@@ -12334,7 +15153,7 @@
       <c r="G2" s="11"/>
       <c r="H2" s="2"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="9"/>
+      <c r="J2" s="2"/>
       <c r="K2" s="11"/>
       <c r="L2" s="9"/>
       <c r="M2" s="11"/>
@@ -15344,39 +18163,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="s">
-        <v>201</v>
+        <v>285</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>214</v>
+        <v>298</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>215</v>
+        <v>299</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>216</v>
+        <v>300</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>217</v>
+        <v>301</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>218</v>
+        <v>302</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>219</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="16" t="s">
-        <v>220</v>
+        <v>304</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>221</v>
+        <v>305</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>221</v>
+        <v>305</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="E2" s="18">
         <v>80.0</v>
@@ -15390,16 +18209,16 @@
     </row>
     <row r="3">
       <c r="A3" s="16" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>224</v>
+        <v>308</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>225</v>
+        <v>309</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>226</v>
+        <v>310</v>
       </c>
       <c r="E3" s="18">
         <v>180.0</v>
@@ -15428,37 +18247,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>227</v>
+        <v>311</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>212</v>
+        <v>296</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>228</v>
+        <v>312</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>201</v>
+        <v>285</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>229</v>
+        <v>313</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>230</v>
+        <v>314</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>231</v>
+        <v>315</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>232</v>
+        <v>316</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>233</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -15480,45 +18299,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="s">
-        <v>234</v>
+        <v>318</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>227</v>
+        <v>311</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>201</v>
+        <v>285</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>200</v>
+        <v>284</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>235</v>
+        <v>319</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>236</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>237</v>
+        <v>321</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>238</v>
+        <v>322</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G2" s="6">
         <v>46185.93864650463</v>
@@ -15526,22 +18345,22 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>241</v>
+        <v>325</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>242</v>
+        <v>326</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G3" s="6">
         <v>46185.94321923611</v>
@@ -15549,22 +18368,22 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>244</v>
+        <v>328</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>245</v>
+        <v>329</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G4" s="6">
         <v>46185.947929629634</v>
@@ -15575,19 +18394,19 @@
         <v>62</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>246</v>
+        <v>330</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="G5" s="6">
         <v>46185.95118355324</v>
@@ -15595,22 +18414,22 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>248</v>
+        <v>332</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>249</v>
+        <v>333</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="G6" s="6">
         <v>46186.28802574074</v>
@@ -15618,22 +18437,22 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>250</v>
+        <v>334</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>251</v>
+        <v>335</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="G7" s="6">
         <v>46186.37949186342</v>
@@ -15641,22 +18460,22 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>253</v>
+        <v>337</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>254</v>
+        <v>338</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G8" s="6">
         <v>46186.41239509259</v>
@@ -15664,22 +18483,22 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>255</v>
+        <v>339</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>256</v>
+        <v>340</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G9" s="6">
         <v>46186.417601712965</v>
@@ -15687,22 +18506,22 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>257</v>
+        <v>341</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>258</v>
+        <v>342</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="G10" s="6">
         <v>46186.43227880787</v>
@@ -15710,22 +18529,22 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>259</v>
+        <v>343</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>260</v>
+        <v>344</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="G11" s="6">
         <v>46186.43385166666</v>
@@ -15733,22 +18552,22 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>261</v>
+        <v>345</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>262</v>
+        <v>346</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="G12" s="6">
         <v>46186.46531371528</v>
@@ -15756,22 +18575,22 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>263</v>
+        <v>347</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>264</v>
+        <v>348</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="G13" s="6">
         <v>46186.51336010417</v>
@@ -15779,22 +18598,22 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>265</v>
+        <v>349</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>266</v>
+        <v>350</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="G14" s="6">
         <v>46186.63879123842</v>
@@ -15802,22 +18621,22 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>267</v>
+        <v>351</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>268</v>
+        <v>352</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="G15" s="6">
         <v>46186.64895690972</v>
@@ -15825,22 +18644,22 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>269</v>
+        <v>353</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>270</v>
+        <v>354</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="G16" s="6">
         <v>46186.651472592595</v>
@@ -15848,22 +18667,22 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>271</v>
+        <v>355</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>272</v>
+        <v>356</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="G17" s="6">
         <v>46186.65388371528</v>
@@ -15871,22 +18690,22 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>273</v>
+        <v>357</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>274</v>
+        <v>358</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G18" s="6">
         <v>46186.74996538194</v>
@@ -15894,22 +18713,22 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>275</v>
+        <v>359</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>276</v>
+        <v>360</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G19" s="6">
         <v>46186.75340984954</v>
@@ -15923,16 +18742,16 @@
         <v>149</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G20" s="6">
         <v>46186.81030033565</v>
@@ -15946,16 +18765,16 @@
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G21" s="6">
         <v>46186.81859570602</v>
@@ -15969,16 +18788,16 @@
         <v>169</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="G22" s="6">
         <v>46186.823546238425</v>
@@ -15992,19 +18811,134 @@
         <v>192</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="G23" s="6">
         <v>46186.829506469905</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G24" s="6">
+        <v>46186.842857511576</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G25" s="6">
+        <v>46186.91818388889</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G26" s="6">
+        <v>46186.92294576389</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G27" s="6">
+        <v>46186.9331603125</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G28" s="6">
+        <v>46186.940831458334</v>
       </c>
     </row>
   </sheetData>
@@ -16025,33 +18959,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>277</v>
+        <v>361</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>234</v>
+        <v>318</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>278</v>
+        <v>362</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>279</v>
+        <v>363</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>280</v>
+        <v>364</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>235</v>
+        <v>319</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>236</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>281</v>
+        <v>365</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>282</v>
+        <v>366</v>
       </c>
       <c r="C2" s="9">
         <v>46186.0</v>
@@ -16063,7 +18997,7 @@
         <v>1.0</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G2" s="6">
         <v>46185.85522081019</v>
@@ -16071,10 +19005,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>283</v>
+        <v>367</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>282</v>
+        <v>366</v>
       </c>
       <c r="C3" s="9">
         <v>46185.0</v>
@@ -16086,7 +19020,7 @@
         <v>2.0</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G3" s="6">
         <v>46185.85522081019</v>
@@ -16094,10 +19028,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>284</v>
+        <v>368</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>285</v>
+        <v>369</v>
       </c>
       <c r="C4" s="9">
         <v>46186.0</v>
@@ -16109,7 +19043,7 @@
         <v>1.0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G4" s="6">
         <v>46185.86117096065</v>
@@ -16117,10 +19051,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>286</v>
+        <v>370</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>285</v>
+        <v>369</v>
       </c>
       <c r="C5" s="9">
         <v>46187.0</v>
@@ -16132,7 +19066,7 @@
         <v>2.0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G5" s="6">
         <v>46185.86117096065</v>
@@ -16140,10 +19074,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>287</v>
+        <v>371</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>285</v>
+        <v>369</v>
       </c>
       <c r="C6" s="9">
         <v>46185.0</v>
@@ -16155,7 +19089,7 @@
         <v>3.0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G6" s="6">
         <v>46185.86117096065</v>
@@ -16163,10 +19097,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>288</v>
+        <v>372</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>289</v>
+        <v>373</v>
       </c>
       <c r="C7" s="9">
         <v>46186.0</v>
@@ -16178,7 +19112,7 @@
         <v>1.0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G7" s="6">
         <v>46185.86662434028</v>
@@ -16186,10 +19120,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>290</v>
+        <v>374</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>289</v>
+        <v>373</v>
       </c>
       <c r="C8" s="9">
         <v>46187.0</v>
@@ -16201,7 +19135,7 @@
         <v>2.0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G8" s="6">
         <v>46185.86662434028</v>
@@ -16209,10 +19143,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>291</v>
+        <v>375</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>289</v>
+        <v>373</v>
       </c>
       <c r="C9" s="9">
         <v>46185.0</v>
@@ -16224,7 +19158,7 @@
         <v>3.0</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G9" s="6">
         <v>46185.86662434028</v>
@@ -16232,10 +19166,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>292</v>
+        <v>376</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>293</v>
+        <v>377</v>
       </c>
       <c r="C10" s="9">
         <v>46186.0</v>
@@ -16247,7 +19181,7 @@
         <v>1.0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G10" s="6">
         <v>46185.87604545139</v>
@@ -16255,10 +19189,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>294</v>
+        <v>378</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>293</v>
+        <v>377</v>
       </c>
       <c r="C11" s="9">
         <v>46186.0</v>
@@ -16270,7 +19204,7 @@
         <v>2.0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G11" s="6">
         <v>46185.87604545139</v>
@@ -16278,10 +19212,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>295</v>
+        <v>379</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>296</v>
+        <v>380</v>
       </c>
       <c r="C12" s="9">
         <v>46186.0</v>
@@ -16293,7 +19227,7 @@
         <v>1.0</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G12" s="6">
         <v>46185.880830740745</v>
@@ -16301,10 +19235,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>297</v>
+        <v>381</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>298</v>
+        <v>382</v>
       </c>
       <c r="C13" s="9">
         <v>46186.0</v>
@@ -16316,7 +19250,7 @@
         <v>1.0</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>299</v>
+        <v>383</v>
       </c>
       <c r="G13" s="6">
         <v>46185.90712123843</v>
@@ -16324,10 +19258,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>300</v>
+        <v>384</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>301</v>
+        <v>385</v>
       </c>
       <c r="C14" s="9">
         <v>46185.0</v>
@@ -16339,7 +19273,7 @@
         <v>1.0</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="G14" s="6">
         <v>46185.909134305555</v>
@@ -16347,7 +19281,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>302</v>
+        <v>386</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -16362,7 +19296,7 @@
         <v>1.0</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>299</v>
+        <v>383</v>
       </c>
       <c r="G15" s="6">
         <v>46185.95119975695</v>
@@ -16370,10 +19304,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>303</v>
+        <v>387</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>248</v>
+        <v>332</v>
       </c>
       <c r="C16" s="9">
         <v>46187.0</v>
@@ -16385,7 +19319,7 @@
         <v>1.0</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>299</v>
+        <v>383</v>
       </c>
       <c r="G16" s="6">
         <v>46186.28802998843</v>
@@ -16393,10 +19327,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>304</v>
+        <v>388</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>250</v>
+        <v>334</v>
       </c>
       <c r="C17" s="9">
         <v>46240.0</v>
@@ -16408,7 +19342,7 @@
         <v>1.0</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="G17" s="6">
         <v>46186.37949752314</v>
@@ -16416,10 +19350,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>305</v>
+        <v>389</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>253</v>
+        <v>337</v>
       </c>
       <c r="C18" s="9">
         <v>46195.0</v>
@@ -16431,7 +19365,7 @@
         <v>1.0</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G18" s="6">
         <v>46186.41240255787</v>
@@ -16439,10 +19373,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>306</v>
+        <v>390</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>255</v>
+        <v>339</v>
       </c>
       <c r="C19" s="9">
         <v>46188.0</v>
@@ -16454,7 +19388,7 @@
         <v>1.0</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G19" s="6">
         <v>46186.41762684028</v>
@@ -16462,10 +19396,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>307</v>
+        <v>391</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>257</v>
+        <v>341</v>
       </c>
       <c r="C20" s="9">
         <v>46188.0</v>
@@ -16477,7 +19411,7 @@
         <v>1.0</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>299</v>
+        <v>383</v>
       </c>
       <c r="G20" s="6">
         <v>46186.432285104165</v>
@@ -16485,10 +19419,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>308</v>
+        <v>392</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>259</v>
+        <v>343</v>
       </c>
       <c r="C21" s="9">
         <v>46188.0</v>
@@ -16500,7 +19434,7 @@
         <v>1.0</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>299</v>
+        <v>383</v>
       </c>
       <c r="G21" s="6">
         <v>46186.433856041665</v>
@@ -16508,10 +19442,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>309</v>
+        <v>393</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>261</v>
+        <v>345</v>
       </c>
       <c r="C22" s="9">
         <v>46186.0</v>
@@ -16523,7 +19457,7 @@
         <v>1.0</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>299</v>
+        <v>383</v>
       </c>
       <c r="G22" s="6">
         <v>46186.46532699074</v>
@@ -16531,10 +19465,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>310</v>
+        <v>394</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>263</v>
+        <v>347</v>
       </c>
       <c r="C23" s="9">
         <v>46188.0</v>
@@ -16546,7 +19480,7 @@
         <v>1.0</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>299</v>
+        <v>383</v>
       </c>
       <c r="G23" s="6">
         <v>46186.51336833333</v>
@@ -16554,10 +19488,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>311</v>
+        <v>395</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>265</v>
+        <v>349</v>
       </c>
       <c r="C24" s="9">
         <v>46188.0</v>
@@ -16569,7 +19503,7 @@
         <v>1.0</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>299</v>
+        <v>383</v>
       </c>
       <c r="G24" s="6">
         <v>46186.63879921296</v>
@@ -16577,10 +19511,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>312</v>
+        <v>396</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>267</v>
+        <v>351</v>
       </c>
       <c r="C25" s="9">
         <v>46190.0</v>
@@ -16592,7 +19526,7 @@
         <v>1.0</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="G25" s="6">
         <v>46186.64896158565</v>
@@ -16600,10 +19534,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>313</v>
+        <v>397</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>269</v>
+        <v>353</v>
       </c>
       <c r="C26" s="9">
         <v>46191.0</v>
@@ -16615,7 +19549,7 @@
         <v>1.0</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="G26" s="6">
         <v>46186.65148021991</v>
@@ -16623,10 +19557,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>314</v>
+        <v>398</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>271</v>
+        <v>355</v>
       </c>
       <c r="C27" s="9">
         <v>46191.0</v>
@@ -16638,7 +19572,7 @@
         <v>1.0</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>299</v>
+        <v>383</v>
       </c>
       <c r="G27" s="6">
         <v>46186.65389151621</v>
@@ -16646,13 +19580,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>315</v>
+        <v>399</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>273</v>
+        <v>357</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>316</v>
+        <v>400</v>
       </c>
       <c r="D28" s="21">
         <v>0.6041666666678793</v>
@@ -16661,7 +19595,7 @@
         <v>1.0</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G28" s="6">
         <v>46186.74997243055</v>
@@ -16669,13 +19603,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>317</v>
+        <v>401</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>275</v>
+        <v>359</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>316</v>
+        <v>400</v>
       </c>
       <c r="D29" s="21">
         <v>0.6041666666678793</v>
@@ -16684,7 +19618,7 @@
         <v>1.0</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G29" s="6">
         <v>46186.75342905092</v>
@@ -16692,13 +19626,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>318</v>
+        <v>402</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>316</v>
+        <v>400</v>
       </c>
       <c r="D30" s="21">
         <v>0.6041666666678793</v>
@@ -16707,7 +19641,7 @@
         <v>1.0</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G30" s="6">
         <v>46186.81031998842</v>
@@ -16715,13 +19649,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>319</v>
+        <v>403</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>316</v>
+        <v>400</v>
       </c>
       <c r="D31" s="21">
         <v>0.5625</v>
@@ -16730,7 +19664,7 @@
         <v>1.0</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="G31" s="6">
         <v>46186.81860835648</v>
@@ -16738,13 +19672,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>320</v>
+        <v>404</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>316</v>
+        <v>400</v>
       </c>
       <c r="D32" s="21">
         <v>0.6041666666678793</v>
@@ -16753,7 +19687,7 @@
         <v>1.0</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>299</v>
+        <v>383</v>
       </c>
       <c r="G32" s="6">
         <v>46186.8235540162</v>
@@ -16761,13 +19695,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>321</v>
+        <v>405</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>193</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>316</v>
+        <v>400</v>
       </c>
       <c r="D33" s="21">
         <v>0.7083333333321207</v>
@@ -16776,10 +19710,148 @@
         <v>1.0</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>299</v>
+        <v>383</v>
       </c>
       <c r="G33" s="6">
         <v>46186.829514259254</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D34" s="21">
+        <v>0.3958333333321207</v>
+      </c>
+      <c r="E34" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="G34" s="6">
+        <v>46186.84286603009</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D35" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="E35" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="G35" s="6">
+        <v>46186.84286603009</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D36" s="21">
+        <v>0.4583333333321207</v>
+      </c>
+      <c r="E36" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G36" s="6">
+        <v>46186.918198263884</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D37" s="21">
+        <v>0.3958333333321207</v>
+      </c>
+      <c r="E37" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="G37" s="6">
+        <v>46186.922953078705</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D38" s="21">
+        <v>0.5208333333321207</v>
+      </c>
+      <c r="E38" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="G38" s="6">
+        <v>46186.9331718287</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D39" s="21">
+        <v>0.625</v>
+      </c>
+      <c r="E39" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="G39" s="6">
+        <v>46186.94084517361</v>
       </c>
     </row>
   </sheetData>
@@ -16796,21 +19868,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="s">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>201</v>
+        <v>285</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>219</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="16" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>220</v>
+        <v>304</v>
       </c>
       <c r="C2" s="14" t="b">
         <v>1</v>
@@ -16818,10 +19890,10 @@
     </row>
     <row r="3">
       <c r="A3" s="16" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="C3" s="14" t="b">
         <v>1</v>
@@ -16829,10 +19901,10 @@
     </row>
     <row r="4">
       <c r="A4" s="16" t="s">
-        <v>322</v>
+        <v>415</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>220</v>
+        <v>304</v>
       </c>
       <c r="C4" s="14" t="b">
         <v>1</v>

--- a/Docs/SmartFlow Beauty Demo.xlsx
+++ b/Docs/SmartFlow Beauty Demo.xlsx
@@ -18,10 +18,11 @@
     <sheet state="visible" name="Providers" sheetId="13" r:id="rId17"/>
     <sheet state="visible" name="Notifications" sheetId="14" r:id="rId18"/>
     <sheet state="visible" name="Messages" sheetId="15" r:id="rId19"/>
-    <sheet state="visible" name="CustomerConflicts" sheetId="16" r:id="rId20"/>
-    <sheet state="visible" name="Locations" sheetId="17" r:id="rId21"/>
-    <sheet state="visible" name="Customers" sheetId="18" r:id="rId22"/>
-    <sheet state="visible" name="Appointments" sheetId="19" r:id="rId23"/>
+    <sheet state="visible" name="RequestRecipients" sheetId="16" r:id="rId20"/>
+    <sheet state="visible" name="CustomerConflicts" sheetId="17" r:id="rId21"/>
+    <sheet state="visible" name="Locations" sheetId="18" r:id="rId22"/>
+    <sheet state="visible" name="Customers" sheetId="19" r:id="rId23"/>
+    <sheet state="visible" name="Appointments" sheetId="20" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3799" uniqueCount="1185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4188" uniqueCount="1286">
   <si>
     <t>key</t>
   </si>
@@ -2320,6 +2321,180 @@
     <t>approve_option_1 | req_1781584663429</t>
   </si>
   <si>
+    <t>text=0998765643, state=[WAITING_MY_APPOINTMENTS_PHONE], length=29</t>
+  </si>
+  <si>
+    <t>{"id":"5628137156229063692","from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"ru"},"message":{"message_id":3247,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781593600,"text":"17.06.2026 11:00\n\n💅 Окрашивание\n👩‍💼 Алиса\n📍 Alice Hair Hub\n📝 Комментарий: -","reply_markup":{"inline_keyboard":[[{"text":"📅 Перенести","callback_data":"reschedule_appointment|appt_1781549316543"}],[{"text":"❌ Отменить","callback_data":"cancel_appointment|appt_1781549316543"}]]}},"chat_instance":"-760725032823406943","data":"reschedule_appointment|appt_1781549316543"}</t>
+  </si>
+  <si>
+    <t>reschedule_appointment | appt_1781549316543</t>
+  </si>
+  <si>
+    <t>{"ok":true,"result":{"message_id":3247,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781593600,"edit_date":1781593607,"text":"\u041f\u043e\u0434\u0442\u0432\u0435\u0440\u0434\u0438\u0442\u0435 \u043f\u0435\u0440\u0435\u043d\u043e\u0441 \u0437\u0430\u043f\u0438\u0441\u0438","reply_markup":{"inline_keyboard":[[{"text":"\u2705 \u0414\u0430","callback_data":"confirm_reschedule|appt_1781549316543"}],[{"text":"\u21a9\ufe0f \u041d\u0435\u0442","callback_data":"back_to_appointment|appt_1781549316543"}]]}}}</t>
+  </si>
+  <si>
+    <t>{"id":"5628137157277214577","from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"ru"},"message":{"message_id":3247,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781593600,"edit_date":1781593607,"text":"Подтвердите перенос записи","reply_markup":{"inline_keyboard":[[{"text":"✅ Да","callback_data":"confirm_reschedule|appt_1781549316543"}],[{"text":"↩️ Нет","callback_data":"back_to_appointment|appt_1781549316543"}]]}},"chat_instance":"-760725032823406943","data":"confirm_reschedule|appt_1781549316543"}</t>
+  </si>
+  <si>
+    <t>confirm_reschedule | appt_1781549316543</t>
+  </si>
+  <si>
+    <t>text=Завтра, state=[WAITING_RESCHEDULE_DATE], length=23</t>
+  </si>
+  <si>
+    <t>AVAILABLE_SLOT_BLOCKERS</t>
+  </si>
+  <si>
+    <t>{"providerId":"prov_001","customerId":"cust_1781549290789","date":"2026-06-16T21:00:00.000Z","providerAppointments":[{"startTime":"11:00","endTime":"14:00"}],"conflictCustomerIds":[],"conflictAppointments":[]}</t>
+  </si>
+  <si>
+    <t>{"providerId":"prov_001","customerId":"cust_1781549290789","dateValue":"2026-06-16T21:00:00.000Z","durationMinutes":180,"schedule":{"isWorking":true,"startTime":"07:00","endTime":"20:00"},"startMinutes":420,"endMinutes":1200,"busyIntervals":[{"start":660,"end":840}]}</t>
+  </si>
+  <si>
+    <t>text=08:00, state=[WAITING_RESCHEDULE_TIME], length=23</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"","service_id":"","provider_id":"","reschedule_appointment_id":"appt_1781549316543","pending_calendar_event_id":"","option_count":"","current_option_date":"","current_option_time":"","option1_date":"","option1_time":"","option2_date":"","option2_time":"","option3_date":"","option3_time":"","reschedule_date":"2026-06-16T21:00:00.000Z","reschedule_time":"","customer_name":"","customer_phone":"","customer_note":"","customer_id":""}</t>
+  </si>
+  <si>
+    <t>{"appointment_id":"appt_1781549316543","request_id":"req_1781549291426","customer_id":"cust_1781549290789","service_id":"serv_002","provider_id":"prov_001","location_id":"loc_001","start_at":"2026-06-17T08:00:00.000Z","end_at":"2026-06-17T11:00:00.000Z","status":"confirmed","calendar_event_id":"7ajgn4bkn67b9rlkurql0d0mso@google.com","created_at":"2026-06-15T18:48:36.543Z","updated_at":"2026-06-16T05:09:59.645Z","customer_note":"","reminder_24h_sent_at":"2026-06-16T05:09:59.356Z"}</t>
+  </si>
+  <si>
+    <t>appt_1781549316543</t>
+  </si>
+  <si>
+    <t>text=ывы, state=[WAITING_CUSTOMER_NAME], length=21</t>
+  </si>
+  <si>
+    <t>text=0440002211, state=[WAITING_CUSTOMER_PHONE], length=22</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_001","provider_id":"prov_001","reschedule_appointment_id":"","pending_calendar_event_id":"","option_count":0,"current_option_date":"2026-06-16T21:00:00.000Z","current_option_time":"","option1_date":"","option1_time":"","option2_date":"","option2_time":"","option3_date":"","option3_time":"","reschedule_date":"","reschedule_time":"","customer_name":"ывы","customer_phone":"0440002211","customer_note":"","customer_id":""}</t>
+  </si>
+  <si>
+    <t>{"providerId":"prov_001","customerId":"","date":"2026-06-16T21:00:00.000Z","providerAppointments":[{"startTime":"08:00","endTime":"11:00"}],"conflictCustomerIds":[],"conflictAppointments":[]}</t>
+  </si>
+  <si>
+    <t>{"providerId":"prov_001","customerId":"","dateValue":"2026-06-16T21:00:00.000Z","durationMinutes":80,"schedule":{"isWorking":true,"startTime":"07:00","endTime":"20:00"},"startMinutes":420,"endMinutes":1200,"busyIntervals":[{"start":480,"end":660}]}</t>
+  </si>
+  <si>
+    <t>["11:00","11:30","12:00","12:30","13:00","13:30","14:00","14:30","15:00","15:30","16:00","16:30","17:00","17:30","18:00","18:30"]</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_001","provider_id":"prov_001","reschedule_appointment_id":"","pending_calendar_event_id":"","option_count":1,"current_option_date":"2026-06-16T21:00:00.000Z","current_option_time":"1899-12-30T08:57:56.000Z","option1_date":"Wed Jun 17 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","option1_time":"1899-12-30T08:57:56.000Z","option2_date":"","option2_time":"","option3_date":"","option3_time":"","reschedule_date":"","reschedule_time":"","customer_name":"ывы","customer_phone":"0440002211","customer_note":"","customer_id":""}</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_001","provider_id":"prov_001","reschedule_appointment_id":"","pending_calendar_event_id":"","option_count":2,"current_option_date":"2026-06-16T21:00:00.000Z","current_option_time":"1899-12-30T11:57:56.000Z","option1_date":"Wed Jun 17 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","option1_time":"1899-12-30T08:57:56.000Z","option2_date":"Wed Jun 17 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","option2_time":"1899-12-30T11:57:56.000Z","option3_date":"","option3_time":"","reschedule_date":"","reschedule_time":"","customer_name":"ывы","customer_phone":"0440002211","customer_note":"","customer_id":""}</t>
+  </si>
+  <si>
+    <t>cust_1781595159028</t>
+  </si>
+  <si>
+    <t>req_1781595160209</t>
+  </si>
+  <si>
+    <t>{"id":"3118605849523187731","from":{"id":726107007,"is_bot":false,"first_name":"Serhii","username":"Serhii_Tsi","language_code":"en"},"message":{"message_id":3282,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":726107007,"first_name":"Serhii","username":"Serhii_Tsi","type":"private"},"date":1781595168,"text":"Новая запись\n\n👤 Клиент: ывы\n📞 Телефон: 0440002211\n📝 Комментарий: -\n\n📍 Филиал: Alice Hair Hub\n💅 Услуга: Стрижка\n👩‍💼 Мастер: Алиса\n\nВарианты времени:\n1) 17.06.2026 11:00\n2) 17.06.2026 14:00","entities":[{"offset":0,"length":12,"type":"bold"},{"offset":137,"length":17,"type":"bold"}],"reply_markup":{"inline_keyboard":[[{"text":"✅ 1","callback_data":"approve_option_1|req_1781595160209"},{"text":"✅ 2","callback_data":"approve_option_2|req_1781595160209"}],[{"text":"❌ Reject","callback_data":"reject_request|req_1781595160209"}]]}},"chat_instance":"-653345212733041723","data":"approve_option_1|req_1781595160209"}</t>
+  </si>
+  <si>
+    <t>approve_option_1 | req_1781595160209</t>
+  </si>
+  <si>
+    <t>text=Апр, state=[WAITING_CUSTOMER_NAME], length=21</t>
+  </si>
+  <si>
+    <t>text=0665437687, state=[WAITING_CUSTOMER_PHONE], length=22</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_001","provider_id":"prov_002","reschedule_appointment_id":"","pending_calendar_event_id":"","option_count":0,"current_option_date":"2026-06-16T21:00:00.000Z","current_option_time":"","option1_date":"","option1_time":"","option2_date":"","option2_time":"","option3_date":"","option3_time":"","reschedule_date":"","reschedule_time":"","customer_name":"Апр","customer_phone":"0665437687","customer_note":"","customer_id":""}</t>
+  </si>
+  <si>
+    <t>{"providerId":"prov_002","customerId":"","date":"2026-06-16T21:00:00.000Z","providerAppointments":[],"conflictCustomerIds":[],"conflictAppointments":[]}</t>
+  </si>
+  <si>
+    <t>{"providerId":"prov_002","customerId":"","dateValue":"2026-06-16T21:00:00.000Z","durationMinutes":80,"schedule":{"isWorking":true,"startTime":"07:00","endTime":"20:00"},"startMinutes":420,"endMinutes":1200,"busyIntervals":[]}</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_001","provider_id":"prov_002","reschedule_appointment_id":"","pending_calendar_event_id":"","option_count":1,"current_option_date":"2026-06-16T21:00:00.000Z","current_option_time":"1899-12-30T05:57:56.000Z","option1_date":"Wed Jun 17 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","option1_time":"1899-12-30T05:57:56.000Z","option2_date":"","option2_time":"","option3_date":"","option3_time":"","reschedule_date":"","reschedule_time":"","customer_name":"Апр","customer_phone":"0665437687","customer_note":"","customer_id":""}</t>
+  </si>
+  <si>
+    <t>cust_1781600562235</t>
+  </si>
+  <si>
+    <t>req_1781600563407</t>
+  </si>
+  <si>
+    <t>{"id":"3118605851935784314","from":{"id":726107007,"is_bot":false,"first_name":"Serhii","username":"Serhii_Tsi","language_code":"en"},"message":{"message_id":3307,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":726107007,"first_name":"Serhii","username":"Serhii_Tsi","type":"private"},"date":1781600570,"text":"Новая запись\n\n👤 Клиент: Апр\n📞 Телефон: 0665437687\n📝 Комментарий: -\n\n📍 Филиал: Alice Hair Hub\n💅 Услуга: Стрижка\n👩‍💼 Мастер: Ольга\n\nВарианты времени:\n1) 17.06.2026 08:00","entities":[{"offset":0,"length":12,"type":"bold"},{"offset":137,"length":17,"type":"bold"}],"reply_markup":{"inline_keyboard":[[{"text":"✅ 1","callback_data":"approve_option_1|req_1781600563407"}],[{"text":"❌ Reject","callback_data":"reject_request|req_1781600563407"}]]}},"chat_instance":"-653345212733041723","data":"approve_option_1|req_1781600563407"}</t>
+  </si>
+  <si>
+    <t>approve_option_1 | req_1781600563407</t>
+  </si>
+  <si>
+    <t>text=Прп, state=[WAITING_CUSTOMER_NAME], length=21</t>
+  </si>
+  <si>
+    <t>text=0778986545, state=[WAITING_CUSTOMER_PHONE], length=22</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","reschedule_appointment_id":"","pending_calendar_event_id":"","option_count":0,"current_option_date":"2026-06-16T21:00:00.000Z","current_option_time":"","option1_date":"","option1_time":"","option2_date":"","option2_time":"","option3_date":"","option3_time":"","reschedule_date":"","reschedule_time":"","customer_name":"Прп","customer_phone":"0778986545","customer_note":"","customer_id":""}</t>
+  </si>
+  <si>
+    <t>{"providerId":"prov_001","customerId":"","date":"2026-06-16T21:00:00.000Z","providerAppointments":[{"startTime":"08:00","endTime":"11:00"},{"startTime":"11:00","endTime":"12:20"}],"conflictCustomerIds":[],"conflictAppointments":[]}</t>
+  </si>
+  <si>
+    <t>{"providerId":"prov_001","customerId":"","dateValue":"2026-06-16T21:00:00.000Z","durationMinutes":180,"schedule":{"isWorking":true,"startTime":"07:00","endTime":"20:00"},"startMinutes":420,"endMinutes":1200,"busyIntervals":[{"start":480,"end":660},{"start":660,"end":740}]}</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_001","reschedule_appointment_id":"","pending_calendar_event_id":"","option_count":1,"current_option_date":"2026-06-16T21:00:00.000Z","current_option_time":"1899-12-30T10:27:56.000Z","option1_date":"Wed Jun 17 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","option1_time":"1899-12-30T10:27:56.000Z","option2_date":"","option2_time":"","option3_date":"","option3_time":"","reschedule_date":"","reschedule_time":"","customer_name":"Прп","customer_phone":"0778986545","customer_note":"","customer_id":""}</t>
+  </si>
+  <si>
+    <t>cust_1781603867410</t>
+  </si>
+  <si>
+    <t>req_1781603868134</t>
+  </si>
+  <si>
+    <t>{"id":"3118605850142391472","from":{"id":726107007,"is_bot":false,"first_name":"Serhii","username":"Serhii_Tsi","language_code":"en"},"message":{"message_id":3332,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":726107007,"first_name":"Serhii","username":"Serhii_Tsi","type":"private"},"date":1781603876,"text":"Новая запись\n\n👤 Клиент: Прп\n📞 Телефон: 0778986545\n📝 Комментарий: -\n\n📍 Филиал: Alice Hair Hub\n💅 Услуга: Окрашивание\n👩‍💼 Мастер: Алиса\n\nВарианты времени:\n1) 17.06.2026 12:30","entities":[{"offset":0,"length":12,"type":"bold"},{"offset":141,"length":17,"type":"bold"}],"reply_markup":{"inline_keyboard":[[{"text":"✅ 1","callback_data":"approve_option_1|req_1781603868134"}],[{"text":"❌ Reject","callback_data":"reject_request|req_1781603868134"}]]}},"chat_instance":"-653345212733041723","data":"approve_option_1|req_1781603868134"}</t>
+  </si>
+  <si>
+    <t>approve_option_1 | req_1781603868134</t>
+  </si>
+  <si>
+    <t>text=0987654323, state=[WAITING_CUSTOMER_PHONE], length=22</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_002","reschedule_appointment_id":"","pending_calendar_event_id":"","option_count":0,"current_option_date":"2026-06-16T21:00:00.000Z","current_option_time":"","option1_date":"","option1_time":"","option2_date":"","option2_time":"","option3_date":"","option3_time":"","reschedule_date":"","reschedule_time":"","customer_name":"Апа","customer_phone":"0987654323","customer_note":"","customer_id":""}</t>
+  </si>
+  <si>
+    <t>{"providerId":"prov_002","customerId":"","date":"2026-06-16T21:00:00.000Z","providerAppointments":[{"startTime":"08:00","endTime":"09:20"}],"conflictCustomerIds":[],"conflictAppointments":[]}</t>
+  </si>
+  <si>
+    <t>{"providerId":"prov_002","customerId":"","dateValue":"2026-06-16T21:00:00.000Z","durationMinutes":180,"schedule":{"isWorking":true,"startTime":"07:00","endTime":"20:00"},"startMinutes":420,"endMinutes":1200,"busyIntervals":[{"start":480,"end":560}]}</t>
+  </si>
+  <si>
+    <t>["09:30","10:00","10:30","11:00","11:30","12:00","12:30","13:00","13:30","14:00","14:30","15:00","15:30","16:00","16:30","17:00"]</t>
+  </si>
+  <si>
+    <t>text=13:30, state=[WAITING_OPTION_TIME], length=19</t>
+  </si>
+  <si>
+    <t>{"telegram_id":7752853740,"location_id":"loc_001","service_id":"serv_002","provider_id":"prov_002","reschedule_appointment_id":"","pending_calendar_event_id":"","option_count":1,"current_option_date":"2026-06-16T21:00:00.000Z","current_option_time":"1899-12-30T11:27:56.000Z","option1_date":"Wed Jun 17 2026 00:00:00 GMT+0300 (Oost-Europese zomertijd)","option1_time":"1899-12-30T11:27:56.000Z","option2_date":"","option2_time":"","option3_date":"","option3_time":"","reschedule_date":"","reschedule_time":"","customer_name":"Апа","customer_phone":"0987654323","customer_note":"","customer_id":""}</t>
+  </si>
+  <si>
+    <t>cust_1781608315929</t>
+  </si>
+  <si>
+    <t>req_1781608316889</t>
+  </si>
+  <si>
+    <t>{"id":"5628137154747093034","from":{"id":7752853740,"is_bot":false,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","language_code":"en"},"message":{"message_id":3359,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":7752853740,"first_name":"Run","last_name":"Pipelines","username":"RunPipelines","type":"private"},"date":1781608327,"text":"Новая запись\n\n👤 Клиент: Апа\n📞 Телефон: 0987654323\n📝 Комментарий: -\n\n📍 Филиал: Alice Hair Hub\n💅 Услуга: Окрашивание\n👩‍💼 Мастер: Ольга\n\nВарианты времени:\n1) 17.06.2026 13:30","entities":[{"offset":0,"length":12,"type":"bold"},{"offset":141,"length":17,"type":"bold"}],"reply_markup":{"inline_keyboard":[[{"text":"✅ 1","callback_data":"approve_option_1|req_1781608316889"}],[{"text":"❌ Reject","callback_data":"reject_request|req_1781608316889"}]]}},"chat_instance":"-760725032823406943","data":"approve_option_1|req_1781608316889"}</t>
+  </si>
+  <si>
+    <t>approve_option_1 | req_1781608316889</t>
+  </si>
+  <si>
+    <t>{"id":"3118605852165810284","from":{"id":726107007,"is_bot":false,"first_name":"Serhii","username":"Serhii_Tsi","language_code":"ru"},"message":{"message_id":3358,"from":{"id":8771518181,"is_bot":true,"first_name":"SmartFlow Beauty Demo","username":"smartflow_beauty_demo_bot"},"chat":{"id":726107007,"first_name":"Serhii","username":"Serhii_Tsi","type":"private"},"date":1781608326,"text":"Новая запись\n\n👤 Клиент: Апа\n📞 Телефон: 0987654323\n📝 Комментарий: -\n\n📍 Филиал: Alice Hair Hub\n💅 Услуга: Окрашивание\n👩‍💼 Мастер: Ольга\n\nВарианты времени:\n1) 17.06.2026 13:30","entities":[{"offset":0,"length":12,"type":"bold"},{"offset":141,"length":17,"type":"bold"}],"reply_markup":{"inline_keyboard":[[{"text":"✅ 1","callback_data":"approve_option_1|req_1781608316889"}],[{"text":"❌ Reject","callback_data":"reject_request|req_1781608316889"}]]}},"chat_instance":"-653345212733041723","data":"approve_option_1|req_1781608316889"}</t>
+  </si>
+  <si>
     <t>location_id</t>
   </si>
   <si>
@@ -2494,6 +2669,24 @@
     <t>opt_1781584664287</t>
   </si>
   <si>
+    <t>opt_1781595161155</t>
+  </si>
+  <si>
+    <t>opt_1781595161321</t>
+  </si>
+  <si>
+    <t>rejected</t>
+  </si>
+  <si>
+    <t>opt_1781600564046</t>
+  </si>
+  <si>
+    <t>opt_1781603869051</t>
+  </si>
+  <si>
+    <t>opt_1781608317746</t>
+  </si>
+  <si>
     <t>day_of_week</t>
   </si>
   <si>
@@ -3451,6 +3644,75 @@
     <t>Dnipro, Starokozatska, 53</t>
   </si>
   <si>
+    <t>CALENDAR_CUSTOMER</t>
+  </si>
+  <si>
+    <t>CALENDAR_PHONE</t>
+  </si>
+  <si>
+    <t>CALENDAR_SERVICE</t>
+  </si>
+  <si>
+    <t>CALENDAR_PROVIDER</t>
+  </si>
+  <si>
+    <t>CALENDAR_LOCATION</t>
+  </si>
+  <si>
+    <t>Локація</t>
+  </si>
+  <si>
+    <t>Локация</t>
+  </si>
+  <si>
+    <t>CALENDAR_NOTE</t>
+  </si>
+  <si>
+    <t>Коментар</t>
+  </si>
+  <si>
+    <t>Комментарий</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>recipient_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>receive_new_requests</t>
+  </si>
+  <si>
+    <t>rec_001</t>
+  </si>
+  <si>
+    <t>Борис</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>provider</t>
+  </si>
+  <si>
+    <t>rec_002</t>
+  </si>
+  <si>
+    <t>rec_003</t>
+  </si>
+  <si>
+    <t>Администратор</t>
+  </si>
+  <si>
+    <t>reception</t>
+  </si>
+  <si>
     <t>conflict_customer_id</t>
   </si>
   <si>
@@ -3517,9 +3779,6 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>language</t>
   </si>
   <si>
@@ -3550,6 +3809,30 @@
     <t>0988767865</t>
   </si>
   <si>
+    <t>ывы</t>
+  </si>
+  <si>
+    <t>0440002211</t>
+  </si>
+  <si>
+    <t>Апр</t>
+  </si>
+  <si>
+    <t>0665437687</t>
+  </si>
+  <si>
+    <t>Прп</t>
+  </si>
+  <si>
+    <t>0778986545</t>
+  </si>
+  <si>
+    <t>Апа</t>
+  </si>
+  <si>
+    <t>0987654323</t>
+  </si>
+  <si>
     <t>start_at</t>
   </si>
   <si>
@@ -3577,9 +3860,6 @@
     <t>snrti3r1c4oprmqs7kumuijuvo@google.com</t>
   </si>
   <si>
-    <t>appt_1781549316543</t>
-  </si>
-  <si>
     <t>7ajgn4bkn67b9rlkurql0d0mso@google.com</t>
   </si>
   <si>
@@ -3593,6 +3873,30 @@
   </si>
   <si>
     <t>ique4qlc54urjsr8jgc6paqn7g@google.com</t>
+  </si>
+  <si>
+    <t>appt_1781595189666</t>
+  </si>
+  <si>
+    <t>j75j6k077afulrshfu53bmfcvg@google.com</t>
+  </si>
+  <si>
+    <t>appt_1781600592867</t>
+  </si>
+  <si>
+    <t>0p3sbt61gmbk3jiccadpe8uqdk@google.com</t>
+  </si>
+  <si>
+    <t>appt_1781603894838</t>
+  </si>
+  <si>
+    <t>niounghor816n9nli8p7d539tg@google.com</t>
+  </si>
+  <si>
+    <t>appt_1781608366938</t>
+  </si>
+  <si>
+    <t>j423qh372ir9nhs0lj9mabi6ds@google.com</t>
   </si>
 </sst>
 </file>
@@ -3655,7 +3959,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3727,6 +4031,7 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -3786,6 +4091,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -4107,9 +4416,6 @@
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="2">
-        <v>7.26107007E8</v>
-      </c>
       <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
@@ -4177,25 +4483,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>762</v>
+        <v>820</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>795</v>
+        <v>853</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>818</v>
+        <v>882</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>819</v>
+        <v>883</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>820</v>
+        <v>884</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>821</v>
+        <v>885</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>798</v>
+        <v>856</v>
       </c>
     </row>
     <row r="2">
@@ -4203,10 +4509,10 @@
         <v>574</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>822</v>
+        <v>886</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>823</v>
+        <v>887</v>
       </c>
       <c r="D2" s="8">
         <v>0.2916666666666667</v>
@@ -4223,10 +4529,10 @@
         <v>574</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>822</v>
+        <v>886</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>824</v>
+        <v>888</v>
       </c>
       <c r="D3" s="8">
         <v>0.2916666666666667</v>
@@ -4243,10 +4549,10 @@
         <v>574</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>822</v>
+        <v>886</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>825</v>
+        <v>889</v>
       </c>
       <c r="D4" s="8">
         <v>0.2916666666666667</v>
@@ -4263,10 +4569,10 @@
         <v>574</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>822</v>
+        <v>886</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>826</v>
+        <v>890</v>
       </c>
       <c r="D5" s="8">
         <v>0.2916666666666667</v>
@@ -4283,10 +4589,10 @@
         <v>574</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>822</v>
+        <v>886</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>827</v>
+        <v>891</v>
       </c>
       <c r="D6" s="8">
         <v>0.2916666666666667</v>
@@ -4303,10 +4609,10 @@
         <v>574</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>822</v>
+        <v>886</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>828</v>
+        <v>892</v>
       </c>
       <c r="D7" s="8">
         <v>0.375</v>
@@ -4323,16 +4629,16 @@
         <v>574</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>822</v>
+        <v>886</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>829</v>
+        <v>893</v>
       </c>
       <c r="F8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>830</v>
+        <v>894</v>
       </c>
     </row>
     <row r="9">
@@ -4348,16 +4654,16 @@
         <v>751</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>831</v>
+        <v>895</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>823</v>
+        <v>887</v>
       </c>
       <c r="F10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>830</v>
+        <v>894</v>
       </c>
     </row>
     <row r="11">
@@ -4365,10 +4671,10 @@
         <v>751</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>831</v>
+        <v>895</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>824</v>
+        <v>888</v>
       </c>
       <c r="D11" s="8">
         <v>0.2916666666666667</v>
@@ -4385,10 +4691,10 @@
         <v>751</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>831</v>
+        <v>895</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>825</v>
+        <v>889</v>
       </c>
       <c r="D12" s="8">
         <v>0.2916666666666667</v>
@@ -4405,10 +4711,10 @@
         <v>751</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>831</v>
+        <v>895</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>826</v>
+        <v>890</v>
       </c>
       <c r="D13" s="8">
         <v>0.2916666666666667</v>
@@ -4425,10 +4731,10 @@
         <v>751</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>831</v>
+        <v>895</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>827</v>
+        <v>891</v>
       </c>
       <c r="D14" s="8">
         <v>0.2916666666666667</v>
@@ -4445,10 +4751,10 @@
         <v>751</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>831</v>
+        <v>895</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>828</v>
+        <v>892</v>
       </c>
       <c r="D15" s="8">
         <v>0.375</v>
@@ -4465,16 +4771,16 @@
         <v>751</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>831</v>
+        <v>895</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>829</v>
+        <v>893</v>
       </c>
       <c r="F16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>830</v>
+        <v>894</v>
       </c>
     </row>
   </sheetData>
@@ -4491,25 +4797,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>762</v>
+        <v>820</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>795</v>
+        <v>853</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>832</v>
+        <v>896</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>819</v>
+        <v>883</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>820</v>
+        <v>884</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>821</v>
+        <v>885</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>798</v>
+        <v>856</v>
       </c>
     </row>
     <row r="2">
@@ -4517,7 +4823,7 @@
         <v>574</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>822</v>
+        <v>886</v>
       </c>
       <c r="C2" s="10">
         <v>46187.0</v>
@@ -4526,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>830</v>
+        <v>894</v>
       </c>
     </row>
     <row r="3">
@@ -4534,7 +4840,7 @@
         <v>751</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>833</v>
+        <v>897</v>
       </c>
       <c r="C3" s="10">
         <v>46187.0</v>
@@ -4543,7 +4849,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>830</v>
+        <v>894</v>
       </c>
     </row>
     <row r="4">
@@ -4591,33 +4897,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>834</v>
+        <v>898</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>835</v>
+        <v>899</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>836</v>
+        <v>900</v>
       </c>
       <c r="E1" s="23" t="s">
-        <v>837</v>
+        <v>901</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>838</v>
+        <v>902</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>839</v>
+        <v>903</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>551</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>840</v>
+        <v>904</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>823</v>
+        <v>887</v>
       </c>
       <c r="G2" s="8">
         <v>0.2916666666666667</v>
@@ -4631,19 +4937,19 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>841</v>
+        <v>905</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>842</v>
+        <v>906</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>551</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>840</v>
+        <v>904</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>824</v>
+        <v>888</v>
       </c>
       <c r="G3" s="8">
         <v>0.2916666666666667</v>
@@ -4657,19 +4963,19 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>843</v>
+        <v>907</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>844</v>
+        <v>908</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>551</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>840</v>
+        <v>904</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>825</v>
+        <v>889</v>
       </c>
       <c r="G4" s="8">
         <v>0.2916666666666667</v>
@@ -4686,10 +4992,10 @@
         <v>551</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>840</v>
+        <v>904</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>826</v>
+        <v>890</v>
       </c>
       <c r="G5" s="8">
         <v>0.2916666666666667</v>
@@ -4706,10 +5012,10 @@
         <v>551</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>840</v>
+        <v>904</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>827</v>
+        <v>891</v>
       </c>
       <c r="G6" s="8">
         <v>0.2916666666666667</v>
@@ -4726,10 +5032,10 @@
         <v>551</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>840</v>
+        <v>904</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>828</v>
+        <v>892</v>
       </c>
       <c r="G7" s="8">
         <v>0.375</v>
@@ -4746,24 +5052,24 @@
         <v>551</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>840</v>
+        <v>904</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>829</v>
+        <v>893</v>
       </c>
       <c r="I8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>830</v>
+        <v>894</v>
       </c>
     </row>
     <row r="10">
       <c r="D10" s="23" t="s">
-        <v>836</v>
+        <v>900</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>845</v>
+        <v>909</v>
       </c>
     </row>
     <row r="12">
@@ -4771,7 +5077,7 @@
         <v>551</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>840</v>
+        <v>904</v>
       </c>
       <c r="F12" s="10">
         <v>46188.0</v>
@@ -4780,7 +5086,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>830</v>
+        <v>894</v>
       </c>
     </row>
     <row r="13">
@@ -4788,7 +5094,7 @@
         <v>551</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>840</v>
+        <v>904</v>
       </c>
       <c r="F13" s="10">
         <v>46189.0</v>
@@ -4803,52 +5109,52 @@
         <v>1</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>846</v>
+        <v>910</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>847</v>
+        <v>911</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>848</v>
+        <v>912</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>849</v>
+        <v>913</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>850</v>
+        <v>914</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>851</v>
+        <v>915</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>852</v>
+        <v>916</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>853</v>
+        <v>917</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>854</v>
+        <v>918</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>848</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -4868,31 +5174,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>762</v>
+        <v>820</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>760</v>
+        <v>818</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>780</v>
+        <v>838</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>781</v>
+        <v>839</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>782</v>
+        <v>840</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>793</v>
+        <v>851</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>855</v>
+        <v>919</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>785</v>
+        <v>843</v>
       </c>
     </row>
     <row r="2">
@@ -4903,20 +5209,20 @@
         <v>118</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>856</v>
+        <v>920</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>822</v>
+        <v>886</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>857</v>
+        <v>921</v>
       </c>
       <c r="F2" s="18">
         <f>+380111111111</f>
         <v>380111111111</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>858</v>
+        <v>922</v>
       </c>
       <c r="I2" s="13" t="b">
         <v>1</v>
@@ -4930,20 +5236,20 @@
         <v>118</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>833</v>
+        <v>897</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>833</v>
+        <v>897</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>859</v>
+        <v>923</v>
       </c>
       <c r="F3" s="18">
         <f>+380111111113</f>
         <v>380111111113</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>858</v>
+        <v>922</v>
       </c>
       <c r="I3" s="13" t="b">
         <v>1</v>
@@ -4966,22 +5272,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="s">
-        <v>860</v>
+        <v>924</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>861</v>
+        <v>925</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>862</v>
+        <v>926</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>863</v>
+        <v>927</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>864</v>
+        <v>928</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>800</v>
+        <v>858</v>
       </c>
     </row>
     <row r="2">
@@ -5023,979 +5329,1063 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>865</v>
+        <v>929</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>866</v>
+        <v>930</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>867</v>
+        <v>931</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>868</v>
+        <v>932</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>869</v>
+        <v>933</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>870</v>
+        <v>934</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>871</v>
+        <v>935</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>872</v>
+        <v>936</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>873</v>
+        <v>937</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>874</v>
+        <v>938</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>875</v>
+        <v>939</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>876</v>
+        <v>940</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>877</v>
+        <v>941</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>878</v>
+        <v>942</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>879</v>
+        <v>943</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>880</v>
+        <v>944</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>881</v>
+        <v>945</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>882</v>
+        <v>946</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>883</v>
+        <v>947</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>884</v>
+        <v>948</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>885</v>
+        <v>949</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>886</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>887</v>
+        <v>951</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>888</v>
+        <v>952</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>889</v>
+        <v>953</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>890</v>
+        <v>954</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>891</v>
+        <v>955</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>892</v>
+        <v>956</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>893</v>
+        <v>957</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>894</v>
+        <v>958</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>895</v>
+        <v>959</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>896</v>
+        <v>960</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>897</v>
+        <v>961</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>898</v>
+        <v>962</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>899</v>
+        <v>963</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>900</v>
+        <v>964</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>901</v>
+        <v>965</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>902</v>
+        <v>966</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>903</v>
+        <v>967</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>904</v>
+        <v>968</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>905</v>
+        <v>969</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>906</v>
+        <v>970</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>907</v>
+        <v>971</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>908</v>
+        <v>972</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>909</v>
+        <v>973</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>910</v>
+        <v>974</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>911</v>
+        <v>975</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>912</v>
+        <v>976</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>913</v>
+        <v>977</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>914</v>
+        <v>978</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>915</v>
+        <v>979</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>916</v>
+        <v>980</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>917</v>
+        <v>981</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>918</v>
+        <v>982</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>919</v>
+        <v>983</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>920</v>
+        <v>984</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>921</v>
+        <v>985</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>922</v>
+        <v>986</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>923</v>
+        <v>987</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>924</v>
+        <v>988</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>925</v>
+        <v>989</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>926</v>
+        <v>990</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>927</v>
+        <v>991</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>928</v>
+        <v>992</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>929</v>
+        <v>993</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>930</v>
+        <v>994</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>931</v>
+        <v>995</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>932</v>
+        <v>996</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>932</v>
+        <v>996</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>933</v>
+        <v>997</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>934</v>
+        <v>998</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>935</v>
+        <v>999</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>936</v>
+        <v>1000</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>937</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>938</v>
+        <v>1002</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>939</v>
+        <v>1003</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>940</v>
+        <v>1004</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>941</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>942</v>
+        <v>1006</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>943</v>
+        <v>1007</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>944</v>
+        <v>1008</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>945</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>946</v>
+        <v>1010</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>947</v>
+        <v>1011</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>948</v>
+        <v>1012</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>949</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>950</v>
+        <v>1014</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>951</v>
+        <v>1015</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>952</v>
+        <v>1016</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>953</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>954</v>
+        <v>1018</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>955</v>
+        <v>1019</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>955</v>
+        <v>1019</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>956</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>957</v>
+        <v>1021</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>958</v>
+        <v>1022</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>959</v>
+        <v>1023</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>960</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>961</v>
+        <v>1025</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>962</v>
+        <v>1026</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>963</v>
+        <v>1027</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>964</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>965</v>
+        <v>1029</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>966</v>
+        <v>1030</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>967</v>
+        <v>1031</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>968</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>969</v>
+        <v>1033</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>970</v>
+        <v>1034</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>971</v>
+        <v>1035</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>972</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>973</v>
+        <v>1037</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>974</v>
+        <v>1038</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>975</v>
+        <v>1039</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>976</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>977</v>
+        <v>1041</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>978</v>
+        <v>1042</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>979</v>
+        <v>1043</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>980</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>981</v>
+        <v>1045</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>982</v>
+        <v>1046</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>983</v>
+        <v>1047</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>984</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>985</v>
+        <v>1049</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>986</v>
+        <v>1050</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>987</v>
+        <v>1051</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>988</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>989</v>
+        <v>1053</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>990</v>
+        <v>1054</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>991</v>
+        <v>1055</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>992</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>993</v>
+        <v>1057</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>994</v>
+        <v>1058</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>995</v>
+        <v>1059</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>996</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>997</v>
+        <v>1061</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>998</v>
+        <v>1062</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>999</v>
+        <v>1063</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1000</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>1001</v>
+        <v>1065</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1002</v>
+        <v>1066</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1002</v>
+        <v>1066</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1003</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>1004</v>
+        <v>1068</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1005</v>
+        <v>1069</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1006</v>
+        <v>1070</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1007</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>1008</v>
+        <v>1072</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1009</v>
+        <v>1073</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1009</v>
+        <v>1073</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1010</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>1011</v>
+        <v>1075</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1012</v>
+        <v>1076</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1013</v>
+        <v>1077</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1014</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>1015</v>
+        <v>1079</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1016</v>
+        <v>1080</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1017</v>
+        <v>1081</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1018</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>1019</v>
+        <v>1083</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1020</v>
+        <v>1084</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1021</v>
+        <v>1085</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1022</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>1023</v>
+        <v>1087</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1024</v>
+        <v>1088</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1025</v>
+        <v>1089</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1026</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>1027</v>
+        <v>1091</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>1028</v>
+        <v>1092</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1029</v>
+        <v>1093</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1030</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>1031</v>
+        <v>1095</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1032</v>
+        <v>1096</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1033</v>
+        <v>1097</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1034</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>1035</v>
+        <v>1099</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1036</v>
+        <v>1100</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1037</v>
+        <v>1101</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1038</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>1039</v>
+        <v>1103</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1040</v>
+        <v>1104</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1041</v>
+        <v>1105</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1042</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>1043</v>
+        <v>1107</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>1044</v>
+        <v>1108</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1045</v>
+        <v>1109</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1046</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>1047</v>
+        <v>1111</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1048</v>
+        <v>1112</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1049</v>
+        <v>1113</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1050</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>1051</v>
+        <v>1115</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1052</v>
+        <v>1116</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1053</v>
+        <v>1117</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1054</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>1055</v>
+        <v>1119</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1056</v>
+        <v>1120</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1057</v>
+        <v>1121</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1058</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>1059</v>
+        <v>1123</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1060</v>
+        <v>1124</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1061</v>
+        <v>1125</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1062</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>1063</v>
+        <v>1127</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1064</v>
+        <v>1128</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1065</v>
+        <v>1129</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1066</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>1067</v>
+        <v>1131</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1068</v>
+        <v>1132</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1069</v>
+        <v>1133</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1070</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>1071</v>
+        <v>1135</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1072</v>
+        <v>1136</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1073</v>
+        <v>1137</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1074</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>1075</v>
+        <v>1139</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>1076</v>
+        <v>1140</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1077</v>
+        <v>1141</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1078</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>1079</v>
+        <v>1143</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1080</v>
+        <v>1144</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1081</v>
+        <v>1145</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1082</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>1083</v>
+        <v>1147</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1084</v>
+        <v>1148</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1085</v>
+        <v>1149</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1086</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>1087</v>
+        <v>1151</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1088</v>
+        <v>1152</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1089</v>
+        <v>1153</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1090</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>1091</v>
+        <v>1155</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1092</v>
+        <v>1156</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1093</v>
+        <v>1157</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1094</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>1095</v>
+        <v>1159</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1096</v>
+        <v>1160</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1097</v>
+        <v>1161</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1098</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>1099</v>
+        <v>1163</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1100</v>
+        <v>1164</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1101</v>
+        <v>1165</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1102</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>1103</v>
+        <v>1167</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1104</v>
+        <v>1168</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1105</v>
+        <v>1169</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1106</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>1107</v>
+        <v>1171</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1108</v>
+        <v>1172</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1109</v>
+        <v>1173</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1110</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>1111</v>
+        <v>1175</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1112</v>
+        <v>1176</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1113</v>
+        <v>1177</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1114</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>1115</v>
+        <v>1179</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1116</v>
+        <v>1180</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1117</v>
+        <v>1181</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1118</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>1119</v>
+        <v>1183</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1120</v>
+        <v>1184</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1121</v>
+        <v>1185</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1122</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>1123</v>
+        <v>1187</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1124</v>
+        <v>1188</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1125</v>
+        <v>1189</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1126</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>1127</v>
+        <v>1191</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1128</v>
+        <v>1192</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1129</v>
+        <v>1193</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1130</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>1131</v>
+        <v>1195</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1132</v>
+        <v>1196</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1132</v>
+        <v>1196</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1132</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>1133</v>
+        <v>1197</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1134</v>
+        <v>1198</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1135</v>
+        <v>1199</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1136</v>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>1211</v>
       </c>
     </row>
   </sheetData>
@@ -6010,78 +6400,197 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
+    <col customWidth="1" min="3" max="3" width="15.88"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C2" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="D2" s="25"/>
+      <c r="E2" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C5" s="2">
+        <v>8.3456789E8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
     <col customWidth="1" min="2" max="2" width="17.38"/>
     <col customWidth="1" min="4" max="4" width="16.88"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>779</v>
+        <v>837</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1137</v>
+        <v>1224</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>785</v>
+        <v>843</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>798</v>
+        <v>856</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1138</v>
+        <v>1225</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1139</v>
+        <v>1226</v>
       </c>
       <c r="C2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1140</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>1139</v>
+        <v>1226</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1138</v>
+        <v>1225</v>
       </c>
       <c r="C3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1140</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>1141</v>
+        <v>1228</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1142</v>
+        <v>1229</v>
       </c>
       <c r="C5" s="2" t="b">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1143</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>1142</v>
+        <v>1229</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1141</v>
+        <v>1228</v>
       </c>
       <c r="C6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1143</v>
+        <v>1230</v>
       </c>
     </row>
   </sheetData>
@@ -6089,7 +6598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -6109,37 +6618,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>760</v>
+        <v>818</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1144</v>
+        <v>1231</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1145</v>
+        <v>1232</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1146</v>
+        <v>1233</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1147</v>
+        <v>1234</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1148</v>
+        <v>1235</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1149</v>
+        <v>1236</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1150</v>
+        <v>1237</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>1151</v>
+        <v>1238</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>1152</v>
+        <v>1239</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>785</v>
+        <v>843</v>
       </c>
     </row>
     <row r="2">
@@ -6147,25 +6656,25 @@
         <v>118</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1131</v>
+        <v>1195</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1133</v>
+        <v>1197</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1153</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>1154</v>
+        <v>1240</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>1241</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1155</v>
-      </c>
-      <c r="G2" s="25" t="s">
-        <v>1156</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>1157</v>
+        <v>1242</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>1244</v>
       </c>
       <c r="I2" s="2">
         <v>3.80000000001E11</v>
@@ -6174,7 +6683,7 @@
         <v>3.80000000002E11</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>1158</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="3">
@@ -9142,7 +9651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -9159,34 +9668,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>779</v>
+        <v>837</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1159</v>
+        <v>1213</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>793</v>
+        <v>851</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1160</v>
+        <v>1246</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1161</v>
+        <v>1247</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>800</v>
+        <v>858</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>798</v>
+        <v>856</v>
       </c>
     </row>
     <row r="2">
@@ -9197,10 +9706,10 @@
         <v>7.75285374E9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1162</v>
+        <v>1248</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>1163</v>
+        <v>1249</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -9212,7 +9721,7 @@
         <v>46188.92779366898</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
     </row>
     <row r="3">
@@ -9223,10 +9732,10 @@
         <v>7.75285374E9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1164</v>
+        <v>1250</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>1165</v>
+        <v>1251</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -9238,7 +9747,7 @@
         <v>46188.71443525463</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
     </row>
     <row r="4">
@@ -9249,10 +9758,10 @@
         <v>7.75285374E9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1166</v>
+        <v>1252</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>1167</v>
+        <v>1253</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -9264,7 +9773,7 @@
         <v>46188.90845820602</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
     </row>
     <row r="5">
@@ -9275,10 +9784,10 @@
         <v>7.75285374E9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1168</v>
+        <v>1254</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>1169</v>
+        <v>1255</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -9290,28 +9799,112 @@
         <v>46189.317849768515</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="B6" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46189.43934060185</v>
+      </c>
+      <c r="G6" s="6">
+        <v>46189.43934060185</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B7" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46189.50187771991</v>
+      </c>
+      <c r="G7" s="6">
+        <v>46189.50187771991</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="D6" s="12"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7">
-      <c r="D7" s="12"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8">
-      <c r="D8" s="12"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
+      <c r="B8" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46189.54013206018</v>
+      </c>
+      <c r="G8" s="6">
+        <v>46189.54013206018</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>860</v>
+      </c>
     </row>
     <row r="9">
-      <c r="D9" s="12"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
+      <c r="A9" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="B9" s="2">
+        <v>7.75285374E9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46189.59161953704</v>
+      </c>
+      <c r="G9" s="6">
+        <v>46189.59161953704</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>860</v>
+      </c>
     </row>
     <row r="10">
       <c r="D10" s="12"/>
@@ -12355,322 +12948,6 @@
     </row>
     <row r="996">
       <c r="D996" s="12"/>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="7" max="7" width="14.0"/>
-    <col customWidth="1" min="8" max="8" width="16.5"/>
-    <col customWidth="1" min="10" max="10" width="36.63"/>
-    <col customWidth="1" min="13" max="13" width="23.5"/>
-    <col customWidth="1" min="14" max="14" width="18.38"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="14" t="s">
-        <v>861</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>799</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>779</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>761</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>762</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>760</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>1170</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>1171</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>800</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>1172</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G2" s="26">
-        <v>46191.354166666664</v>
-      </c>
-      <c r="H2" s="26">
-        <v>46191.645833333336</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="K2" s="6">
-        <v>46188.65666847222</v>
-      </c>
-      <c r="L2" s="6">
-        <v>46188.97535425926</v>
-      </c>
-      <c r="N2" s="21"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1175</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G3" s="26">
-        <v>46189.416666666664</v>
-      </c>
-      <c r="H3" s="26">
-        <v>46189.708333333336</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>1176</v>
-      </c>
-      <c r="K3" s="6">
-        <v>46188.66288041667</v>
-      </c>
-      <c r="L3" s="6">
-        <v>46188.67364415509</v>
-      </c>
-      <c r="N3" s="21">
-        <v>46188.673639305554</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>1177</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G4" s="26">
-        <v>46188.75</v>
-      </c>
-      <c r="H4" s="26">
-        <v>46188.805555555555</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>1178</v>
-      </c>
-      <c r="K4" s="6">
-        <v>46188.71468287037</v>
-      </c>
-      <c r="L4" s="6">
-        <v>46188.71474319445</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1179</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G5" s="26">
-        <v>46190.458333333336</v>
-      </c>
-      <c r="H5" s="26">
-        <v>46190.583333333336</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>1180</v>
-      </c>
-      <c r="K5" s="6">
-        <v>46188.90875628473</v>
-      </c>
-      <c r="L5" s="6">
-        <v>46189.34027366898</v>
-      </c>
-      <c r="N5" s="21">
-        <v>46189.34027032407</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G6" s="26">
-        <v>46192.375</v>
-      </c>
-      <c r="H6" s="26">
-        <v>46192.666666666664</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>1181</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>1182</v>
-      </c>
-      <c r="K6" s="6">
-        <v>46188.928415312505</v>
-      </c>
-      <c r="L6" s="6">
-        <v>46188.934881203706</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G7" s="26">
-        <v>46189.5</v>
-      </c>
-      <c r="H7" s="26">
-        <v>46189.625</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="K7" s="6">
-        <v>46189.31825292824</v>
-      </c>
-      <c r="L7" s="6">
-        <v>46189.31830775463</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-    </row>
-    <row r="9">
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-    </row>
-    <row r="10">
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -12705,7 +12982,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="6">
-        <v>46189.31808834491</v>
+        <v>46189.591767499995</v>
       </c>
     </row>
     <row r="3">
@@ -12715,6 +12992,465 @@
       <c r="B3" s="2"/>
       <c r="C3" s="6">
         <v>46187.922235034726</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="7" max="7" width="14.0"/>
+    <col customWidth="1" min="8" max="8" width="16.5"/>
+    <col customWidth="1" min="10" max="10" width="36.63"/>
+    <col customWidth="1" min="13" max="13" width="23.5"/>
+    <col customWidth="1" min="14" max="14" width="18.38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="s">
+        <v>925</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>857</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>837</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>819</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>820</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>818</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>858</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>1266</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="27">
+        <v>46191.354166666664</v>
+      </c>
+      <c r="H2" s="27">
+        <v>46191.645833333336</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="K2" s="6">
+        <v>46188.65666847222</v>
+      </c>
+      <c r="L2" s="6">
+        <v>46188.97535425926</v>
+      </c>
+      <c r="N2" s="21"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="27">
+        <v>46189.416666666664</v>
+      </c>
+      <c r="H3" s="27">
+        <v>46189.708333333336</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>1270</v>
+      </c>
+      <c r="K3" s="6">
+        <v>46188.66288041667</v>
+      </c>
+      <c r="L3" s="6">
+        <v>46188.67364415509</v>
+      </c>
+      <c r="N3" s="21">
+        <v>46188.673639305554</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G4" s="27">
+        <v>46188.75</v>
+      </c>
+      <c r="H4" s="27">
+        <v>46188.805555555555</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K4" s="6">
+        <v>46188.71468287037</v>
+      </c>
+      <c r="L4" s="6">
+        <v>46188.71474319445</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5" s="27">
+        <v>46190.333333333336</v>
+      </c>
+      <c r="H5" s="27">
+        <v>46190.458333333336</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="K5" s="6">
+        <v>46188.90875628473</v>
+      </c>
+      <c r="L5" s="6">
+        <v>46189.42359324074</v>
+      </c>
+      <c r="N5" s="21">
+        <v>46189.42359116898</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G6" s="27">
+        <v>46192.375</v>
+      </c>
+      <c r="H6" s="27">
+        <v>46192.666666666664</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="K6" s="6">
+        <v>46188.928415312505</v>
+      </c>
+      <c r="L6" s="6">
+        <v>46188.934881203706</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G7" s="27">
+        <v>46189.5</v>
+      </c>
+      <c r="H7" s="27">
+        <v>46189.625</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="K7" s="6">
+        <v>46189.31825292824</v>
+      </c>
+      <c r="L7" s="6">
+        <v>46189.31830775463</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" s="27">
+        <v>46190.458333333336</v>
+      </c>
+      <c r="H8" s="27">
+        <v>46190.51388888889</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="K8" s="6">
+        <v>46189.43969520833</v>
+      </c>
+      <c r="L8" s="6">
+        <v>46189.44460809028</v>
+      </c>
+      <c r="N8" s="21">
+        <v>46189.44460364583</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G9" s="27">
+        <v>46190.333333333336</v>
+      </c>
+      <c r="H9" s="27">
+        <v>46190.38888888889</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="K9" s="6">
+        <v>46189.50223225694</v>
+      </c>
+      <c r="L9" s="6">
+        <v>46189.50698366898</v>
+      </c>
+      <c r="N9" s="21">
+        <v>46189.50697722222</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="27">
+        <v>46190.520833333336</v>
+      </c>
+      <c r="H10" s="27">
+        <v>46190.645833333336</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="K10" s="6">
+        <v>46189.540449513894</v>
+      </c>
+      <c r="L10" s="6">
+        <v>46189.548547847226</v>
+      </c>
+      <c r="N10" s="21">
+        <v>46189.54854243055</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G11" s="27">
+        <v>46190.5625</v>
+      </c>
+      <c r="H11" s="27">
+        <v>46190.6875</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="K11" s="6">
+        <v>46189.59220993056</v>
+      </c>
+      <c r="L11" s="6">
+        <v>46189.59237387731</v>
       </c>
     </row>
   </sheetData>
@@ -30632,6 +31368,1414 @@
       </c>
       <c r="C1632" s="2" t="s">
         <v>759</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" s="6">
+        <v>46189.42041331019</v>
+      </c>
+      <c r="B1633" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1633" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" s="6">
+        <v>46189.42050277778</v>
+      </c>
+      <c r="B1634" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1634" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" s="6">
+        <v>46189.42060414352</v>
+      </c>
+      <c r="B1635" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1635" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="6">
+        <v>46189.42063386574</v>
+      </c>
+      <c r="B1636" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1636" s="2">
+        <v>9.98765643E8</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="6">
+        <v>46189.42095113426</v>
+      </c>
+      <c r="B1637" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1637" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" s="6">
+        <v>46189.421040925925</v>
+      </c>
+      <c r="B1638" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1638" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="6">
+        <v>46189.42118422454</v>
+      </c>
+      <c r="B1639" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1639" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" s="6">
+        <v>46189.42121905093</v>
+      </c>
+      <c r="B1640" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1640" s="2">
+        <v>9.98765643E8</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" s="6">
+        <v>46189.421349861106</v>
+      </c>
+      <c r="B1641" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1641" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" s="6">
+        <v>46189.42135755787</v>
+      </c>
+      <c r="B1642" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C1642" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" s="6">
+        <v>46189.42138319444</v>
+      </c>
+      <c r="B1643" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C1643" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" s="6">
+        <v>46189.421410625</v>
+      </c>
+      <c r="B1644" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1644" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="6">
+        <v>46189.42141542824</v>
+      </c>
+      <c r="B1645" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C1645" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" s="6">
+        <v>46189.42161179398</v>
+      </c>
+      <c r="B1646" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1646" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="6">
+        <v>46189.421756192125</v>
+      </c>
+      <c r="B1647" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C1647" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="6">
+        <v>46189.421759282406</v>
+      </c>
+      <c r="B1648" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C1648" s="2" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="6">
+        <v>46189.421820069445</v>
+      </c>
+      <c r="B1649" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1649" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="6">
+        <v>46189.421861932875</v>
+      </c>
+      <c r="B1650" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C1650" s="8">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="6">
+        <v>46189.42186847222</v>
+      </c>
+      <c r="B1651" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C1651" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="6">
+        <v>46189.42188017361</v>
+      </c>
+      <c r="B1652" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C1652" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="6">
+        <v>46189.42200064815</v>
+      </c>
+      <c r="B1653" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C1653" s="2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="6">
+        <v>46189.4372434375</v>
+      </c>
+      <c r="B1654" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1654" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="6">
+        <v>46189.43735158565</v>
+      </c>
+      <c r="B1655" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1655" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="6">
+        <v>46189.43751741898</v>
+      </c>
+      <c r="B1656" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1656" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" s="6">
+        <v>46189.43767627315</v>
+      </c>
+      <c r="B1657" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1657" s="2" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="6">
+        <v>46189.43776744213</v>
+      </c>
+      <c r="B1658" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1658" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="6">
+        <v>46189.437807650465</v>
+      </c>
+      <c r="B1659" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1659" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="6">
+        <v>46189.4379091088</v>
+      </c>
+      <c r="B1660" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1660" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="6">
+        <v>46189.43807336806</v>
+      </c>
+      <c r="B1661" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1661" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="6">
+        <v>46189.43822335648</v>
+      </c>
+      <c r="B1662" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1662" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" s="6">
+        <v>46189.4382750463</v>
+      </c>
+      <c r="B1663" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1663" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="6">
+        <v>46189.43830335648</v>
+      </c>
+      <c r="B1664" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C1664" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="6">
+        <v>46189.43830925926</v>
+      </c>
+      <c r="B1665" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C1665" s="2">
+        <v>80.0</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="6">
+        <v>46189.43836642361</v>
+      </c>
+      <c r="B1666" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C1666" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="6">
+        <v>46189.438368773146</v>
+      </c>
+      <c r="B1667" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C1667" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="6">
+        <v>46189.43837113426</v>
+      </c>
+      <c r="B1668" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1668" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="6">
+        <v>46189.43844587963</v>
+      </c>
+      <c r="B1669" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1669" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="6">
+        <v>46189.43861340277</v>
+      </c>
+      <c r="B1670" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1670" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="6">
+        <v>46189.438741192134</v>
+      </c>
+      <c r="B1671" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1671" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="6">
+        <v>46189.43880565972</v>
+      </c>
+      <c r="B1672" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1672" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="6">
+        <v>46189.438830949075</v>
+      </c>
+      <c r="B1673" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C1673" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="6">
+        <v>46189.43883988426</v>
+      </c>
+      <c r="B1674" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C1674" s="2">
+        <v>80.0</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="6">
+        <v>46189.43892153935</v>
+      </c>
+      <c r="B1675" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C1675" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="6">
+        <v>46189.438925995375</v>
+      </c>
+      <c r="B1676" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C1676" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="6">
+        <v>46189.43893909722</v>
+      </c>
+      <c r="B1677" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1677" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="6">
+        <v>46189.43904747685</v>
+      </c>
+      <c r="B1678" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1678" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="6">
+        <v>46189.439185428244</v>
+      </c>
+      <c r="B1679" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1679" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="6">
+        <v>46189.43929608796</v>
+      </c>
+      <c r="B1680" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1680" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="6">
+        <v>46189.43932873843</v>
+      </c>
+      <c r="B1681" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1681" s="2" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="6">
+        <v>46189.439344768514</v>
+      </c>
+      <c r="B1682" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1682" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="6">
+        <v>46189.43935748843</v>
+      </c>
+      <c r="B1683" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1683" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" s="6">
+        <v>46189.439371851855</v>
+      </c>
+      <c r="B1684" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1684" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="6">
+        <v>46189.43963842593</v>
+      </c>
+      <c r="B1685" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1685" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="6">
+        <v>46189.43966234954</v>
+      </c>
+      <c r="B1686" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C1686" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="6">
+        <v>46189.499999884254</v>
+      </c>
+      <c r="B1687" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1687" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="6">
+        <v>46189.50011166667</v>
+      </c>
+      <c r="B1688" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1688" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="6">
+        <v>46189.50035030092</v>
+      </c>
+      <c r="B1689" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1689" s="2" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="6">
+        <v>46189.500521215276</v>
+      </c>
+      <c r="B1690" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1690" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="6">
+        <v>46189.500704687496</v>
+      </c>
+      <c r="B1691" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1691" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="6">
+        <v>46189.500745613426</v>
+      </c>
+      <c r="B1692" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1692" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="6">
+        <v>46189.50091971065</v>
+      </c>
+      <c r="B1693" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1693" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="6">
+        <v>46189.5010768287</v>
+      </c>
+      <c r="B1694" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1694" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="6">
+        <v>46189.501259236116</v>
+      </c>
+      <c r="B1695" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1695" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="6">
+        <v>46189.50129934028</v>
+      </c>
+      <c r="B1696" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1696" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="6">
+        <v>46189.50130732638</v>
+      </c>
+      <c r="B1697" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C1697" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="6">
+        <v>46189.501311678236</v>
+      </c>
+      <c r="B1698" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C1698" s="2">
+        <v>80.0</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="6">
+        <v>46189.50134607639</v>
+      </c>
+      <c r="B1699" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C1699" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="6">
+        <v>46189.50134831019</v>
+      </c>
+      <c r="B1700" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C1700" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="6">
+        <v>46189.50135064815</v>
+      </c>
+      <c r="B1701" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1701" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="6">
+        <v>46189.50153350695</v>
+      </c>
+      <c r="B1702" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1702" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="6">
+        <v>46189.501733171295</v>
+      </c>
+      <c r="B1703" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1703" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" s="6">
+        <v>46189.501828333334</v>
+      </c>
+      <c r="B1704" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1704" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="6">
+        <v>46189.501870231485</v>
+      </c>
+      <c r="B1705" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1705" s="2" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="6">
+        <v>46189.501881122684</v>
+      </c>
+      <c r="B1706" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1706" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="6">
+        <v>46189.501893912035</v>
+      </c>
+      <c r="B1707" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1707" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="6">
+        <v>46189.50190120371</v>
+      </c>
+      <c r="B1708" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1708" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="6">
+        <v>46189.50218600694</v>
+      </c>
+      <c r="B1709" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1709" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="6">
+        <v>46189.50219594907</v>
+      </c>
+      <c r="B1710" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C1710" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="6">
+        <v>46189.538204375</v>
+      </c>
+      <c r="B1711" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1711" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="6">
+        <v>46189.53830594907</v>
+      </c>
+      <c r="B1712" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1712" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="6">
+        <v>46189.53843197916</v>
+      </c>
+      <c r="B1713" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1713" s="2" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="6">
+        <v>46189.53861754629</v>
+      </c>
+      <c r="B1714" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1714" s="2" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="6">
+        <v>46189.53875234954</v>
+      </c>
+      <c r="B1715" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1715" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="6">
+        <v>46189.53878267361</v>
+      </c>
+      <c r="B1716" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1716" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="6">
+        <v>46189.538854722225</v>
+      </c>
+      <c r="B1717" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1717" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="6">
+        <v>46189.5390400926</v>
+      </c>
+      <c r="B1718" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1718" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="6">
+        <v>46189.53950503472</v>
+      </c>
+      <c r="B1719" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1719" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="6">
+        <v>46189.539552835646</v>
+      </c>
+      <c r="B1720" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1720" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="6">
+        <v>46189.53956833333</v>
+      </c>
+      <c r="B1721" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C1721" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="6">
+        <v>46189.53957399305</v>
+      </c>
+      <c r="B1722" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C1722" s="2">
+        <v>180.0</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="6">
+        <v>46189.53962517361</v>
+      </c>
+      <c r="B1723" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C1723" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="6">
+        <v>46189.53962840278</v>
+      </c>
+      <c r="B1724" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C1724" s="2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="6">
+        <v>46189.5396309375</v>
+      </c>
+      <c r="B1725" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1725" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="6">
+        <v>46189.5398124537</v>
+      </c>
+      <c r="B1726" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1726" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="6">
+        <v>46189.539949976854</v>
+      </c>
+      <c r="B1727" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1727" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="6">
+        <v>46189.540092627314</v>
+      </c>
+      <c r="B1728" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1728" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="6">
+        <v>46189.540117384255</v>
+      </c>
+      <c r="B1729" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1729" s="2" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="6">
+        <v>46189.54013537037</v>
+      </c>
+      <c r="B1730" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1730" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="6">
+        <v>46189.54014603009</v>
+      </c>
+      <c r="B1731" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1731" s="2" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="6">
+        <v>46189.540153553244</v>
+      </c>
+      <c r="B1732" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1732" s="2" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="6">
+        <v>46189.54042979167</v>
+      </c>
+      <c r="B1733" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1733" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="6">
+        <v>46189.540438020835</v>
+      </c>
+      <c r="B1734" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C1734" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="6">
+        <v>46189.58975408565</v>
+      </c>
+      <c r="B1735" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1735" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="6">
+        <v>46189.58991427084</v>
+      </c>
+      <c r="B1736" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1736" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="6">
+        <v>46189.59014035879</v>
+      </c>
+      <c r="B1737" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1737" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="6">
+        <v>46189.59028755787</v>
+      </c>
+      <c r="B1738" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1738" s="2" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="6">
+        <v>46189.590393101855</v>
+      </c>
+      <c r="B1739" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1739" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="6">
+        <v>46189.59042104166</v>
+      </c>
+      <c r="B1740" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1740" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="6">
+        <v>46189.59049519676</v>
+      </c>
+      <c r="B1741" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1741" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="6">
+        <v>46189.59062715278</v>
+      </c>
+      <c r="B1742" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1742" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="6">
+        <v>46189.59082894676</v>
+      </c>
+      <c r="B1743" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1743" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="6">
+        <v>46189.59086965278</v>
+      </c>
+      <c r="B1744" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1744" s="2" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="6">
+        <v>46189.59088364583</v>
+      </c>
+      <c r="B1745" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C1745" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="6">
+        <v>46189.59088912037</v>
+      </c>
+      <c r="B1746" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C1746" s="2">
+        <v>180.0</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="6">
+        <v>46189.59093119213</v>
+      </c>
+      <c r="B1747" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C1747" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="6">
+        <v>46189.59093414352</v>
+      </c>
+      <c r="B1748" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C1748" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="6">
+        <v>46189.59093688657</v>
+      </c>
+      <c r="B1749" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1749" s="2" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="6">
+        <v>46189.5913134838</v>
+      </c>
+      <c r="B1750" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1750" s="2" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="6">
+        <v>46189.59146753472</v>
+      </c>
+      <c r="B1751" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1751" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="6">
+        <v>46189.59156840278</v>
+      </c>
+      <c r="B1752" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1752" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="6">
+        <v>46189.591610497686</v>
+      </c>
+      <c r="B1753" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1753" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="6">
+        <v>46189.591623541666</v>
+      </c>
+      <c r="B1754" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1754" s="2" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="6">
+        <v>46189.59163383102</v>
+      </c>
+      <c r="B1755" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1755" s="2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="6">
+        <v>46189.591643611115</v>
+      </c>
+      <c r="B1756" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1756" s="2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="6">
+        <v>46189.592181493055</v>
+      </c>
+      <c r="B1757" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1757" s="2" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="6">
+        <v>46189.59219011574</v>
+      </c>
+      <c r="B1758" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C1758" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="6">
+        <v>46189.592677175926</v>
+      </c>
+      <c r="B1759" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1759" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="6">
+        <v>46189.59268736111</v>
+      </c>
+      <c r="B1760" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C1760" s="2" t="s">
+        <v>816</v>
       </c>
     </row>
   </sheetData>
@@ -30659,64 +32803,64 @@
         <v>28</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>760</v>
+        <v>818</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>761</v>
+        <v>819</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>762</v>
+        <v>820</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>763</v>
+        <v>821</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>764</v>
+        <v>822</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>765</v>
+        <v>823</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>766</v>
+        <v>824</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>767</v>
+        <v>825</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>768</v>
+        <v>826</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>769</v>
+        <v>827</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>770</v>
+        <v>828</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>771</v>
+        <v>829</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>772</v>
+        <v>830</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>773</v>
+        <v>831</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>774</v>
+        <v>832</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>775</v>
+        <v>833</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>776</v>
+        <v>834</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>777</v>
+        <v>835</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>778</v>
+        <v>836</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>779</v>
+        <v>837</v>
       </c>
     </row>
     <row r="2">
@@ -33737,39 +35881,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>761</v>
+        <v>819</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>780</v>
+        <v>838</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>781</v>
+        <v>839</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>782</v>
+        <v>840</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>783</v>
+        <v>841</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>784</v>
+        <v>842</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>785</v>
+        <v>843</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="s">
-        <v>786</v>
+        <v>844</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>787</v>
+        <v>845</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>787</v>
+        <v>845</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>788</v>
+        <v>846</v>
       </c>
       <c r="E2" s="17">
         <v>80.0</v>
@@ -33783,16 +35927,16 @@
     </row>
     <row r="3">
       <c r="A3" s="15" t="s">
-        <v>789</v>
+        <v>847</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>790</v>
+        <v>848</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>791</v>
+        <v>849</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>792</v>
+        <v>850</v>
       </c>
       <c r="E3" s="17">
         <v>180.0</v>
@@ -33823,37 +35967,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>779</v>
+        <v>837</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>776</v>
+        <v>834</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>793</v>
+        <v>851</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>761</v>
+        <v>819</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>794</v>
+        <v>852</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>762</v>
+        <v>820</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>795</v>
+        <v>853</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>796</v>
+        <v>854</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>797</v>
+        <v>855</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>798</v>
+        <v>856</v>
       </c>
     </row>
     <row r="2">
@@ -33862,7 +36006,7 @@
       </c>
       <c r="C2" s="19"/>
       <c r="D2" s="2" t="s">
-        <v>789</v>
+        <v>847</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>574</v>
@@ -33894,28 +36038,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>799</v>
+        <v>857</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>779</v>
+        <v>837</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>761</v>
+        <v>819</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>762</v>
+        <v>820</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>760</v>
+        <v>818</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>800</v>
+        <v>858</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>778</v>
+        <v>836</v>
       </c>
     </row>
     <row r="2">
@@ -33926,7 +36070,7 @@
         <v>650</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>789</v>
+        <v>847</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>574</v>
@@ -33935,7 +36079,7 @@
         <v>118</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="G2" s="6">
         <v>46188.65644706019</v>
@@ -33949,7 +36093,7 @@
         <v>650</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>789</v>
+        <v>847</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>574</v>
@@ -33958,7 +36102,7 @@
         <v>118</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="G3" s="6">
         <v>46188.662697928245</v>
@@ -33972,7 +36116,7 @@
         <v>688</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>786</v>
+        <v>844</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>574</v>
@@ -33981,7 +36125,7 @@
         <v>118</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="G4" s="6">
         <v>46188.714445289355</v>
@@ -33995,7 +36139,7 @@
         <v>700</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>789</v>
+        <v>847</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>574</v>
@@ -34004,7 +36148,7 @@
         <v>118</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="G5" s="6">
         <v>46188.9084655787</v>
@@ -34018,7 +36162,7 @@
         <v>650</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>789</v>
+        <v>847</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>574</v>
@@ -34027,7 +36171,7 @@
         <v>118</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="G6" s="6">
         <v>46188.92779746528</v>
@@ -34041,7 +36185,7 @@
         <v>756</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>789</v>
+        <v>847</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>751</v>
@@ -34050,23 +36194,103 @@
         <v>118</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="G7" s="6">
         <v>46189.31786376158</v>
       </c>
     </row>
     <row r="8">
-      <c r="G8" s="6"/>
+      <c r="A8" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="G8" s="6">
+        <v>46189.43935428241</v>
+      </c>
     </row>
     <row r="9">
-      <c r="G9" s="6"/>
+      <c r="A9" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="G9" s="6">
+        <v>46189.50189128472</v>
+      </c>
     </row>
     <row r="10">
-      <c r="G10" s="6"/>
+      <c r="A10" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="G10" s="6">
+        <v>46189.540140439814</v>
+      </c>
     </row>
     <row r="11">
-      <c r="G11" s="6"/>
+      <c r="A11" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="G11" s="6">
+        <v>46189.59163065972</v>
+      </c>
     </row>
     <row r="12">
       <c r="G12" s="6"/>
@@ -34146,36 +36370,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>803</v>
+        <v>861</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>799</v>
+        <v>857</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>804</v>
+        <v>862</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>805</v>
+        <v>863</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>806</v>
+        <v>864</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>800</v>
+        <v>858</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>807</v>
+        <v>865</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>651</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>808</v>
+        <v>866</v>
       </c>
       <c r="D2" s="20">
         <v>0.2916666666678793</v>
@@ -34184,7 +36408,7 @@
         <v>1.0</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>809</v>
+        <v>867</v>
       </c>
       <c r="G2" s="6">
         <v>46188.65645473379</v>
@@ -34192,13 +36416,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>810</v>
+        <v>868</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>665</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>808</v>
+        <v>866</v>
       </c>
       <c r="D3" s="20">
         <v>0.4166666666678793</v>
@@ -34207,7 +36431,7 @@
         <v>1.0</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>809</v>
+        <v>867</v>
       </c>
       <c r="G3" s="6">
         <v>46188.662710046294</v>
@@ -34215,13 +36439,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>811</v>
+        <v>869</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>689</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>812</v>
+        <v>870</v>
       </c>
       <c r="D4" s="20">
         <v>0.75</v>
@@ -34230,7 +36454,7 @@
         <v>1.0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>809</v>
+        <v>867</v>
       </c>
       <c r="G4" s="6">
         <v>46188.71445289352</v>
@@ -34238,13 +36462,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>813</v>
+        <v>871</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>701</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>814</v>
+        <v>872</v>
       </c>
       <c r="D5" s="20">
         <v>0.4583333333321207</v>
@@ -34253,7 +36477,7 @@
         <v>1.0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>809</v>
+        <v>867</v>
       </c>
       <c r="G5" s="6">
         <v>46188.90847733796</v>
@@ -34261,13 +36485,13 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>815</v>
+        <v>873</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>713</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>816</v>
+        <v>874</v>
       </c>
       <c r="D6" s="20">
         <v>0.3333333333321207</v>
@@ -34276,7 +36500,7 @@
         <v>1.0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>809</v>
+        <v>867</v>
       </c>
       <c r="G6" s="6">
         <v>46188.9278031713</v>
@@ -34284,13 +36508,13 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>817</v>
+        <v>875</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>757</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>808</v>
+        <v>866</v>
       </c>
       <c r="D7" s="20">
         <v>0.5</v>
@@ -34299,36 +36523,126 @@
         <v>1.0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>809</v>
+        <v>867</v>
       </c>
       <c r="G7" s="6">
         <v>46189.317873692125</v>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="21"/>
-      <c r="D8" s="20"/>
-      <c r="G8" s="6"/>
+      <c r="A8" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="D8" s="20">
+        <v>0.4583333333321207</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="G8" s="6">
+        <v>46189.43936521991</v>
+      </c>
     </row>
     <row r="9">
-      <c r="C9" s="21"/>
-      <c r="D9" s="20"/>
-      <c r="G9" s="6"/>
+      <c r="A9" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="D9" s="20">
+        <v>0.5833333333321207</v>
+      </c>
+      <c r="E9" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="G9" s="6">
+        <v>46189.43936521991</v>
+      </c>
     </row>
     <row r="10">
-      <c r="C10" s="21"/>
-      <c r="D10" s="20"/>
-      <c r="G10" s="6"/>
+      <c r="A10" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="D10" s="20">
+        <v>0.3333333333321207</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="G10" s="6">
+        <v>46189.50189868055</v>
+      </c>
     </row>
     <row r="11">
-      <c r="C11" s="21"/>
-      <c r="D11" s="20"/>
-      <c r="G11" s="6"/>
+      <c r="A11" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="D11" s="20">
+        <v>0.5208333333321207</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="G11" s="6">
+        <v>46189.54015105324</v>
+      </c>
     </row>
     <row r="12">
-      <c r="C12" s="21"/>
-      <c r="D12" s="20"/>
-      <c r="G12" s="6"/>
+      <c r="A12" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="D12" s="20">
+        <v>0.5625</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="G12" s="6">
+        <v>46189.5916405787</v>
+      </c>
     </row>
     <row r="13">
       <c r="C13" s="21"/>
@@ -34539,13 +36853,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="s">
-        <v>762</v>
+        <v>820</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>761</v>
+        <v>819</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>785</v>
+        <v>843</v>
       </c>
     </row>
     <row r="2">
@@ -34553,7 +36867,7 @@
         <v>574</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>786</v>
+        <v>844</v>
       </c>
       <c r="C2" s="13" t="b">
         <v>1</v>
@@ -34564,7 +36878,7 @@
         <v>574</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>789</v>
+        <v>847</v>
       </c>
       <c r="C3" s="13" t="b">
         <v>1</v>
@@ -34575,7 +36889,7 @@
         <v>751</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>786</v>
+        <v>844</v>
       </c>
       <c r="C4" s="13" t="b">
         <v>1</v>
@@ -34586,7 +36900,7 @@
         <v>751</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>789</v>
+        <v>847</v>
       </c>
       <c r="C5" s="13" t="b">
         <v>1</v>

--- a/Docs/SmartFlow Beauty Demo.xlsx
+++ b/Docs/SmartFlow Beauty Demo.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7076" uniqueCount="2114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7192" uniqueCount="2168">
   <si>
     <t>key</t>
   </si>
@@ -82,7 +82,7 @@
     <t>AppsScriptUrl</t>
   </si>
   <si>
-    <t>https://script.google.com/macros/s/AKfycbznqKo-3n_ByZ6J4QcPdm70ol-uVny5ThAuhYblCPe61W8lHEEZCn0Md2ByKdp4N14B/exec</t>
+    <t>https://script.google.com/macros/s/AKfycbyC-jhQ_iwaJsxoDtW0HxNLQNRnPWRdUMZpfnmLj-_YlvrG4JqO6omyD2P10-piLWvc/exec</t>
   </si>
   <si>
     <t>OwnerTelegramId</t>
@@ -3319,6 +3319,99 @@
     <t>{"data":"confirm_cancel|appt_1782036944533","action":"confirm_cancel","requestId":"appt_1782036944533","ownerChatId":726107007}</t>
   </si>
   <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922221,\n\"message\":{\"message_id\":1298,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782038222,\"text\":\"\\ud83d\\udcc5 \\u0417\\u0430\\u043f\\u0438\\u0441\\u0438\"}}"}</t>
+  </si>
+  <si>
+    <t>{"text":"📅 Записи","state":""}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922222,\n\"message\":{\"message_id\":1300,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782038283,\"text\":\"\\ud83d\\udcc5 \\u0417\\u0430\\u043f\\u0438\\u0441\\u0438\"}}"}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922223,\n\"message\":{\"message_id\":1301,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782045107,\"text\":\"\\ud83d\\udcc5 \\u0417\\u0430\\u043f\\u0438\\u0441\\u0438\"}}"}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922224,\n\"message\":{\"message_id\":1302,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782045250,\"text\":\"\\ud83d\\udcc5 \\u0417\\u0430\\u043f\\u0438\\u0441\\u0438\"}}"}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922225,\n\"message\":{\"message_id\":1303,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782045419,\"text\":\"\\ud83d\\udcc5 \\u0417\\u0430\\u043f\\u0438\\u0441\\u0438\"}}"}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922226,\n\"message\":{\"message_id\":1304,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782045765,\"text\":\"\\ud83d\\udcc5 \\u0417\\u0430\\u043f\\u0438\\u0441\\u0438\"}}"}</t>
+  </si>
+  <si>
+    <t>ADMIN_APPOINTMENTS_DEBUG</t>
+  </si>
+  <si>
+    <t>{"text":"📅 Записи","appointmentsText":"📅 Записи","equal":true}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922227,\n\"message\":{\"message_id\":1305,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782047530,\"text\":\"\\ud83d\\udcc5 \\u0417\\u0430\\u043f\\u0438\\u0441\\u0438\"}}"}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922228,\n\"message\":{\"message_id\":1306,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782047568,\"text\":\"/start\",\"entities\":[{\"offset\":0,\"length\":6,\"type\":\"bot_command\"}]}}"}</t>
+  </si>
+  <si>
+    <t>{"text":"/start","appointmentsText":"📅 Записи","equal":false}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922229,\n\"message\":{\"message_id\":1308,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782047578,\"text\":\"\\ud83d\\udcc5 \\u0417\\u0430\\u043f\\u0438\\u0441\\u0438\"}}"}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922230,\n\"message\":{\"message_id\":1309,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782048708,\"text\":\"\\ud83d\\udcc5 \\u0417\\u0430\\u043f\\u0438\\u0441\\u0438\"}}"}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922231,\n\"message\":{\"message_id\":1310,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782049182,\"text\":\"\\ud83d\\udcc5 \\u0417\\u0430\\u043f\\u0438\\u0441\\u0438\"}}"}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922232,\n\"message\":{\"message_id\":1312,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782049715,\"text\":\"\\ud83c\\udfe0 \\u0413\\u043b\\u0430\\u0432\\u043d\\u043e\\u0435 \\u043c\\u0435\\u043d\\u044e\"}}"}</t>
+  </si>
+  <si>
+    <t>{"text":"🏠 Главное меню","appointmentsText":"📅 Записи","equal":false}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922233,\n\"message\":{\"message_id\":1314,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782049731,\"text\":\"\\ud83d\\udcc5 \\u0417\\u0430\\u043f\\u0438\\u0441\\u0438\"}}"}</t>
+  </si>
+  <si>
+    <t>APPOINTMENTS_KEYS_DEBUG</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922234,\n\"message\":{\"message_id\":1316,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782050210,\"text\":\"\\ud83c\\udfe0 \\u0413\\u043b\\u0430\\u0432\\u043d\\u043e\\u0435 \\u043c\\u0435\\u043d\\u044e\"}}"}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922235,\n\"message\":{\"message_id\":1318,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782050225,\"text\":\"\\ud83d\\udcc5 \\u0417\\u0430\\u043f\\u0438\\u0441\\u0438\"}}"}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922236,\n\"message\":{\"message_id\":1320,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782050249,\"text\":\"\\ud83c\\udfe0 \\u0413\\u043b\\u0430\\u0432\\u043d\\u043e\\u0435 \\u043c\\u0435\\u043d\\u044e\"}}"}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922237,\n\"message\":{\"message_id\":1322,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782050318,\"text\":\"\\ud83d\\udc85 \\u0423\\u0441\\u043b\\u0443\\u0433\\u0438\"}}"}</t>
+  </si>
+  <si>
+    <t>{"text":"💅 Услуги","appointmentsText":"📅 Записи","equal":false}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922238,\n\"message\":{\"message_id\":1324,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782050332,\"text\":\"\\u2b05\\ufe0f \\u041d\\u0430\\u0437\\u0430\\u0434\"}}"}</t>
+  </si>
+  <si>
+    <t>{"text":"⬅️ Назад","appointmentsText":"📅 Записи","equal":false}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922239,\n\"message\":{\"message_id\":1326,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782061705,\"text\":\"\\ud83d\\udcc5 \\u0417\\u0430\\u043f\\u0438\\u0441\\u0438\"}}"}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922240,\n\"message\":{\"message_id\":1328,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782061723,\"text\":\"\\ud83d\\udcc5 \\u0421\\u0435\\u0433\\u043e\\u0434\\u043d\\u044f\"}}"}</t>
+  </si>
+  <si>
+    <t>{"text":"📅 Сегодня","appointmentsText":"📅 Записи","equal":false}</t>
+  </si>
+  <si>
+    <t>{"parameters":{"bot":"admin"},"body":"{\"update_id\":38922241,\n\"message\":{\"message_id\":1330,\"from\":{\"id\":726107007,\"is_bot\":false,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"language_code\":\"ru\"},\"chat\":{\"id\":726107007,\"first_name\":\"Serhii\",\"username\":\"Serhii_Tsi\",\"type\":\"private\"},\"date\":1782061747,\"text\":\"\\ud83c\\udfe0 \\u0413\\u043b\\u0430\\u0432\\u043d\\u043e\\u0435 \\u043c\\u0435\\u043d\\u044e\"}}"}</t>
+  </si>
+  <si>
     <t>location_id</t>
   </si>
   <si>
@@ -3445,9 +3538,6 @@
     <t>session_data</t>
   </si>
   <si>
-    <t>{}</t>
-  </si>
-  <si>
     <t>name_key</t>
   </si>
   <si>
@@ -5933,6 +6023,78 @@
   </si>
   <si>
     <t>Custom service terms deleted</t>
+  </si>
+  <si>
+    <t>ADMIN_APPOINTMENTS_TODAY</t>
+  </si>
+  <si>
+    <t>📅 Сьогодні</t>
+  </si>
+  <si>
+    <t>📅 Сегодня</t>
+  </si>
+  <si>
+    <t>📅 Today</t>
+  </si>
+  <si>
+    <t>ADMIN_APPOINTMENTS_BY_PROVIDER</t>
+  </si>
+  <si>
+    <t>👩‍💼 За майстром</t>
+  </si>
+  <si>
+    <t>👩‍💼 По мастеру</t>
+  </si>
+  <si>
+    <t>👩‍💼 By provider</t>
+  </si>
+  <si>
+    <t>ADMIN_APPOINTMENTS_BY_CUSTOMER</t>
+  </si>
+  <si>
+    <t>📞 За клієнтом</t>
+  </si>
+  <si>
+    <t>📞 По клиенту</t>
+  </si>
+  <si>
+    <t>📞 By customer</t>
+  </si>
+  <si>
+    <t>ADMIN_APPOINTMENTS_UPCOMING</t>
+  </si>
+  <si>
+    <t>📋 Майбутні записи</t>
+  </si>
+  <si>
+    <t>📋 Будущие записи</t>
+  </si>
+  <si>
+    <t>📋 Upcoming appointments</t>
+  </si>
+  <si>
+    <t>APPOINTMENTS_TODAY_TITLE</t>
+  </si>
+  <si>
+    <t>Записи на сьогодні</t>
+  </si>
+  <si>
+    <t>Записи на сегодня</t>
+  </si>
+  <si>
+    <t>Today appointments</t>
+  </si>
+  <si>
+    <t>NO_APPOINTMENTS_FOUND</t>
+  </si>
+  <si>
+    <t>Записів не знайдено</t>
+  </si>
+  <si>
+    <t>Записей не найдено</t>
+  </si>
+  <si>
+    <t>No appointments found</t>
   </si>
   <si>
     <t>LOCATION_NAME_001</t>
@@ -6978,36 +7140,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1192</v>
+        <v>1222</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1159</v>
+        <v>1189</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1193</v>
+        <v>1223</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1194</v>
+        <v>1224</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1195</v>
+        <v>1225</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1160</v>
+        <v>1190</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1196</v>
+        <v>1226</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1161</v>
+        <v>1191</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1197</v>
+        <v>1227</v>
       </c>
       <c r="D2" s="17">
         <v>0.2916666666678793</v>
@@ -7016,7 +7178,7 @@
         <v>1.0</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G2" s="8">
         <v>46188.65645473379</v>
@@ -7024,13 +7186,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>1199</v>
+        <v>1229</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1165</v>
+        <v>1195</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1197</v>
+        <v>1227</v>
       </c>
       <c r="D3" s="17">
         <v>0.4166666666678793</v>
@@ -7039,7 +7201,7 @@
         <v>1.0</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G3" s="8">
         <v>46188.662710046294</v>
@@ -7047,13 +7209,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>1200</v>
+        <v>1230</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1166</v>
+        <v>1196</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1201</v>
+        <v>1231</v>
       </c>
       <c r="D4" s="17">
         <v>0.75</v>
@@ -7062,7 +7224,7 @@
         <v>1.0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G4" s="8">
         <v>46188.71445289352</v>
@@ -7070,13 +7232,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>1202</v>
+        <v>1232</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1169</v>
+        <v>1199</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1203</v>
+        <v>1233</v>
       </c>
       <c r="D5" s="17">
         <v>0.4583333333321207</v>
@@ -7085,7 +7247,7 @@
         <v>1.0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G5" s="8">
         <v>46188.90847733796</v>
@@ -7093,13 +7255,13 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>1204</v>
+        <v>1234</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1171</v>
+        <v>1201</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1205</v>
+        <v>1235</v>
       </c>
       <c r="D6" s="17">
         <v>0.3333333333321207</v>
@@ -7108,7 +7270,7 @@
         <v>1.0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G6" s="8">
         <v>46188.9278031713</v>
@@ -7116,13 +7278,13 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>1206</v>
+        <v>1236</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1172</v>
+        <v>1202</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1197</v>
+        <v>1227</v>
       </c>
       <c r="D7" s="17">
         <v>0.5</v>
@@ -7131,7 +7293,7 @@
         <v>1.0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G7" s="8">
         <v>46189.317873692125</v>
@@ -7139,13 +7301,13 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>1207</v>
+        <v>1237</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1174</v>
+        <v>1204</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1203</v>
+        <v>1233</v>
       </c>
       <c r="D8" s="17">
         <v>0.4583333333321207</v>
@@ -7154,7 +7316,7 @@
         <v>1.0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G8" s="8">
         <v>46189.43936521991</v>
@@ -7162,13 +7324,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>1208</v>
+        <v>1238</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1174</v>
+        <v>1204</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1203</v>
+        <v>1233</v>
       </c>
       <c r="D9" s="17">
         <v>0.5833333333321207</v>
@@ -7177,7 +7339,7 @@
         <v>2.0</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1209</v>
+        <v>1239</v>
       </c>
       <c r="G9" s="8">
         <v>46189.43936521991</v>
@@ -7185,13 +7347,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>1210</v>
+        <v>1240</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1176</v>
+        <v>1206</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1203</v>
+        <v>1233</v>
       </c>
       <c r="D10" s="17">
         <v>0.3333333333321207</v>
@@ -7200,7 +7362,7 @@
         <v>1.0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G10" s="8">
         <v>46189.50189868055</v>
@@ -7208,13 +7370,13 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>1211</v>
+        <v>1241</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1178</v>
+        <v>1208</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1203</v>
+        <v>1233</v>
       </c>
       <c r="D11" s="17">
         <v>0.5208333333321207</v>
@@ -7223,7 +7385,7 @@
         <v>1.0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G11" s="8">
         <v>46189.54015105324</v>
@@ -7231,13 +7393,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>1212</v>
+        <v>1242</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1180</v>
+        <v>1210</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1203</v>
+        <v>1233</v>
       </c>
       <c r="D12" s="17">
         <v>0.5625</v>
@@ -7246,7 +7408,7 @@
         <v>1.0</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G12" s="8">
         <v>46189.5916405787</v>
@@ -7254,13 +7416,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>1213</v>
+        <v>1243</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1182</v>
+        <v>1212</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1203</v>
+        <v>1233</v>
       </c>
       <c r="D13" s="17">
         <v>0.6458333333321207</v>
@@ -7269,7 +7431,7 @@
         <v>1.0</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G13" s="8">
         <v>46189.67521545139</v>
@@ -7277,13 +7439,13 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>1214</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>1184</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>1215</v>
+        <v>1245</v>
       </c>
       <c r="D14" s="17">
         <v>0.6458333333321207</v>
@@ -7292,7 +7454,7 @@
         <v>1.0</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1186</v>
+        <v>1216</v>
       </c>
       <c r="G14" s="8">
         <v>46190.42388396991</v>
@@ -7300,13 +7462,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>1216</v>
+        <v>1246</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1187</v>
+        <v>1217</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1217</v>
+        <v>1247</v>
       </c>
       <c r="D15" s="17">
         <v>0.3541666666678793</v>
@@ -7315,7 +7477,7 @@
         <v>1.0</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G15" s="8">
         <v>46190.43210313657</v>
@@ -7323,13 +7485,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>1218</v>
+        <v>1248</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1189</v>
+        <v>1219</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1217</v>
+        <v>1247</v>
       </c>
       <c r="D16" s="17">
         <v>0.5</v>
@@ -7338,7 +7500,7 @@
         <v>1.0</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G16" s="8">
         <v>46190.49150554398</v>
@@ -7346,13 +7508,13 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>1219</v>
+        <v>1249</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1191</v>
+        <v>1221</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1217</v>
+        <v>1247</v>
       </c>
       <c r="D17" s="17">
         <v>0.6041666666678793</v>
@@ -7361,7 +7523,7 @@
         <v>1.0</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G17" s="8">
         <v>46190.52212725695</v>
@@ -7369,13 +7531,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>1220</v>
+        <v>1250</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>313</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1217</v>
+        <v>1247</v>
       </c>
       <c r="D18" s="17">
         <v>0.375</v>
@@ -7384,7 +7546,7 @@
         <v>1.0</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G18" s="8">
         <v>46191.932762083336</v>
@@ -7392,13 +7554,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>1221</v>
+        <v>1251</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>626</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1222</v>
+        <v>1252</v>
       </c>
       <c r="D19" s="17">
         <v>0.3333333333321207</v>
@@ -7407,7 +7569,7 @@
         <v>1.0</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G19" s="8">
         <v>46193.53664446759</v>
@@ -7415,13 +7577,13 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>1223</v>
+        <v>1253</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>686</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1222</v>
+        <v>1252</v>
       </c>
       <c r="D20" s="17">
         <v>0.4166666666678793</v>
@@ -7430,7 +7592,7 @@
         <v>1.0</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G20" s="8">
         <v>46193.56815467593</v>
@@ -7438,13 +7600,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>1224</v>
+        <v>1254</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>710</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1222</v>
+        <v>1252</v>
       </c>
       <c r="D21" s="17">
         <v>0.4583333333321207</v>
@@ -7453,7 +7615,7 @@
         <v>1.0</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G21" s="8">
         <v>46193.58834351852</v>
@@ -7461,13 +7623,13 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>1225</v>
+        <v>1255</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>734</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1222</v>
+        <v>1252</v>
       </c>
       <c r="D22" s="17">
         <v>0.5208333333321207</v>
@@ -7476,7 +7638,7 @@
         <v>1.0</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G22" s="8">
         <v>46193.684204212965</v>
@@ -7484,7 +7646,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>1226</v>
+        <v>1256</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>760</v>
@@ -7499,7 +7661,7 @@
         <v>1.0</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G23" s="8">
         <v>46193.71243143518</v>
@@ -7507,7 +7669,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>1227</v>
+        <v>1257</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>857</v>
@@ -7522,7 +7684,7 @@
         <v>1.0</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G24" s="8">
         <v>46193.84162313657</v>
@@ -7530,7 +7692,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>1228</v>
+        <v>1258</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>922</v>
@@ -7545,7 +7707,7 @@
         <v>1.0</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G25" s="8">
         <v>46194.40339665509</v>
@@ -7553,7 +7715,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>1229</v>
+        <v>1259</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>946</v>
@@ -7568,7 +7730,7 @@
         <v>1.0</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G26" s="8">
         <v>46194.409719166666</v>
@@ -7576,7 +7738,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>1230</v>
+        <v>1260</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>971</v>
@@ -7591,7 +7753,7 @@
         <v>1.0</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G27" s="8">
         <v>46194.44813730324</v>
@@ -7599,7 +7761,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>1231</v>
+        <v>1261</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>992</v>
@@ -7614,7 +7776,7 @@
         <v>1.0</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G28" s="8">
         <v>46194.452012511574</v>
@@ -7622,7 +7784,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>1232</v>
+        <v>1262</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>1059</v>
@@ -7637,7 +7799,7 @@
         <v>1.0</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="G29" s="8">
         <v>46194.55216422454</v>
@@ -7769,10 +7931,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="s">
-        <v>1097</v>
+        <v>1128</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>1096</v>
+        <v>1127</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>27</v>
@@ -7783,7 +7945,7 @@
         <v>616</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="C2" s="16" t="b">
         <v>1</v>
@@ -7794,7 +7956,7 @@
         <v>616</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="C3" s="16" t="b">
         <v>1</v>
@@ -7805,7 +7967,7 @@
         <v>294</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="C4" s="16" t="b">
         <v>1</v>
@@ -7816,7 +7978,7 @@
         <v>294</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="C5" s="16" t="b">
         <v>1</v>
@@ -7836,22 +7998,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1097</v>
+        <v>1128</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1233</v>
+        <v>1263</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1234</v>
+        <v>1264</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1235</v>
+        <v>1265</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1236</v>
+        <v>1266</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1152</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="2">
@@ -7967,7 +8129,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1237</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="9">
@@ -7981,7 +8143,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1237</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="10">
@@ -8080,12 +8242,12 @@
         <v>0</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1237</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>1238</v>
+        <v>1268</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>29</v>
@@ -8102,7 +8264,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>1238</v>
+        <v>1268</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>31</v>
@@ -8119,7 +8281,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>1238</v>
+        <v>1268</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>33</v>
@@ -8136,7 +8298,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>1238</v>
+        <v>1268</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>35</v>
@@ -8153,7 +8315,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>1238</v>
+        <v>1268</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>37</v>
@@ -8170,7 +8332,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>1238</v>
+        <v>1268</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>39</v>
@@ -8187,7 +8349,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>1238</v>
+        <v>1268</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>41</v>
@@ -8204,7 +8366,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>1239</v>
+        <v>1269</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>29</v>
@@ -8221,7 +8383,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>1239</v>
+        <v>1269</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>31</v>
@@ -8238,7 +8400,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>1239</v>
+        <v>1269</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>33</v>
@@ -8255,7 +8417,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>1239</v>
+        <v>1269</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>35</v>
@@ -8272,7 +8434,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>1239</v>
+        <v>1269</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>37</v>
@@ -8289,7 +8451,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>1239</v>
+        <v>1269</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>39</v>
@@ -8306,7 +8468,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>1239</v>
+        <v>1269</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>41</v>
@@ -8323,7 +8485,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>1240</v>
+        <v>1270</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>29</v>
@@ -8340,7 +8502,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>1240</v>
+        <v>1270</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>31</v>
@@ -8357,7 +8519,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>1240</v>
+        <v>1270</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>33</v>
@@ -8374,7 +8536,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>1240</v>
+        <v>1270</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>35</v>
@@ -8391,7 +8553,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>1240</v>
+        <v>1270</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>37</v>
@@ -8408,7 +8570,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>1240</v>
+        <v>1270</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>39</v>
@@ -8425,7 +8587,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>1240</v>
+        <v>1270</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>41</v>
@@ -8458,39 +8620,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1158</v>
+        <v>1188</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1097</v>
+        <v>1128</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1241</v>
+        <v>1271</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1234</v>
+        <v>1264</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1235</v>
+        <v>1265</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1236</v>
+        <v>1266</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1242</v>
+        <v>1272</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>27</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1243</v>
+        <v>1273</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1238</v>
+        <v>1268</v>
       </c>
       <c r="C2" s="14">
         <v>46216.0</v>
@@ -8505,7 +8667,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1244</v>
+        <v>1274</v>
       </c>
       <c r="H2" s="2" t="b">
         <v>1</v>
@@ -8516,10 +8678,10 @@
     </row>
     <row r="3">
       <c r="A3" s="20" t="s">
-        <v>1245</v>
+        <v>1275</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1238</v>
+        <v>1268</v>
       </c>
       <c r="C3" s="14">
         <v>46215.0</v>
@@ -8528,7 +8690,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1246</v>
+        <v>1276</v>
       </c>
       <c r="H3" s="2" t="b">
         <v>1</v>
@@ -8539,10 +8701,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>1247</v>
+        <v>1277</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1238</v>
+        <v>1268</v>
       </c>
       <c r="C4" s="14">
         <v>46214.0</v>
@@ -8551,7 +8713,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1248</v>
+        <v>1278</v>
       </c>
       <c r="H4" s="2" t="b">
         <v>1</v>
@@ -8562,10 +8724,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>1249</v>
+        <v>1279</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1238</v>
+        <v>1268</v>
       </c>
       <c r="C5" s="14">
         <v>46213.0</v>
@@ -8574,7 +8736,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1250</v>
+        <v>1280</v>
       </c>
       <c r="H5" s="2" t="b">
         <v>1</v>
@@ -8585,10 +8747,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>1251</v>
+        <v>1281</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1238</v>
+        <v>1268</v>
       </c>
       <c r="C6" s="14">
         <v>46212.0</v>
@@ -8597,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1250</v>
+        <v>1280</v>
       </c>
       <c r="H6" s="2" t="b">
         <v>0</v>
@@ -8642,30 +8804,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1252</v>
+        <v>1282</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1253</v>
+        <v>1283</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>1254</v>
+        <v>1284</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>1255</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1256</v>
+        <v>1286</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1257</v>
+        <v>1287</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1258</v>
+        <v>1288</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1259</v>
+        <v>1289</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>29</v>
@@ -8682,16 +8844,16 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>1260</v>
+        <v>1290</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1261</v>
+        <v>1291</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1258</v>
+        <v>1288</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1259</v>
+        <v>1289</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>31</v>
@@ -8708,16 +8870,16 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>1262</v>
+        <v>1292</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1263</v>
+        <v>1293</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1258</v>
+        <v>1288</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1259</v>
+        <v>1289</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>33</v>
@@ -8734,10 +8896,10 @@
     </row>
     <row r="5">
       <c r="D5" s="2" t="s">
-        <v>1258</v>
+        <v>1288</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1259</v>
+        <v>1289</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>35</v>
@@ -8754,10 +8916,10 @@
     </row>
     <row r="6">
       <c r="D6" s="2" t="s">
-        <v>1258</v>
+        <v>1288</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1259</v>
+        <v>1289</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>37</v>
@@ -8774,10 +8936,10 @@
     </row>
     <row r="7">
       <c r="D7" s="2" t="s">
-        <v>1258</v>
+        <v>1288</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1259</v>
+        <v>1289</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>39</v>
@@ -8794,10 +8956,10 @@
     </row>
     <row r="8">
       <c r="D8" s="2" t="s">
-        <v>1258</v>
+        <v>1288</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1259</v>
+        <v>1289</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>41</v>
@@ -8806,23 +8968,23 @@
         <v>0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1237</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="10">
       <c r="D10" s="21" t="s">
-        <v>1254</v>
+        <v>1284</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>1264</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="12">
       <c r="D12" s="2" t="s">
-        <v>1258</v>
+        <v>1288</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1259</v>
+        <v>1289</v>
       </c>
       <c r="F12" s="12">
         <v>46188.0</v>
@@ -8831,15 +8993,15 @@
         <v>0</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1237</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="13">
       <c r="D13" s="2" t="s">
-        <v>1258</v>
+        <v>1288</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1259</v>
+        <v>1289</v>
       </c>
       <c r="F13" s="12">
         <v>46189.0</v>
@@ -8854,52 +9016,52 @@
         <v>1</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1265</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>1266</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>1267</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>1268</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>1269</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>1270</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>1271</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>1272</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>1273</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>1267</v>
+        <v>1297</v>
       </c>
     </row>
   </sheetData>
@@ -8921,22 +9083,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1097</v>
+        <v>1128</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1095</v>
+        <v>1126</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1138</v>
+        <v>1168</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1149</v>
+        <v>1179</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>43</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1274</v>
+        <v>1304</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>27</v>
@@ -8947,10 +9109,10 @@
         <v>616</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1275</v>
+        <v>1305</v>
       </c>
       <c r="D2" s="22">
         <f>+380111111111</f>
@@ -8968,10 +9130,10 @@
         <v>294</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1276</v>
+        <v>1306</v>
       </c>
       <c r="D3" s="22">
         <f>+380111111113</f>
@@ -8986,13 +9148,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>1258</v>
+        <v>1288</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1277</v>
+        <v>1307</v>
       </c>
       <c r="D4" s="2">
         <v>3.56532525E8</v>
@@ -9006,13 +9168,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>1278</v>
+        <v>1308</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1279</v>
+        <v>1309</v>
       </c>
       <c r="D5" s="2">
         <v>3.80000000004E11</v>
@@ -9026,13 +9188,13 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>1238</v>
+        <v>1268</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1280</v>
+        <v>1310</v>
       </c>
       <c r="D6" s="2">
         <v>3.805263545E9</v>
@@ -9046,13 +9208,13 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>1239</v>
+        <v>1269</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1281</v>
+        <v>1311</v>
       </c>
       <c r="D7" s="2">
         <v>1.23456798E8</v>
@@ -9066,13 +9228,13 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>1240</v>
+        <v>1270</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1282</v>
+        <v>1312</v>
       </c>
       <c r="D8" s="2">
         <v>2.54569872E8</v>
@@ -9101,22 +9263,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="s">
-        <v>1283</v>
+        <v>1313</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>1284</v>
+        <v>1314</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>1285</v>
+        <v>1315</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>1286</v>
+        <v>1316</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>1287</v>
+        <v>1317</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>1160</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="2">
@@ -9158,32 +9320,32 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1288</v>
+        <v>1318</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1289</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1290</v>
+        <v>1320</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1291</v>
+        <v>1321</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1292</v>
+        <v>1322</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1293</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>1294</v>
+        <v>1324</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>771</v>
@@ -9192,1505 +9354,1505 @@
         <v>771</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1295</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>1296</v>
+        <v>1326</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1297</v>
+        <v>1327</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1298</v>
+        <v>1328</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1299</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>1300</v>
+        <v>1330</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1301</v>
+        <v>1331</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1302</v>
+        <v>1332</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1303</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>1304</v>
+        <v>1334</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1305</v>
+        <v>1335</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1306</v>
+        <v>1336</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1307</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>1308</v>
+        <v>1338</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1309</v>
+        <v>1339</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1310</v>
+        <v>1340</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1311</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>1312</v>
+        <v>1342</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1313</v>
+        <v>1343</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1314</v>
+        <v>1344</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1315</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>1316</v>
+        <v>1346</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1317</v>
+        <v>1347</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1318</v>
+        <v>1348</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1319</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>1320</v>
+        <v>1350</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1321</v>
+        <v>1351</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1322</v>
+        <v>1352</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1323</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>1324</v>
+        <v>1354</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1325</v>
+        <v>1355</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1326</v>
+        <v>1356</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1327</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>1328</v>
+        <v>1358</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1329</v>
+        <v>1359</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1330</v>
+        <v>1360</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1331</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>1332</v>
+        <v>1362</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1333</v>
+        <v>1363</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1334</v>
+        <v>1364</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1335</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>1336</v>
+        <v>1366</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1337</v>
+        <v>1367</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1338</v>
+        <v>1368</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1339</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>1340</v>
+        <v>1370</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1341</v>
+        <v>1371</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1342</v>
+        <v>1372</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1343</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>1344</v>
+        <v>1374</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1345</v>
+        <v>1375</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1346</v>
+        <v>1376</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1347</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>1348</v>
+        <v>1378</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1349</v>
+        <v>1379</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1350</v>
+        <v>1380</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1351</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>1352</v>
+        <v>1382</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1353</v>
+        <v>1383</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1354</v>
+        <v>1384</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1355</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>1356</v>
+        <v>1386</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1357</v>
+        <v>1387</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1357</v>
+        <v>1387</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1358</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>1359</v>
+        <v>1389</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1360</v>
+        <v>1390</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1361</v>
+        <v>1391</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1362</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>1363</v>
+        <v>1393</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1366</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>1367</v>
+        <v>1397</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1368</v>
+        <v>1398</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1369</v>
+        <v>1399</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1370</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>1371</v>
+        <v>1401</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1372</v>
+        <v>1402</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1373</v>
+        <v>1403</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1374</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>1375</v>
+        <v>1405</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1376</v>
+        <v>1406</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1377</v>
+        <v>1407</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1378</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>1379</v>
+        <v>1409</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1381</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>1382</v>
+        <v>1412</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1383</v>
+        <v>1413</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1384</v>
+        <v>1414</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1385</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>1386</v>
+        <v>1416</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1387</v>
+        <v>1417</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1388</v>
+        <v>1418</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1389</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>1390</v>
+        <v>1420</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1391</v>
+        <v>1421</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1392</v>
+        <v>1422</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1393</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>1394</v>
+        <v>1424</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1395</v>
+        <v>1425</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1396</v>
+        <v>1426</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1397</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>1398</v>
+        <v>1428</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1399</v>
+        <v>1429</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1400</v>
+        <v>1430</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1401</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1403</v>
+        <v>1433</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1404</v>
+        <v>1434</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1405</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>1406</v>
+        <v>1436</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1407</v>
+        <v>1437</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1408</v>
+        <v>1438</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1409</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>1410</v>
+        <v>1440</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1411</v>
+        <v>1441</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1412</v>
+        <v>1442</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1413</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>1414</v>
+        <v>1444</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1415</v>
+        <v>1445</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1416</v>
+        <v>1446</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1417</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>1418</v>
+        <v>1448</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1419</v>
+        <v>1449</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1420</v>
+        <v>1450</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1421</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>1422</v>
+        <v>1452</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1423</v>
+        <v>1453</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1424</v>
+        <v>1454</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1425</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>1426</v>
+        <v>1456</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1427</v>
+        <v>1457</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1427</v>
+        <v>1457</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1428</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>1429</v>
+        <v>1459</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1430</v>
+        <v>1460</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1431</v>
+        <v>1461</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1432</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>1433</v>
+        <v>1463</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1434</v>
+        <v>1464</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1434</v>
+        <v>1464</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1435</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>1436</v>
+        <v>1466</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1437</v>
+        <v>1467</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1438</v>
+        <v>1468</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1439</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>1440</v>
+        <v>1470</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1441</v>
+        <v>1471</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1442</v>
+        <v>1472</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1443</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>1444</v>
+        <v>1474</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1445</v>
+        <v>1475</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1446</v>
+        <v>1476</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1447</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>1448</v>
+        <v>1478</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>1449</v>
+        <v>1479</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1450</v>
+        <v>1480</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1451</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>1452</v>
+        <v>1482</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1453</v>
+        <v>1483</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1454</v>
+        <v>1484</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1455</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>1456</v>
+        <v>1486</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1457</v>
+        <v>1487</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1458</v>
+        <v>1488</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1459</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>1460</v>
+        <v>1490</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1461</v>
+        <v>1491</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1462</v>
+        <v>1492</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1463</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>1464</v>
+        <v>1494</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>1465</v>
+        <v>1495</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1466</v>
+        <v>1496</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1467</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>1468</v>
+        <v>1498</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1469</v>
+        <v>1499</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1470</v>
+        <v>1500</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1471</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>1472</v>
+        <v>1502</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1473</v>
+        <v>1503</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1474</v>
+        <v>1504</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1475</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>1476</v>
+        <v>1506</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1477</v>
+        <v>1507</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1478</v>
+        <v>1508</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1479</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>1480</v>
+        <v>1510</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1482</v>
+        <v>1512</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1483</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>1484</v>
+        <v>1514</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1485</v>
+        <v>1515</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1486</v>
+        <v>1516</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1487</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>1488</v>
+        <v>1518</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1489</v>
+        <v>1519</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1490</v>
+        <v>1520</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1491</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>1492</v>
+        <v>1522</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1493</v>
+        <v>1523</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1494</v>
+        <v>1524</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1495</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>1496</v>
+        <v>1526</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>1497</v>
+        <v>1527</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1498</v>
+        <v>1528</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1499</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>1500</v>
+        <v>1530</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1501</v>
+        <v>1531</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1502</v>
+        <v>1532</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1503</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>1504</v>
+        <v>1534</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1505</v>
+        <v>1535</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1506</v>
+        <v>1536</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1507</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>1508</v>
+        <v>1538</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1509</v>
+        <v>1539</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1510</v>
+        <v>1540</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1511</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>1512</v>
+        <v>1542</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1513</v>
+        <v>1543</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1514</v>
+        <v>1544</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1515</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>1516</v>
+        <v>1546</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1517</v>
+        <v>1547</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1518</v>
+        <v>1548</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1519</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>1520</v>
+        <v>1550</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1521</v>
+        <v>1551</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1522</v>
+        <v>1552</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1523</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>1524</v>
+        <v>1554</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1525</v>
+        <v>1555</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1526</v>
+        <v>1556</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1527</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>1528</v>
+        <v>1558</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1529</v>
+        <v>1559</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1530</v>
+        <v>1560</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1531</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>1532</v>
+        <v>1562</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1533</v>
+        <v>1563</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1534</v>
+        <v>1564</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1535</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>1536</v>
+        <v>1566</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1537</v>
+        <v>1567</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1538</v>
+        <v>1568</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1539</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>1540</v>
+        <v>1570</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1541</v>
+        <v>1571</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1542</v>
+        <v>1572</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1543</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>1544</v>
+        <v>1574</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1545</v>
+        <v>1575</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1546</v>
+        <v>1576</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1547</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>1548</v>
+        <v>1578</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1549</v>
+        <v>1579</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1550</v>
+        <v>1580</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1551</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>1552</v>
+        <v>1582</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1553</v>
+        <v>1583</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1554</v>
+        <v>1584</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1555</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>1556</v>
+        <v>1586</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1430</v>
+        <v>1460</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1431</v>
+        <v>1461</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1432</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>1557</v>
+        <v>1587</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1434</v>
+        <v>1464</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>1434</v>
+        <v>1464</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1435</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>1558</v>
+        <v>1588</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1441</v>
+        <v>1471</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1442</v>
+        <v>1472</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>1443</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>1559</v>
+        <v>1589</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1445</v>
+        <v>1475</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>1446</v>
+        <v>1476</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>1447</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>1560</v>
+        <v>1590</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1561</v>
+        <v>1591</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1562</v>
+        <v>1592</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>1439</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>1563</v>
+        <v>1593</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1564</v>
+        <v>1594</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1565</v>
+        <v>1595</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>1566</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>1567</v>
+        <v>1597</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1568</v>
+        <v>1598</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>1569</v>
+        <v>1599</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>1570</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>1571</v>
+        <v>1601</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1572</v>
+        <v>1602</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>1573</v>
+        <v>1603</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>1574</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>1575</v>
+        <v>1605</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1576</v>
+        <v>1606</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>1577</v>
+        <v>1607</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>1578</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>1579</v>
+        <v>1609</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1580</v>
+        <v>1610</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>1581</v>
+        <v>1611</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>1582</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>1583</v>
+        <v>1613</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1584</v>
+        <v>1614</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>1584</v>
+        <v>1614</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>1585</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>1586</v>
+        <v>1616</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1587</v>
+        <v>1617</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>1588</v>
+        <v>1618</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>1589</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>1590</v>
+        <v>1620</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1591</v>
+        <v>1621</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>1592</v>
+        <v>1622</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>1593</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>1594</v>
+        <v>1624</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1595</v>
+        <v>1625</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>1596</v>
+        <v>1626</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>1597</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>1598</v>
+        <v>1628</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1599</v>
+        <v>1629</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>1600</v>
+        <v>1630</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>1601</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>1602</v>
+        <v>1632</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1603</v>
+        <v>1633</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>1604</v>
+        <v>1634</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>1605</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>1606</v>
+        <v>1636</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1607</v>
+        <v>1637</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>1608</v>
+        <v>1638</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>1609</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>1610</v>
+        <v>1640</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1611</v>
+        <v>1641</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>1612</v>
+        <v>1642</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1613</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>1614</v>
+        <v>1644</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1615</v>
+        <v>1645</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>1616</v>
+        <v>1646</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>1617</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>1618</v>
+        <v>1648</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1619</v>
+        <v>1649</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>1620</v>
+        <v>1650</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>1621</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>1622</v>
+        <v>1652</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1321</v>
+        <v>1351</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>1322</v>
+        <v>1352</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>1323</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>1623</v>
+        <v>1653</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1624</v>
+        <v>1654</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>1625</v>
+        <v>1655</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>1626</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>1627</v>
+        <v>1657</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1628</v>
+        <v>1658</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>1629</v>
+        <v>1659</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>1630</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>1631</v>
+        <v>1661</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1632</v>
+        <v>1662</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>1633</v>
+        <v>1663</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>1634</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>1635</v>
+        <v>1665</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1636</v>
+        <v>1666</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>1637</v>
+        <v>1667</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>1638</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>1639</v>
+        <v>1669</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1329</v>
+        <v>1359</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>1330</v>
+        <v>1360</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>1331</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>1640</v>
+        <v>1670</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1641</v>
+        <v>1671</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>1642</v>
+        <v>1672</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>1643</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>1644</v>
+        <v>1674</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1645</v>
+        <v>1675</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>1646</v>
+        <v>1676</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>1647</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>1648</v>
+        <v>1678</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1649</v>
+        <v>1679</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>1650</v>
+        <v>1680</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>1651</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>1652</v>
+        <v>1682</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1653</v>
+        <v>1683</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>1654</v>
+        <v>1684</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>1655</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>1656</v>
+        <v>1686</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1657</v>
+        <v>1687</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>1658</v>
+        <v>1688</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>1659</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>1660</v>
+        <v>1690</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1661</v>
+        <v>1691</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>1662</v>
+        <v>1692</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>1663</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>1664</v>
+        <v>1694</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1665</v>
+        <v>1695</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>1666</v>
+        <v>1696</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>1667</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>1668</v>
+        <v>1698</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1437</v>
+        <v>1467</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>1438</v>
+        <v>1468</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1439</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>1669</v>
+        <v>1699</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1434</v>
+        <v>1464</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>1434</v>
+        <v>1464</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>1435</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>1670</v>
+        <v>1700</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1671</v>
+        <v>1701</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>1671</v>
+        <v>1701</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>1671</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>1672</v>
+        <v>1702</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1673</v>
+        <v>1703</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>1674</v>
+        <v>1704</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1675</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>1676</v>
+        <v>1706</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1677</v>
+        <v>1707</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>1678</v>
+        <v>1708</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>1679</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>1680</v>
+        <v>1710</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1681</v>
+        <v>1711</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>1682</v>
+        <v>1712</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1683</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>1684</v>
+        <v>1714</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1572</v>
+        <v>1602</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>1573</v>
+        <v>1603</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1574</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>1685</v>
+        <v>1715</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1686</v>
+        <v>1716</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>1687</v>
+        <v>1717</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>1688</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="111">
@@ -10698,13 +10860,13 @@
         <v>30</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1689</v>
+        <v>1719</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>1690</v>
+        <v>1720</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1691</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="112">
@@ -10712,13 +10874,13 @@
         <v>32</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1692</v>
+        <v>1722</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>1693</v>
+        <v>1723</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1694</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="113">
@@ -10726,13 +10888,13 @@
         <v>34</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1695</v>
+        <v>1725</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>1696</v>
+        <v>1726</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1697</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="114">
@@ -10740,13 +10902,13 @@
         <v>36</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1698</v>
+        <v>1728</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>1699</v>
+        <v>1729</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1700</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="115">
@@ -10754,13 +10916,13 @@
         <v>38</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1701</v>
+        <v>1731</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>1702</v>
+        <v>1732</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>1703</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="116">
@@ -10768,13 +10930,13 @@
         <v>40</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1704</v>
+        <v>1734</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>1705</v>
+        <v>1735</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>1706</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="117">
@@ -10782,881 +10944,881 @@
         <v>42</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1707</v>
+        <v>1737</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>1708</v>
+        <v>1738</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>1709</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>1710</v>
+        <v>1740</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1711</v>
+        <v>1741</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>1712</v>
+        <v>1742</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1713</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>1714</v>
+        <v>1744</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1715</v>
+        <v>1745</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>1716</v>
+        <v>1746</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1717</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>1718</v>
+        <v>1748</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1719</v>
+        <v>1749</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>1720</v>
+        <v>1750</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1721</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>1722</v>
+        <v>1752</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1723</v>
+        <v>1753</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>1724</v>
+        <v>1754</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1725</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>1726</v>
+        <v>1756</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1727</v>
+        <v>1757</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>1728</v>
+        <v>1758</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1729</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>1730</v>
+        <v>1760</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1297</v>
+        <v>1327</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>1298</v>
+        <v>1328</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1731</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>1732</v>
+        <v>1762</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1733</v>
+        <v>1763</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>1734</v>
+        <v>1764</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1735</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>1736</v>
+        <v>1766</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1737</v>
+        <v>1767</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>1738</v>
+        <v>1768</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1739</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>1740</v>
+        <v>1770</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1741</v>
+        <v>1771</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>1742</v>
+        <v>1772</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1743</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>1744</v>
+        <v>1774</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1745</v>
+        <v>1775</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>1746</v>
+        <v>1776</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1747</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>1250</v>
+        <v>1280</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1748</v>
+        <v>1778</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>1749</v>
+        <v>1779</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1750</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>1246</v>
+        <v>1276</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1751</v>
+        <v>1781</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>1752</v>
+        <v>1782</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1753</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>1248</v>
+        <v>1278</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1686</v>
+        <v>1716</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>1687</v>
+        <v>1717</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1688</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>1754</v>
+        <v>1784</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1755</v>
+        <v>1785</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>1756</v>
+        <v>1786</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1757</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>1244</v>
+        <v>1274</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1758</v>
+        <v>1788</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>1759</v>
+        <v>1789</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1760</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>1761</v>
+        <v>1791</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1329</v>
+        <v>1359</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>1330</v>
+        <v>1360</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1331</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>1762</v>
+        <v>1792</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1297</v>
+        <v>1327</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>1298</v>
+        <v>1328</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1731</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>1763</v>
+        <v>1793</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1764</v>
+        <v>1794</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>1765</v>
+        <v>1795</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1766</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>1767</v>
+        <v>1797</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1768</v>
+        <v>1798</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>1769</v>
+        <v>1799</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>1771</v>
+        <v>1801</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1772</v>
+        <v>1802</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>1773</v>
+        <v>1803</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1774</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>1775</v>
+        <v>1805</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1776</v>
+        <v>1806</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>1777</v>
+        <v>1807</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1778</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>1779</v>
+        <v>1809</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1780</v>
+        <v>1810</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>1781</v>
+        <v>1811</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>1782</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>1783</v>
+        <v>1813</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1784</v>
+        <v>1814</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>1785</v>
+        <v>1815</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>1786</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>1787</v>
+        <v>1817</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1788</v>
+        <v>1818</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>1789</v>
+        <v>1819</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>1790</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>1791</v>
+        <v>1821</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1792</v>
+        <v>1822</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>1793</v>
+        <v>1823</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>1794</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>1795</v>
+        <v>1825</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1796</v>
+        <v>1826</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>1797</v>
+        <v>1827</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>1798</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>1799</v>
+        <v>1829</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1800</v>
+        <v>1830</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>1801</v>
+        <v>1831</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1802</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>1575</v>
+        <v>1605</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1576</v>
+        <v>1606</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>1577</v>
+        <v>1607</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>1578</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>1803</v>
+        <v>1833</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1804</v>
+        <v>1834</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>1805</v>
+        <v>1835</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>1806</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>1807</v>
+        <v>1837</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1808</v>
+        <v>1838</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>1809</v>
+        <v>1839</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>1810</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>1811</v>
+        <v>1841</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1812</v>
+        <v>1842</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>1813</v>
+        <v>1843</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>1814</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>1815</v>
+        <v>1845</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1816</v>
+        <v>1846</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>1817</v>
+        <v>1847</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>1818</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>1819</v>
+        <v>1849</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1820</v>
+        <v>1850</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>1821</v>
+        <v>1851</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>1822</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>1823</v>
+        <v>1853</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1824</v>
+        <v>1854</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>1825</v>
+        <v>1855</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>1826</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>1827</v>
+        <v>1857</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1828</v>
+        <v>1858</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>1829</v>
+        <v>1859</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>1831</v>
+        <v>1861</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>1321</v>
+        <v>1351</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>1322</v>
+        <v>1352</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>1323</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>1832</v>
+        <v>1862</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>1833</v>
+        <v>1863</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>1834</v>
+        <v>1864</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>1835</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>1836</v>
+        <v>1866</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>1837</v>
+        <v>1867</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>1838</v>
+        <v>1868</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>1839</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>1840</v>
+        <v>1870</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>1841</v>
+        <v>1871</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>1842</v>
+        <v>1872</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>1843</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>1844</v>
+        <v>1874</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>1845</v>
+        <v>1875</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>1846</v>
+        <v>1876</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>1847</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>1848</v>
+        <v>1878</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>1849</v>
+        <v>1879</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>1850</v>
+        <v>1880</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>1851</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>1852</v>
+        <v>1882</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>1853</v>
+        <v>1883</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>1854</v>
+        <v>1884</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>1855</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>1856</v>
+        <v>1886</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>1857</v>
+        <v>1887</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>1858</v>
+        <v>1888</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>1859</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>1860</v>
+        <v>1890</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>1861</v>
+        <v>1891</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>1862</v>
+        <v>1892</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>1863</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>1864</v>
+        <v>1894</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>1865</v>
+        <v>1895</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>1866</v>
+        <v>1896</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>1868</v>
+        <v>1898</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>1869</v>
+        <v>1899</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>1870</v>
+        <v>1900</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>1871</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>1872</v>
+        <v>1902</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>1873</v>
+        <v>1903</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>1874</v>
+        <v>1904</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>1875</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>1876</v>
+        <v>1906</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>1877</v>
+        <v>1907</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>1878</v>
+        <v>1908</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>1879</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>1880</v>
+        <v>1910</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>1881</v>
+        <v>1911</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>1882</v>
+        <v>1912</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>1667</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>1883</v>
+        <v>1913</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>1437</v>
+        <v>1467</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>1438</v>
+        <v>1468</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>1439</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>1884</v>
+        <v>1914</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>1885</v>
+        <v>1915</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>1886</v>
+        <v>1916</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1887</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>1888</v>
+        <v>1918</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>1889</v>
+        <v>1919</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>1890</v>
+        <v>1920</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>1891</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>1892</v>
+        <v>1922</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>1893</v>
+        <v>1923</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>1894</v>
+        <v>1924</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>1895</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>1896</v>
+        <v>1926</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>1897</v>
+        <v>1927</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>1898</v>
+        <v>1928</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>1899</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>1900</v>
+        <v>1930</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>1901</v>
+        <v>1931</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>1902</v>
+        <v>1932</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>1903</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>1904</v>
+        <v>1934</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>1905</v>
+        <v>1935</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>1906</v>
+        <v>1936</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>1907</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>1908</v>
+        <v>1938</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>1909</v>
+        <v>1939</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>1910</v>
+        <v>1940</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>1911</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>1811</v>
+        <v>1841</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>1912</v>
+        <v>1942</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>1913</v>
+        <v>1943</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>1914</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>1915</v>
+        <v>1945</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>1505</v>
+        <v>1535</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>1506</v>
+        <v>1536</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>1916</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>1917</v>
+        <v>1947</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>1912</v>
+        <v>1942</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>1913</v>
+        <v>1943</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>1914</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>1918</v>
+        <v>1948</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>1919</v>
+        <v>1949</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>1920</v>
+        <v>1950</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>1921</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="20" t="s">
-        <v>1922</v>
+        <v>1952</v>
       </c>
       <c r="B179" s="20" t="s">
-        <v>1923</v>
+        <v>1953</v>
       </c>
       <c r="C179" s="20" t="s">
-        <v>1924</v>
+        <v>1954</v>
       </c>
       <c r="D179" s="20" t="s">
-        <v>1925</v>
+        <v>1955</v>
       </c>
       <c r="E179" s="19"/>
       <c r="F179" s="19"/>
@@ -11683,16 +11845,16 @@
     </row>
     <row r="180">
       <c r="A180" s="20" t="s">
-        <v>1926</v>
+        <v>1956</v>
       </c>
       <c r="B180" s="20" t="s">
-        <v>1927</v>
+        <v>1957</v>
       </c>
       <c r="C180" s="20" t="s">
-        <v>1928</v>
+        <v>1958</v>
       </c>
       <c r="D180" s="20" t="s">
-        <v>1929</v>
+        <v>1959</v>
       </c>
       <c r="E180" s="19"/>
       <c r="F180" s="19"/>
@@ -11719,16 +11881,16 @@
     </row>
     <row r="181">
       <c r="A181" s="20" t="s">
-        <v>1930</v>
+        <v>1960</v>
       </c>
       <c r="B181" s="20" t="s">
-        <v>1931</v>
+        <v>1961</v>
       </c>
       <c r="C181" s="20" t="s">
-        <v>1932</v>
+        <v>1962</v>
       </c>
       <c r="D181" s="20" t="s">
-        <v>1933</v>
+        <v>1963</v>
       </c>
       <c r="E181" s="19"/>
       <c r="F181" s="19"/>
@@ -11755,16 +11917,16 @@
     </row>
     <row r="182">
       <c r="A182" s="20" t="s">
-        <v>1934</v>
+        <v>1964</v>
       </c>
       <c r="B182" s="20" t="s">
-        <v>1935</v>
+        <v>1965</v>
       </c>
       <c r="C182" s="20" t="s">
-        <v>1936</v>
+        <v>1966</v>
       </c>
       <c r="D182" s="20" t="s">
-        <v>1937</v>
+        <v>1967</v>
       </c>
       <c r="E182" s="19"/>
       <c r="F182" s="19"/>
@@ -11791,16 +11953,16 @@
     </row>
     <row r="183">
       <c r="A183" s="20" t="s">
-        <v>1938</v>
+        <v>1968</v>
       </c>
       <c r="B183" s="20" t="s">
-        <v>1939</v>
+        <v>1969</v>
       </c>
       <c r="C183" s="20" t="s">
-        <v>1940</v>
+        <v>1970</v>
       </c>
       <c r="D183" s="20" t="s">
-        <v>1941</v>
+        <v>1971</v>
       </c>
       <c r="E183" s="19"/>
       <c r="F183" s="19"/>
@@ -11827,16 +11989,16 @@
     </row>
     <row r="184">
       <c r="A184" s="20" t="s">
-        <v>1942</v>
+        <v>1972</v>
       </c>
       <c r="B184" s="20" t="s">
-        <v>1943</v>
+        <v>1973</v>
       </c>
       <c r="C184" s="20" t="s">
-        <v>1944</v>
+        <v>1974</v>
       </c>
       <c r="D184" s="20" t="s">
-        <v>1945</v>
+        <v>1975</v>
       </c>
       <c r="E184" s="19"/>
       <c r="F184" s="19"/>
@@ -11863,16 +12025,16 @@
     </row>
     <row r="185">
       <c r="A185" s="20" t="s">
-        <v>1946</v>
+        <v>1976</v>
       </c>
       <c r="B185" s="20" t="s">
-        <v>1325</v>
+        <v>1355</v>
       </c>
       <c r="C185" s="20" t="s">
-        <v>1326</v>
+        <v>1356</v>
       </c>
       <c r="D185" s="20" t="s">
-        <v>1327</v>
+        <v>1357</v>
       </c>
       <c r="E185" s="19"/>
       <c r="F185" s="19"/>
@@ -11899,16 +12061,16 @@
     </row>
     <row r="186">
       <c r="A186" s="20" t="s">
-        <v>1947</v>
+        <v>1977</v>
       </c>
       <c r="B186" s="20" t="s">
-        <v>1948</v>
+        <v>1978</v>
       </c>
       <c r="C186" s="20" t="s">
-        <v>1949</v>
+        <v>1979</v>
       </c>
       <c r="D186" s="20" t="s">
-        <v>1950</v>
+        <v>1980</v>
       </c>
       <c r="E186" s="19"/>
       <c r="F186" s="19"/>
@@ -11935,16 +12097,16 @@
     </row>
     <row r="187">
       <c r="A187" s="20" t="s">
-        <v>1951</v>
+        <v>1981</v>
       </c>
       <c r="B187" s="20" t="s">
-        <v>1952</v>
+        <v>1982</v>
       </c>
       <c r="C187" s="20" t="s">
-        <v>1953</v>
+        <v>1983</v>
       </c>
       <c r="D187" s="20" t="s">
-        <v>1954</v>
+        <v>1984</v>
       </c>
       <c r="E187" s="19"/>
       <c r="F187" s="19"/>
@@ -11971,198 +12133,296 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>1955</v>
+        <v>1985</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1956</v>
+        <v>1986</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>1957</v>
+        <v>1987</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1958</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>1959</v>
+        <v>1989</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>1960</v>
+        <v>1990</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>1961</v>
+        <v>1991</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1962</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>1963</v>
+        <v>1993</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>1964</v>
+        <v>1994</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>1965</v>
+        <v>1995</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>1966</v>
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>1998</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>2003</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>2007</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>2018</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>1614</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>1615</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="19" t="s">
-        <v>1967</v>
+        <v>2021</v>
       </c>
       <c r="B212" s="19" t="s">
-        <v>1968</v>
+        <v>2022</v>
       </c>
       <c r="C212" s="19" t="s">
-        <v>1968</v>
+        <v>2022</v>
       </c>
       <c r="D212" s="19" t="s">
-        <v>1968</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="19" t="s">
-        <v>1969</v>
+        <v>2023</v>
       </c>
       <c r="B213" s="19" t="s">
-        <v>1970</v>
+        <v>2024</v>
       </c>
       <c r="C213" s="19" t="s">
-        <v>1971</v>
+        <v>2025</v>
       </c>
       <c r="D213" s="19" t="s">
-        <v>1972</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="19" t="s">
-        <v>1146</v>
+        <v>1176</v>
       </c>
       <c r="B214" s="19" t="s">
-        <v>1973</v>
+        <v>2027</v>
       </c>
       <c r="C214" s="20" t="s">
-        <v>1157</v>
+        <v>1187</v>
       </c>
       <c r="D214" s="19" t="s">
-        <v>1974</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="19" t="s">
-        <v>1275</v>
+        <v>1305</v>
       </c>
       <c r="B215" s="19" t="s">
-        <v>1975</v>
+        <v>2029</v>
       </c>
       <c r="C215" s="19" t="s">
-        <v>1976</v>
+        <v>2030</v>
       </c>
       <c r="D215" s="19" t="s">
-        <v>1977</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="19" t="s">
-        <v>1276</v>
+        <v>1306</v>
       </c>
       <c r="B216" s="19" t="s">
-        <v>1978</v>
+        <v>2032</v>
       </c>
       <c r="C216" s="19" t="s">
-        <v>1978</v>
+        <v>2032</v>
       </c>
       <c r="D216" s="19" t="s">
-        <v>1979</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="19" t="s">
-        <v>1277</v>
+        <v>1307</v>
       </c>
       <c r="B217" s="19" t="s">
-        <v>1980</v>
+        <v>2034</v>
       </c>
       <c r="C217" s="19" t="s">
-        <v>1980</v>
+        <v>2034</v>
       </c>
       <c r="D217" s="19" t="s">
-        <v>1980</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="19" t="s">
-        <v>1279</v>
+        <v>1309</v>
       </c>
       <c r="B218" s="19" t="s">
-        <v>1981</v>
+        <v>2035</v>
       </c>
       <c r="C218" s="19" t="s">
-        <v>1981</v>
+        <v>2035</v>
       </c>
       <c r="D218" s="19" t="s">
-        <v>1981</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="19" t="s">
-        <v>1280</v>
+        <v>1310</v>
       </c>
       <c r="B219" s="19" t="s">
-        <v>1982</v>
+        <v>2036</v>
       </c>
       <c r="C219" s="19" t="s">
-        <v>1982</v>
+        <v>2036</v>
       </c>
       <c r="D219" s="19" t="s">
-        <v>1982</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="19" t="s">
-        <v>1281</v>
+        <v>1311</v>
       </c>
       <c r="B220" s="19" t="s">
-        <v>1983</v>
+        <v>2037</v>
       </c>
       <c r="C220" s="19" t="s">
-        <v>1983</v>
+        <v>2037</v>
       </c>
       <c r="D220" s="19" t="s">
-        <v>1983</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
-        <v>1282</v>
+        <v>1312</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>1984</v>
+        <v>2038</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>1984</v>
+        <v>2038</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>1984</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="s">
-        <v>1148</v>
+        <v>1178</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>1155</v>
+        <v>1185</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>1155</v>
+        <v>1185</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>1155</v>
+        <v>1185</v>
       </c>
     </row>
   </sheetData>
@@ -12182,22 +12442,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1985</v>
+        <v>2039</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1986</v>
+        <v>2040</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1097</v>
+        <v>1128</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1987</v>
+        <v>2041</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1988</v>
+        <v>2042</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>27</v>
@@ -12205,17 +12465,17 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1989</v>
+        <v>2043</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1990</v>
+        <v>2044</v>
       </c>
       <c r="C2" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="D2" s="25"/>
       <c r="E2" s="2" t="s">
-        <v>1991</v>
+        <v>2045</v>
       </c>
       <c r="F2" s="2" t="b">
         <v>1</v>
@@ -12226,16 +12486,16 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>1989</v>
+        <v>2043</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1976</v>
+        <v>2030</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1992</v>
+        <v>2046</v>
       </c>
       <c r="F3" s="2" t="b">
         <v>1</v>
@@ -12246,16 +12506,16 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>1993</v>
+        <v>2047</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1978</v>
+        <v>2032</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>294</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1992</v>
+        <v>2046</v>
       </c>
       <c r="F4" s="2" t="b">
         <v>1</v>
@@ -12266,16 +12526,16 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>1994</v>
+        <v>2048</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1995</v>
+        <v>2049</v>
       </c>
       <c r="C5" s="2">
         <v>8.3456789E8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1996</v>
+        <v>2050</v>
       </c>
       <c r="F5" s="2" t="b">
         <v>0</v>
@@ -12302,72 +12562,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1126</v>
+        <v>1157</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1997</v>
+        <v>2051</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1152</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1998</v>
+        <v>2052</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1999</v>
+        <v>2053</v>
       </c>
       <c r="C2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2000</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>1999</v>
+        <v>2053</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1998</v>
+        <v>2052</v>
       </c>
       <c r="C3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>2000</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>2001</v>
+        <v>2055</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>2002</v>
+        <v>2056</v>
       </c>
       <c r="C5" s="2" t="b">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>2003</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>2002</v>
+        <v>2056</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>2001</v>
+        <v>2055</v>
       </c>
       <c r="C6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>2003</v>
+        <v>2057</v>
       </c>
     </row>
   </sheetData>
@@ -12523,34 +12783,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1095</v>
+        <v>1126</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1138</v>
+        <v>1168</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2004</v>
+        <v>2058</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2005</v>
+        <v>2059</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2006</v>
+        <v>2060</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>2007</v>
+        <v>2061</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>2008</v>
+        <v>2062</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>2009</v>
+        <v>2063</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>2010</v>
+        <v>2064</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>2011</v>
+        <v>2065</v>
       </c>
       <c r="K1" s="13" t="s">
         <v>27</v>
@@ -12558,28 +12818,28 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1967</v>
+        <v>2021</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1969</v>
+        <v>2023</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2012</v>
+        <v>2066</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>2013</v>
+        <v>2067</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>2014</v>
+        <v>2068</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>2015</v>
+        <v>2069</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>2016</v>
+        <v>2070</v>
       </c>
       <c r="I2" s="2">
         <v>3.80000000001E11</v>
@@ -12588,7 +12848,7 @@
         <v>3.80000000002E11</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>2017</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="3">
@@ -15573,48 +15833,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1126</v>
+        <v>1157</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1986</v>
+        <v>2040</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1149</v>
+        <v>1179</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2018</v>
+        <v>2072</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>45</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>2019</v>
+        <v>2073</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>1160</v>
+        <v>1190</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>1152</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1162</v>
+        <v>1192</v>
       </c>
       <c r="B2" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2020</v>
+        <v>2074</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>2021</v>
+        <v>2075</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -15626,21 +15886,21 @@
         <v>46188.92779366898</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>1167</v>
+        <v>1197</v>
       </c>
       <c r="B3" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2022</v>
+        <v>2076</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>2023</v>
+        <v>2077</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -15652,21 +15912,21 @@
         <v>46188.71443525463</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>1170</v>
+        <v>1200</v>
       </c>
       <c r="B4" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2024</v>
+        <v>2078</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>2025</v>
+        <v>2079</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -15678,21 +15938,21 @@
         <v>46188.90845820602</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>1173</v>
+        <v>1203</v>
       </c>
       <c r="B5" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2026</v>
+        <v>2080</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>2027</v>
+        <v>2081</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -15704,21 +15964,21 @@
         <v>46189.317849768515</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>1175</v>
+        <v>1205</v>
       </c>
       <c r="B6" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>2028</v>
+        <v>2082</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>2029</v>
+        <v>2083</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -15730,21 +15990,21 @@
         <v>46189.43934060185</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>1177</v>
+        <v>1207</v>
       </c>
       <c r="B7" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>2030</v>
+        <v>2084</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>2031</v>
+        <v>2085</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -15756,21 +16016,21 @@
         <v>46189.50187771991</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>1179</v>
+        <v>1209</v>
       </c>
       <c r="B8" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>2032</v>
+        <v>2086</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>2033</v>
+        <v>2087</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -15782,21 +16042,21 @@
         <v>46189.54013206018</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>1181</v>
+        <v>1211</v>
       </c>
       <c r="B9" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>2034</v>
+        <v>2088</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>2035</v>
+        <v>2089</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -15808,21 +16068,21 @@
         <v>46189.59161953704</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>1183</v>
+        <v>1213</v>
       </c>
       <c r="B10" s="2">
         <v>7.75285374E9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>2036</v>
+        <v>2090</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>2037</v>
+        <v>2091</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -15834,21 +16094,21 @@
         <v>46189.67519152778</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>1185</v>
+        <v>1215</v>
       </c>
       <c r="B11" s="2">
         <v>7.26107007E8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>2038</v>
+        <v>2092</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>2039</v>
+        <v>2093</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -15860,21 +16120,21 @@
         <v>46190.42386880787</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>2040</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>1188</v>
+        <v>1218</v>
       </c>
       <c r="B12" s="2">
         <v>7.26107007E8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>2041</v>
+        <v>2095</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>2042</v>
+        <v>2096</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -15886,21 +16146,21 @@
         <v>46190.43208802083</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>1190</v>
+        <v>1220</v>
       </c>
       <c r="B13" s="2">
         <v>7.26107007E8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>2043</v>
+        <v>2097</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>2044</v>
+        <v>2098</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -15912,7 +16172,7 @@
         <v>46190.522112314815</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="14">
@@ -15923,10 +16183,10 @@
         <v>7.26107007E8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>2045</v>
+        <v>2099</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>2046</v>
+        <v>2100</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -15938,7 +16198,7 @@
         <v>46191.932750567124</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="15">
@@ -15949,10 +16209,10 @@
         <v>7.26107007E8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>2047</v>
+        <v>2101</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>2048</v>
+        <v>2102</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -15964,7 +16224,7 @@
         <v>46193.53662825232</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="16">
@@ -15975,10 +16235,10 @@
         <v>7.26107007E8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>2049</v>
+        <v>2103</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>2050</v>
+        <v>2104</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -15990,7 +16250,7 @@
         <v>46193.568142222226</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="17">
@@ -16001,10 +16261,10 @@
         <v>7.75285374E9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>2051</v>
+        <v>2105</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>2052</v>
+        <v>2106</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -16016,7 +16276,7 @@
         <v>46193.58831921296</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="18">
@@ -16027,10 +16287,10 @@
         <v>7.75285374E9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>2053</v>
+        <v>2107</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>2054</v>
+        <v>2108</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -16042,7 +16302,7 @@
         <v>46193.68418899305</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="19">
@@ -16053,10 +16313,10 @@
         <v>7.26107007E8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>2055</v>
+        <v>2109</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>2056</v>
+        <v>2110</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -16068,7 +16328,7 @@
         <v>46193.71241508102</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="20">
@@ -16079,10 +16339,10 @@
         <v>7.26107007E8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1156</v>
+        <v>1186</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>1154</v>
+        <v>1184</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -16094,7 +16354,7 @@
         <v>46194.452000879624</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="21">
@@ -16105,10 +16365,10 @@
         <v>7.26107007E8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>2057</v>
+        <v>2111</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>2058</v>
+        <v>2112</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -16120,7 +16380,7 @@
         <v>46194.552135474536</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="22">
@@ -19127,66 +19387,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="s">
-        <v>1284</v>
+        <v>1314</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>1159</v>
+        <v>1189</v>
       </c>
       <c r="C1" s="23" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F1" s="23" t="s">
         <v>1126</v>
       </c>
-      <c r="D1" s="23" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>1097</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>1095</v>
-      </c>
       <c r="G1" s="23" t="s">
-        <v>2059</v>
+        <v>2113</v>
       </c>
       <c r="H1" s="23" t="s">
-        <v>2060</v>
+        <v>2114</v>
       </c>
       <c r="I1" s="23" t="s">
-        <v>1160</v>
+        <v>1190</v>
       </c>
       <c r="J1" s="23" t="s">
-        <v>2061</v>
+        <v>2115</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>45</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>1125</v>
+        <v>1156</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>2062</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>2063</v>
+        <v>2117</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1161</v>
+        <v>1191</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1162</v>
+        <v>1192</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G2" s="28">
         <v>46191.354166666664</v>
@@ -19195,10 +19455,10 @@
         <v>46191.645833333336</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>2064</v>
+        <v>2118</v>
       </c>
       <c r="K2" s="8">
         <v>46188.65666847222</v>
@@ -19212,22 +19472,22 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>2065</v>
+        <v>2119</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1165</v>
+        <v>1195</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1162</v>
+        <v>1192</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G3" s="28">
         <v>46189.416666666664</v>
@@ -19236,10 +19496,10 @@
         <v>46189.708333333336</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>2066</v>
+        <v>2120</v>
       </c>
       <c r="K3" s="8">
         <v>46188.66288041667</v>
@@ -19253,22 +19513,22 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>2067</v>
+        <v>2121</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1166</v>
+        <v>1196</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1167</v>
+        <v>1197</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G4" s="28">
         <v>46188.75</v>
@@ -19277,10 +19537,10 @@
         <v>46188.805555555555</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>2068</v>
+        <v>2122</v>
       </c>
       <c r="K4" s="8">
         <v>46188.71468287037</v>
@@ -19291,22 +19551,22 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>2069</v>
+        <v>2123</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1169</v>
+        <v>1199</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1170</v>
+        <v>1200</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G5" s="28">
         <v>46190.333333333336</v>
@@ -19315,10 +19575,10 @@
         <v>46190.458333333336</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>2070</v>
+        <v>2124</v>
       </c>
       <c r="K5" s="8">
         <v>46188.90875628473</v>
@@ -19332,22 +19592,22 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>2071</v>
+        <v>2125</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1171</v>
+        <v>1201</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1162</v>
+        <v>1192</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G6" s="28">
         <v>46192.375</v>
@@ -19356,10 +19616,10 @@
         <v>46192.666666666664</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>2072</v>
+        <v>2126</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>2073</v>
+        <v>2127</v>
       </c>
       <c r="K6" s="8">
         <v>46188.928415312505</v>
@@ -19370,22 +19630,22 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>2074</v>
+        <v>2128</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1172</v>
+        <v>1202</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1173</v>
+        <v>1203</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>294</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G7" s="28">
         <v>46189.5</v>
@@ -19394,10 +19654,10 @@
         <v>46189.625</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>2075</v>
+        <v>2129</v>
       </c>
       <c r="K7" s="8">
         <v>46189.31825292824</v>
@@ -19408,22 +19668,22 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>2076</v>
+        <v>2130</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1174</v>
+        <v>1204</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1175</v>
+        <v>1205</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G8" s="28">
         <v>46190.458333333336</v>
@@ -19432,10 +19692,10 @@
         <v>46190.51388888889</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>2077</v>
+        <v>2131</v>
       </c>
       <c r="K8" s="8">
         <v>46189.43969520833</v>
@@ -19449,22 +19709,22 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>2078</v>
+        <v>2132</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1176</v>
+        <v>1206</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1177</v>
+        <v>1207</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>294</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G9" s="28">
         <v>46190.333333333336</v>
@@ -19473,10 +19733,10 @@
         <v>46190.38888888889</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>2079</v>
+        <v>2133</v>
       </c>
       <c r="K9" s="8">
         <v>46189.50223225694</v>
@@ -19490,22 +19750,22 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>2080</v>
+        <v>2134</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1178</v>
+        <v>1208</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1179</v>
+        <v>1209</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G10" s="28">
         <v>46190.520833333336</v>
@@ -19514,10 +19774,10 @@
         <v>46190.645833333336</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>2081</v>
+        <v>2135</v>
       </c>
       <c r="K10" s="8">
         <v>46189.540449513894</v>
@@ -19531,22 +19791,22 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>2082</v>
+        <v>2136</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1180</v>
+        <v>1210</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1181</v>
+        <v>1211</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>294</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G11" s="28">
         <v>46190.5625</v>
@@ -19555,10 +19815,10 @@
         <v>46190.6875</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>2083</v>
+        <v>2137</v>
       </c>
       <c r="K11" s="8">
         <v>46189.59220993056</v>
@@ -19572,22 +19832,22 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>2084</v>
+        <v>2138</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1182</v>
+        <v>1212</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1183</v>
+        <v>1213</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G12" s="28">
         <v>46190.645833333336</v>
@@ -19596,10 +19856,10 @@
         <v>46190.770833333336</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>2085</v>
+        <v>2139</v>
       </c>
       <c r="K12" s="8">
         <v>46189.67538244213</v>
@@ -19613,22 +19873,22 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>2086</v>
+        <v>2140</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1187</v>
+        <v>1217</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1188</v>
+        <v>1218</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G13" s="28">
         <v>46192.354166666664</v>
@@ -19637,10 +19897,10 @@
         <v>46192.40972222222</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>2087</v>
+        <v>2141</v>
       </c>
       <c r="K13" s="8">
         <v>46190.43233309028</v>
@@ -19654,22 +19914,22 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>2088</v>
+        <v>2142</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1189</v>
+        <v>1219</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1190</v>
+        <v>1220</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G14" s="28">
         <v>46192.5</v>
@@ -19678,10 +19938,10 @@
         <v>46192.555555555555</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>2089</v>
+        <v>2143</v>
       </c>
       <c r="K14" s="8">
         <v>46190.491720590275</v>
@@ -19695,22 +19955,22 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>2090</v>
+        <v>2144</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1191</v>
+        <v>1221</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1190</v>
+        <v>1220</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G15" s="28">
         <v>46192.604166666664</v>
@@ -19719,10 +19979,10 @@
         <v>46192.645833333336</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>2091</v>
+        <v>2145</v>
       </c>
       <c r="K15" s="8">
         <v>46190.52233620371</v>
@@ -19736,7 +19996,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>2092</v>
+        <v>2146</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>313</v>
@@ -19745,13 +20005,13 @@
         <v>311</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>294</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G16" s="28">
         <v>46192.375</v>
@@ -19760,10 +20020,10 @@
         <v>46192.5</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>2093</v>
+        <v>2147</v>
       </c>
       <c r="K16" s="8">
         <v>46191.93306221065</v>
@@ -19786,13 +20046,13 @@
         <v>625</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G17" s="28">
         <v>46195.375</v>
@@ -19801,10 +20061,10 @@
         <v>46195.416666666664</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>2094</v>
+        <v>2148</v>
       </c>
       <c r="K17" s="8">
         <v>46193.53691313657</v>
@@ -19818,7 +20078,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>2095</v>
+        <v>2149</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>686</v>
@@ -19827,13 +20087,13 @@
         <v>685</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G18" s="28">
         <v>46195.416666666664</v>
@@ -19842,10 +20102,10 @@
         <v>46195.458333333336</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>2096</v>
+        <v>2150</v>
       </c>
       <c r="K18" s="8">
         <v>46193.56842107639</v>
@@ -19859,7 +20119,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>2097</v>
+        <v>2151</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>710</v>
@@ -19868,13 +20128,13 @@
         <v>709</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G19" s="28">
         <v>46195.458333333336</v>
@@ -19883,10 +20143,10 @@
         <v>46195.5</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>2098</v>
+        <v>2152</v>
       </c>
       <c r="K19" s="8">
         <v>46193.58862525463</v>
@@ -19900,7 +20160,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>2099</v>
+        <v>2153</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>734</v>
@@ -19909,13 +20169,13 @@
         <v>733</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G20" s="28">
         <v>46195.520833333336</v>
@@ -19924,10 +20184,10 @@
         <v>46195.5625</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>2100</v>
+        <v>2154</v>
       </c>
       <c r="K20" s="8">
         <v>46193.68446875</v>
@@ -19941,7 +20201,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>2101</v>
+        <v>2155</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>760</v>
@@ -19950,13 +20210,13 @@
         <v>759</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G21" s="28">
         <v>46195.5625</v>
@@ -19965,10 +20225,10 @@
         <v>46195.729166666664</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>2102</v>
+        <v>2156</v>
       </c>
       <c r="K21" s="8">
         <v>46193.712687708336</v>
@@ -19982,7 +20242,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>2103</v>
+        <v>2157</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>857</v>
@@ -19991,13 +20251,13 @@
         <v>856</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G22" s="28">
         <v>46196.291666666664</v>
@@ -20006,10 +20266,10 @@
         <v>46196.458333333336</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>2104</v>
+        <v>2158</v>
       </c>
       <c r="K22" s="8">
         <v>46193.84181295139</v>
@@ -20020,7 +20280,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>2105</v>
+        <v>2159</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>922</v>
@@ -20029,13 +20289,13 @@
         <v>856</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1147</v>
+        <v>1177</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G23" s="28">
         <v>46195.291666666664</v>
@@ -20044,10 +20304,10 @@
         <v>46195.354166666664</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>2106</v>
+        <v>2160</v>
       </c>
       <c r="K23" s="8">
         <v>46194.40390790509</v>
@@ -20061,7 +20321,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>2107</v>
+        <v>2161</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>946</v>
@@ -20070,13 +20330,13 @@
         <v>856</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1147</v>
+        <v>1177</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G24" s="28">
         <v>46195.729166666664</v>
@@ -20085,10 +20345,10 @@
         <v>46195.791666666664</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>2108</v>
+        <v>2162</v>
       </c>
       <c r="K24" s="8">
         <v>46194.40995349537</v>
@@ -20102,7 +20362,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>2109</v>
+        <v>2163</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>971</v>
@@ -20111,13 +20371,13 @@
         <v>856</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G25" s="28">
         <v>46197.291666666664</v>
@@ -20126,10 +20386,10 @@
         <v>46197.333333333336</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>2110</v>
+        <v>2164</v>
       </c>
       <c r="K25" s="8">
         <v>46194.44835803241</v>
@@ -20140,7 +20400,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>2111</v>
+        <v>2165</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>992</v>
@@ -20149,13 +20409,13 @@
         <v>856</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1147</v>
+        <v>1177</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G26" s="28">
         <v>46197.333333333336</v>
@@ -20164,10 +20424,10 @@
         <v>46197.354166666664</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>2112</v>
+        <v>2166</v>
       </c>
       <c r="K26" s="8">
         <v>46194.45221349537</v>
@@ -20187,13 +20447,13 @@
         <v>1058</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G27" s="28">
         <v>46197.645833333336</v>
@@ -20202,10 +20462,10 @@
         <v>46197.8125</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>2072</v>
+        <v>2126</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>2113</v>
+        <v>2167</v>
       </c>
       <c r="K27" s="8">
         <v>46194.55259876157</v>
@@ -20256,7 +20516,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="8">
-        <v>46194.55621079861</v>
+        <v>46194.839721261575</v>
       </c>
     </row>
   </sheetData>
@@ -49372,136 +49632,488 @@
       </c>
     </row>
     <row r="2646">
-      <c r="A2646" s="8"/>
+      <c r="A2646" s="8">
+        <v>46194.567406250004</v>
+      </c>
+      <c r="B2646" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2646" s="2" t="s">
+        <v>1095</v>
+      </c>
     </row>
     <row r="2647">
-      <c r="A2647" s="8"/>
+      <c r="A2647" s="8">
+        <v>46194.56742101852</v>
+      </c>
+      <c r="B2647" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2647" s="2" t="s">
+        <v>1096</v>
+      </c>
     </row>
     <row r="2648">
-      <c r="A2648" s="8"/>
+      <c r="A2648" s="8">
+        <v>46194.56810553241</v>
+      </c>
+      <c r="B2648" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2648" s="2" t="s">
+        <v>1097</v>
+      </c>
     </row>
     <row r="2649">
-      <c r="A2649" s="8"/>
+      <c r="A2649" s="8">
+        <v>46194.56811346065</v>
+      </c>
+      <c r="B2649" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2649" s="2" t="s">
+        <v>1096</v>
+      </c>
     </row>
     <row r="2650">
-      <c r="A2650" s="8"/>
+      <c r="A2650" s="8">
+        <v>46194.647095567125</v>
+      </c>
+      <c r="B2650" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2650" s="2" t="s">
+        <v>1098</v>
+      </c>
     </row>
     <row r="2651">
-      <c r="A2651" s="8"/>
+      <c r="A2651" s="8">
+        <v>46194.64710400463</v>
+      </c>
+      <c r="B2651" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2651" s="2" t="s">
+        <v>1096</v>
+      </c>
     </row>
     <row r="2652">
-      <c r="A2652" s="8"/>
+      <c r="A2652" s="8">
+        <v>46194.64874497685</v>
+      </c>
+      <c r="B2652" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2652" s="2" t="s">
+        <v>1099</v>
+      </c>
     </row>
     <row r="2653">
-      <c r="A2653" s="8"/>
+      <c r="A2653" s="8">
+        <v>46194.64875472222</v>
+      </c>
+      <c r="B2653" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2653" s="2" t="s">
+        <v>1096</v>
+      </c>
     </row>
     <row r="2654">
-      <c r="A2654" s="8"/>
+      <c r="A2654" s="8">
+        <v>46194.650698321755</v>
+      </c>
+      <c r="B2654" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2654" s="2" t="s">
+        <v>1100</v>
+      </c>
     </row>
     <row r="2655">
-      <c r="A2655" s="8"/>
+      <c r="A2655" s="8">
+        <v>46194.65070881945</v>
+      </c>
+      <c r="B2655" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2655" s="2" t="s">
+        <v>1096</v>
+      </c>
     </row>
     <row r="2656">
-      <c r="A2656" s="8"/>
+      <c r="A2656" s="8">
+        <v>46194.65470252315</v>
+      </c>
+      <c r="B2656" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2656" s="2" t="s">
+        <v>1101</v>
+      </c>
     </row>
     <row r="2657">
-      <c r="A2657" s="8"/>
+      <c r="A2657" s="8">
+        <v>46194.65472309028</v>
+      </c>
+      <c r="B2657" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2657" s="2" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="2658">
-      <c r="A2658" s="8"/>
+      <c r="A2658" s="8">
+        <v>46194.67513361111</v>
+      </c>
+      <c r="B2658" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2658" s="2" t="s">
+        <v>1104</v>
+      </c>
     </row>
     <row r="2659">
-      <c r="A2659" s="8"/>
+      <c r="A2659" s="8">
+        <v>46194.6751524537</v>
+      </c>
+      <c r="B2659" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2659" s="2" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="2660">
-      <c r="A2660" s="8"/>
+      <c r="A2660" s="8">
+        <v>46194.675580497686</v>
+      </c>
+      <c r="B2660" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2660" s="2" t="s">
+        <v>1105</v>
+      </c>
     </row>
     <row r="2661">
-      <c r="A2661" s="8"/>
+      <c r="A2661" s="8">
+        <v>46194.675595636574</v>
+      </c>
+      <c r="B2661" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2661" s="2" t="s">
+        <v>1106</v>
+      </c>
     </row>
     <row r="2662">
-      <c r="A2662" s="8"/>
+      <c r="A2662" s="8">
+        <v>46194.67569178241</v>
+      </c>
+      <c r="B2662" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2662" s="2" t="s">
+        <v>1107</v>
+      </c>
     </row>
     <row r="2663">
-      <c r="A2663" s="8"/>
+      <c r="A2663" s="8">
+        <v>46194.67570677084</v>
+      </c>
+      <c r="B2663" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2663" s="2" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="2664">
-      <c r="A2664" s="8"/>
+      <c r="A2664" s="8">
+        <v>46194.688770787034</v>
+      </c>
+      <c r="B2664" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2664" s="2" t="s">
+        <v>1108</v>
+      </c>
     </row>
     <row r="2665">
-      <c r="A2665" s="8"/>
+      <c r="A2665" s="8">
+        <v>46194.68879299768</v>
+      </c>
+      <c r="B2665" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2665" s="2" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="2666">
-      <c r="A2666" s="8"/>
+      <c r="A2666" s="8">
+        <v>46194.694259131946</v>
+      </c>
+      <c r="B2666" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2666" s="2" t="s">
+        <v>1109</v>
+      </c>
     </row>
     <row r="2667">
-      <c r="A2667" s="8"/>
+      <c r="A2667" s="8">
+        <v>46194.69427850694</v>
+      </c>
+      <c r="B2667" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2667" s="2" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="2668">
-      <c r="A2668" s="8"/>
+      <c r="A2668" s="8">
+        <v>46194.70042849537</v>
+      </c>
+      <c r="B2668" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2668" s="2" t="s">
+        <v>1110</v>
+      </c>
     </row>
     <row r="2669">
-      <c r="A2669" s="8"/>
+      <c r="A2669" s="8">
+        <v>46194.700466724535</v>
+      </c>
+      <c r="B2669" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2669" s="2" t="s">
+        <v>1111</v>
+      </c>
     </row>
     <row r="2670">
-      <c r="A2670" s="8"/>
+      <c r="A2670" s="8">
+        <v>46194.700605949074</v>
+      </c>
+      <c r="B2670" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2670" s="2" t="s">
+        <v>1112</v>
+      </c>
     </row>
     <row r="2671">
-      <c r="A2671" s="8"/>
+      <c r="A2671" s="8">
+        <v>46194.70063684028</v>
+      </c>
+      <c r="B2671" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2671" s="2" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="2672">
-      <c r="A2672" s="8"/>
+      <c r="A2672" s="8">
+        <v>46194.700723263886</v>
+      </c>
+      <c r="B2672" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C2672" s="2" t="s">
+        <v>1114</v>
+      </c>
     </row>
     <row r="2673">
-      <c r="A2673" s="8"/>
+      <c r="A2673" s="8">
+        <v>46194.706155312495</v>
+      </c>
+      <c r="B2673" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2673" s="2" t="s">
+        <v>1115</v>
+      </c>
     </row>
     <row r="2674">
-      <c r="A2674" s="8"/>
+      <c r="A2674" s="8">
+        <v>46194.70617613426</v>
+      </c>
+      <c r="B2674" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2674" s="2" t="s">
+        <v>1111</v>
+      </c>
     </row>
     <row r="2675">
-      <c r="A2675" s="8"/>
+      <c r="A2675" s="8">
+        <v>46194.70632532408</v>
+      </c>
+      <c r="B2675" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2675" s="2" t="s">
+        <v>1116</v>
+      </c>
     </row>
     <row r="2676">
-      <c r="A2676" s="8"/>
+      <c r="A2676" s="8">
+        <v>46194.70634900463</v>
+      </c>
+      <c r="B2676" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2676" s="2" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="2677">
-      <c r="A2677" s="8"/>
+      <c r="A2677" s="8">
+        <v>46194.706611354166</v>
+      </c>
+      <c r="B2677" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2677" s="2" t="s">
+        <v>1117</v>
+      </c>
     </row>
     <row r="2678">
-      <c r="A2678" s="8"/>
+      <c r="A2678" s="8">
+        <v>46194.70664020833</v>
+      </c>
+      <c r="B2678" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2678" s="2" t="s">
+        <v>1111</v>
+      </c>
     </row>
     <row r="2679">
-      <c r="A2679" s="8"/>
+      <c r="A2679" s="8">
+        <v>46194.707403831024</v>
+      </c>
+      <c r="B2679" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2679" s="2" t="s">
+        <v>1118</v>
+      </c>
     </row>
     <row r="2680">
-      <c r="A2680" s="8"/>
+      <c r="A2680" s="8">
+        <v>46194.707418125</v>
+      </c>
+      <c r="B2680" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2680" s="2" t="s">
+        <v>1119</v>
+      </c>
     </row>
     <row r="2681">
-      <c r="A2681" s="8"/>
+      <c r="A2681" s="8">
+        <v>46194.70756113426</v>
+      </c>
+      <c r="B2681" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2681" s="2" t="s">
+        <v>1120</v>
+      </c>
     </row>
     <row r="2682">
-      <c r="A2682" s="8"/>
+      <c r="A2682" s="8">
+        <v>46194.707585474534</v>
+      </c>
+      <c r="B2682" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2682" s="2" t="s">
+        <v>1121</v>
+      </c>
     </row>
     <row r="2683">
-      <c r="A2683" s="8"/>
+      <c r="A2683" s="8">
+        <v>46194.707612488426</v>
+      </c>
+      <c r="B2683" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C2683" s="2" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="2684">
-      <c r="A2684" s="8"/>
+      <c r="A2684" s="8">
+        <v>46194.839197395835</v>
+      </c>
+      <c r="B2684" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2684" s="2" t="s">
+        <v>1122</v>
+      </c>
     </row>
     <row r="2685">
-      <c r="A2685" s="8"/>
+      <c r="A2685" s="8">
+        <v>46194.83921982639</v>
+      </c>
+      <c r="B2685" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2685" s="2" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="2686">
-      <c r="A2686" s="8"/>
+      <c r="A2686" s="8">
+        <v>46194.83940607639</v>
+      </c>
+      <c r="B2686" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2686" s="2" t="s">
+        <v>1123</v>
+      </c>
     </row>
     <row r="2687">
-      <c r="A2687" s="8"/>
+      <c r="A2687" s="8">
+        <v>46194.83942418981</v>
+      </c>
+      <c r="B2687" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2687" s="2" t="s">
+        <v>1124</v>
+      </c>
     </row>
     <row r="2688">
-      <c r="A2688" s="8"/>
+      <c r="A2688" s="8">
+        <v>46194.83967707176</v>
+      </c>
+      <c r="B2688" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2688" s="2" t="s">
+        <v>1125</v>
+      </c>
     </row>
     <row r="2689">
-      <c r="A2689" s="8"/>
+      <c r="A2689" s="8">
+        <v>46194.83969493056</v>
+      </c>
+      <c r="B2689" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C2689" s="2" t="s">
+        <v>1111</v>
+      </c>
     </row>
     <row r="2690">
       <c r="A2690" s="8"/>
@@ -51693,130 +52305,130 @@
         <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1095</v>
+        <v>1126</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1096</v>
+        <v>1127</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1097</v>
+        <v>1128</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1098</v>
+        <v>1129</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1099</v>
+        <v>1130</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1100</v>
+        <v>1131</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1101</v>
+        <v>1132</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>1102</v>
+        <v>1133</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>1103</v>
+        <v>1134</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>1104</v>
+        <v>1135</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>1105</v>
+        <v>1136</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>1106</v>
+        <v>1137</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>1107</v>
+        <v>1138</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>1108</v>
+        <v>1139</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>1109</v>
+        <v>1140</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>1110</v>
+        <v>1141</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>1111</v>
+        <v>1142</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>1112</v>
+        <v>1143</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>1113</v>
+        <v>1144</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>1114</v>
+        <v>1145</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>1115</v>
+        <v>1146</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>1116</v>
+        <v>1147</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>1117</v>
+        <v>1148</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>1118</v>
+        <v>1149</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>1119</v>
+        <v>1150</v>
       </c>
       <c r="AA1" s="2" t="s">
-        <v>1120</v>
+        <v>1151</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>1121</v>
+        <v>1152</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>1122</v>
+        <v>1153</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>1123</v>
+        <v>1154</v>
       </c>
       <c r="AE1" s="13" t="s">
-        <v>1124</v>
+        <v>1155</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>1125</v>
+        <v>1156</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>1126</v>
+        <v>1157</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>1127</v>
+        <v>1158</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>1128</v>
+        <v>1159</v>
       </c>
       <c r="AJ1" s="2" t="s">
-        <v>1129</v>
+        <v>1160</v>
       </c>
       <c r="AK1" s="2" t="s">
-        <v>1130</v>
+        <v>1161</v>
       </c>
       <c r="AL1" s="2" t="s">
-        <v>1131</v>
+        <v>1162</v>
       </c>
       <c r="AM1" s="2" t="s">
-        <v>1132</v>
+        <v>1163</v>
       </c>
       <c r="AN1" s="2" t="s">
-        <v>1133</v>
+        <v>1164</v>
       </c>
       <c r="AO1" s="2" t="s">
-        <v>1134</v>
+        <v>1165</v>
       </c>
       <c r="AP1" s="2" t="s">
-        <v>1135</v>
+        <v>1166</v>
       </c>
       <c r="AQ1" s="2" t="s">
-        <v>1136</v>
+        <v>1167</v>
       </c>
       <c r="AR1" s="2" t="s">
         <v>44</v>
@@ -51858,10 +52470,10 @@
       <c r="AI2" s="10"/>
       <c r="AJ2" s="10"/>
       <c r="AQ2" s="2" t="s">
-        <v>1137</v>
+        <v>1114</v>
       </c>
       <c r="AS2" s="14">
-        <v>46194.55584671296</v>
+        <v>46194.83971667824</v>
       </c>
     </row>
     <row r="3">
@@ -54868,42 +55480,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1096</v>
+        <v>1127</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1095</v>
+        <v>1126</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1138</v>
+        <v>1168</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1139</v>
+        <v>1169</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1140</v>
+        <v>1170</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1141</v>
+        <v>1171</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1142</v>
+        <v>1172</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>27</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1146</v>
+        <v>1176</v>
       </c>
       <c r="D2" s="7">
         <v>1500.0</v>
@@ -54926,13 +55538,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>1147</v>
+        <v>1177</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1148</v>
+        <v>1178</v>
       </c>
       <c r="D3" s="7">
         <v>500.0</v>
@@ -54973,31 +55585,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1126</v>
+        <v>1157</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1123</v>
+        <v>1154</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1149</v>
+        <v>1179</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1096</v>
+        <v>1127</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1130</v>
+        <v>1161</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1150</v>
+        <v>1180</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1151</v>
+        <v>1181</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>1152</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="2">
@@ -55005,16 +55617,16 @@
         <v>856</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1153</v>
+        <v>1183</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>1154</v>
+        <v>1184</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1147</v>
+        <v>1177</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1155</v>
+        <v>1185</v>
       </c>
       <c r="F2" s="7">
         <v>30.0</v>
@@ -55031,16 +55643,16 @@
         <v>856</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1156</v>
+        <v>1186</v>
       </c>
       <c r="C3" s="2">
         <v>1.12223344E8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1157</v>
+        <v>1187</v>
       </c>
       <c r="F3" s="7">
         <v>360.0</v>
@@ -58054,25 +58666,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1158</v>
+        <v>1188</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1126</v>
+        <v>1157</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1096</v>
+        <v>1127</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1151</v>
+        <v>1181</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1150</v>
+        <v>1180</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>45</v>
@@ -58097,48 +58709,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="16" t="s">
-        <v>1159</v>
+        <v>1189</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>1126</v>
       </c>
-      <c r="C1" s="16" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>1095</v>
-      </c>
       <c r="F1" s="16" t="s">
-        <v>1160</v>
+        <v>1190</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1125</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1161</v>
+        <v>1191</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1162</v>
+        <v>1192</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G2" s="8">
         <v>46188.65644706019</v>
@@ -58146,22 +58758,22 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>1165</v>
+        <v>1195</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1162</v>
+        <v>1192</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G3" s="8">
         <v>46188.662697928245</v>
@@ -58169,22 +58781,22 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>1166</v>
+        <v>1196</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1167</v>
+        <v>1197</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G4" s="8">
         <v>46188.714445289355</v>
@@ -58192,22 +58804,22 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>1169</v>
+        <v>1199</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1170</v>
+        <v>1200</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G5" s="8">
         <v>46188.9084655787</v>
@@ -58215,22 +58827,22 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>1171</v>
+        <v>1201</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1162</v>
+        <v>1192</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G6" s="8">
         <v>46188.92779746528</v>
@@ -58238,22 +58850,22 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>1172</v>
+        <v>1202</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1173</v>
+        <v>1203</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>294</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G7" s="8">
         <v>46189.31786376158</v>
@@ -58261,22 +58873,22 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>1174</v>
+        <v>1204</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1175</v>
+        <v>1205</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G8" s="8">
         <v>46189.43935428241</v>
@@ -58284,22 +58896,22 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>1176</v>
+        <v>1206</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1177</v>
+        <v>1207</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>294</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G9" s="8">
         <v>46189.50189128472</v>
@@ -58307,22 +58919,22 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>1178</v>
+        <v>1208</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1179</v>
+        <v>1209</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G10" s="8">
         <v>46189.540140439814</v>
@@ -58330,22 +58942,22 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>1180</v>
+        <v>1210</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1181</v>
+        <v>1211</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>294</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G11" s="8">
         <v>46189.59163065972</v>
@@ -58353,22 +58965,22 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>1182</v>
+        <v>1212</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1183</v>
+        <v>1213</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G12" s="8">
         <v>46189.675199687495</v>
@@ -58376,22 +58988,22 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>1184</v>
+        <v>1214</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1185</v>
+        <v>1215</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1186</v>
+        <v>1216</v>
       </c>
       <c r="G13" s="8">
         <v>46190.42387542824</v>
@@ -58399,22 +59011,22 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>1187</v>
+        <v>1217</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1188</v>
+        <v>1218</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G14" s="8">
         <v>46190.432098171295</v>
@@ -58422,22 +59034,22 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>1189</v>
+        <v>1219</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1190</v>
+        <v>1220</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G15" s="8">
         <v>46190.491500752316</v>
@@ -58445,22 +59057,22 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>1191</v>
+        <v>1221</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1190</v>
+        <v>1220</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G16" s="8">
         <v>46190.5221158912</v>
@@ -58474,16 +59086,16 @@
         <v>311</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>294</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G17" s="8">
         <v>46191.93275685185</v>
@@ -58497,16 +59109,16 @@
         <v>625</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G18" s="8">
         <v>46193.53663653936</v>
@@ -58520,16 +59132,16 @@
         <v>685</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G19" s="8">
         <v>46193.568148819446</v>
@@ -58543,16 +59155,16 @@
         <v>709</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G20" s="8">
         <v>46193.58833770834</v>
@@ -58566,16 +59178,16 @@
         <v>733</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G21" s="8">
         <v>46193.68419712963</v>
@@ -58589,16 +59201,16 @@
         <v>759</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G22" s="8">
         <v>46193.7124237963</v>
@@ -58612,16 +59224,16 @@
         <v>856</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G23" s="8">
         <v>46193.84161289352</v>
@@ -58635,16 +59247,16 @@
         <v>856</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1147</v>
+        <v>1177</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G24" s="8">
         <v>46194.403384398145</v>
@@ -58658,16 +59270,16 @@
         <v>856</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1147</v>
+        <v>1177</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G25" s="8">
         <v>46194.40971107639</v>
@@ -58681,16 +59293,16 @@
         <v>856</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G26" s="8">
         <v>46194.44812680555</v>
@@ -58704,16 +59316,16 @@
         <v>856</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1147</v>
+        <v>1177</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G27" s="8">
         <v>46194.45200535879</v>
@@ -58727,16 +59339,16 @@
         <v>1058</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>616</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="G28" s="8">
         <v>46194.5521537037</v>
